--- a/公司项目/认知作战/文档/软件概要设计-模块功能拆分-v2.xlsx
+++ b/公司项目/认知作战/文档/软件概要设计-模块功能拆分-v2.xlsx
@@ -34,3077 +34,3077 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="1023">
-  <si>
-    <t>子系统(一级软部件)</t>
-  </si>
-  <si>
-    <t>代号</t>
-  </si>
-  <si>
-    <t>模块数</t>
-  </si>
-  <si>
-    <t>模块编号</t>
-  </si>
-  <si>
-    <t>模块名称(二级软部件)</t>
-  </si>
-  <si>
-    <t>对应需求</t>
-  </si>
-  <si>
-    <t>职责简述</t>
-  </si>
-  <si>
-    <t>M-DC-00</t>
-  </si>
-  <si>
-    <t>DC</t>
-  </si>
-  <si>
-    <t>4个</t>
-  </si>
-  <si>
-    <t>R-DC-001~008</t>
-  </si>
-  <si>
-    <t>基础设施层的数据采集与 ETL 处理底座，采用「任务驱动采集」范式：采集任务由人工/OCC 情报回注注入任务池，爬虫作为执行器消费任务、按目标定向抓取；通过情报回注与目标扩散形成「OCC 分析→DC 采集」跨子系统反向闭环。原「数据分析与情报」V3.3 起移至 OCC。</t>
-  </si>
-  <si>
-    <t>M-DC-01</t>
-  </si>
-  <si>
-    <t>采集调度与限流（输入闸门与调度大脑）</t>
-  </si>
-  <si>
-    <t>R-DC-003</t>
-  </si>
-  <si>
-    <t>消费人工与情报回注注入的采集任务，管理任务池、目标级去重、调度队列与配额限流，使采得不重复、不丢失、不失控；支撑情报回注入池去重与配额约束。</t>
-  </si>
-  <si>
-    <t>M-DC-02</t>
-  </si>
-  <si>
-    <t>多平台数据采集与策略自优化（爬虫执行器）</t>
-  </si>
-  <si>
-    <t>R-DC-001,004</t>
-  </si>
-  <si>
-    <t>消费任务池下发的任务，按任务目标从 TikTok/Instagram/Facebook/YouTube/X 等海外社交平台采集原始数据（用户/内容/互动/关系），使用代理 IP 与维护账号应对反爬，并面向海外社交平台提供代理网络出口（按平台/地区分配、定时轮换、可用性检测、失效剔除），基于历史指标自适应优化采集策略。</t>
-  </si>
-  <si>
-    <t>M-DC-03</t>
-  </si>
-  <si>
-    <t>数据处理与存储（ETL 数据加工厂）</t>
-  </si>
-  <si>
-    <t>R-DC-005,006</t>
-  </si>
-  <si>
-    <t>对经 Kafka 流入的原始数据做分布式批处理清洗（字段提取、格式标准化、去重、关联），产出结构化干净数据，并按数据特征持久化到不同存储模型（明细入 HBase、元数据/索引入关系库、关系数据入图库），供分析与检索按需读取。</t>
-  </si>
-  <si>
-    <t>M-DC-04</t>
-  </si>
-  <si>
-    <t>情报驱动采集与目标扩散（反向驱动大脑）</t>
-  </si>
-  <si>
-    <t>R-DC-007,008</t>
-  </si>
-  <si>
-    <t>打通「OCC 分析→DC 采集」跨子系统反向驱动链路，使 OCC 数据分析与情报（R-OCC-002~005）产出的目标个体/关联实体/传播节点回注任务池并按关系扩散采集，形成「发现线索→定向扩散采集→锁定目标」的情报驱动闭环。</t>
-  </si>
-  <si>
-    <t>M-MC-00</t>
-  </si>
-  <si>
-    <t>MC</t>
-  </si>
-  <si>
-    <t>14个</t>
-  </si>
-  <si>
-    <t>R-MC-001~014</t>
-  </si>
-  <si>
-    <t>统一自动化执行引擎与多终端执行网关：统一管理移动端（真机/云手机/ARM 板卡/虚拟化真机）与桌面端（指纹浏览器 Profile）两类执行终端；收口所有终端动作（可观测/可审计/可熔断）；承担账号资源平台级权威源与智能体执行宿主两项职责。</t>
-  </si>
-  <si>
-    <t>M-MC-01</t>
-  </si>
-  <si>
-    <t>执行终端接入与台账（终端资源池管理者）</t>
-  </si>
-  <si>
-    <t>R-MC-001</t>
-  </si>
-  <si>
-    <t>统一管理四类执行终端（移动端真机/云手机/ARM 板卡/虚拟化真机、桌面端指纹浏览器 Profile）的接入注册、台账维护、分组标签、实时状态监控与批量操作，提供终端资源池。</t>
-  </si>
-  <si>
-    <t>M-MC-02</t>
-  </si>
-  <si>
-    <t>终端身份与环境隔离（终端身份伪造与隔离底座）</t>
-  </si>
-  <si>
-    <t>R-MC-002</t>
-  </si>
-  <si>
-    <t>通过终端指纹固化（移动端硬件/软件指纹、桌面端 Profile 渲染层指纹 20+ 维），使终端长期呈现一致真人设备身份；终端间环境（指纹、网络、账号、Cookie/缓存）相互隔离，降低被风控识别概率。</t>
-  </si>
-  <si>
-    <t>M-MC-03</t>
-  </si>
-  <si>
-    <t>终端风控分级与代理绑定（终端健康哨兵与风控对抗）</t>
-  </si>
-  <si>
-    <t>R-MC-003</t>
-  </si>
-  <si>
-    <t>按指纹真实度对终端风控分级（养号优先选高真实度）；识别平台风控信号主动规避、持续触发时降级；为每终端/Profile 分配独立固定代理 IP 并绑定（仅失效时切换重新固定）。</t>
-  </si>
-  <si>
-    <t>M-MC-04</t>
-  </si>
-  <si>
-    <t>远程控制（人机交互窗口）</t>
-  </si>
-  <si>
-    <t>R-MC-004</t>
-  </si>
-  <si>
-    <t>对单台及多台终端提供低延迟实时画面预览与输入控制，支持多终端同屏监控；移动端用 WebRTC 通道、桌面端指纹浏览器 Profile 用商用 API 画面预览。远控通道与任务执行通道相互分离。</t>
-  </si>
-  <si>
-    <t>M-MC-05</t>
-  </si>
-  <si>
-    <t>统一执行网关（动作收口核心）</t>
-  </si>
-  <si>
-    <t>R-MC-005</t>
-  </si>
-  <si>
-    <t>以统一执行网关作为所有执行终端动作的唯一收口，对动作鉴权（校验来源/目标合法性）、记录（写动作日志并全量上报 OM）、熔断（检测风控信号或异常频率时停止后续动作）、转发落地；保证每一个动作可观测、可审计、可熔断、动作不裸奔。</t>
-  </si>
-  <si>
-    <t>M-MC-06</t>
-  </si>
-  <si>
-    <t>双执行模式与执行目标（执行引擎）</t>
-  </si>
-  <si>
-    <t>R-MC-006</t>
-  </si>
-  <si>
-    <t>提供脚本模式与智能体模式两种执行引擎，分别承载固定流程驱动与大模型实时决策驱动的作业，覆盖移动端终端与桌面端 Profile，支持群控、养号与内容投放三类执行目标；所有动作经 R-MC-005 统一执行网关落地。</t>
-  </si>
-  <si>
-    <t>M-MC-07</t>
-  </si>
-  <si>
-    <t>任务管理（任务调度中枢）</t>
-  </si>
-  <si>
-    <t>R-MC-007</t>
-  </si>
-  <si>
-    <t>把操作意图转换为设备可执行的任务并调度，支撑各类作业的排队、分发、重试与定时执行。</t>
-  </si>
-  <si>
-    <t>M-MC-08</t>
-  </si>
-  <si>
-    <t>自动化编排能力（自动化能力中枢）</t>
-  </si>
-  <si>
-    <t>R-MC-008</t>
-  </si>
-  <si>
-    <t>提供自动化能力的中枢，覆盖从模板任务到可视化工作流再到脚本开发的递进式编排，支持 ADB/CDP 等多种自动化通道，针对 TikTok/Facebook 等平台实现模拟点击自动化；产出动作均经执行网关落地，不直接操作设备。</t>
-  </si>
-  <si>
-    <t>M-MC-09</t>
-  </si>
-  <si>
-    <t>账号操作编排与养号（账号自动化编排）</t>
-  </si>
-  <si>
-    <t>R-MC-009</t>
-  </si>
-  <si>
-    <t>承载养号、账号-终端-代理绑定、登录状态维护等可自动化的账号操作的执行编排，以及养号拟人化节奏策略（内置）。认知作战账号经移动端 ADB/无障碍通道养号、爬虫账号经桌面端 CDP 通道养护。</t>
-  </si>
-  <si>
-    <t>M-MC-10</t>
-  </si>
-  <si>
-    <t>可观测性与作业统计复盘（全链路可观测与复盘大脑）</t>
-  </si>
-  <si>
-    <t>R-MC-010</t>
-  </si>
-  <si>
-    <t>使终端、账号、任务的每个动作可知可追溯，支撑记录、回传、告警、审计，并完成蜂群作业数据统计与任务复盘、将投送效果联动回传上游供效果评估闭环；动作留痕与作业统计统一收口于本功能（避免重复采集）。</t>
-  </si>
-  <si>
-    <t>M-MC-11</t>
-  </si>
-  <si>
-    <t>账号主数据管理（账号资源权威源）</t>
-  </si>
-  <si>
-    <t>R-MC-011</t>
-  </si>
-  <si>
-    <t>平台级权威源，唯一维护社交媒体账号主数据（注册、凭据、验证、风险评估、生命周期、账号分类），经事件总线向 DC/SWM/OCC 分发 account_id，保证全网一致、凭据加密、被封账号全网即时失效；账号分爬虫账号(桌面端)与认知作战账号(移动端)两类。</t>
-  </si>
-  <si>
-    <t>M-MC-12</t>
-  </si>
-  <si>
-    <t>智能体账号分层分组（账号组织）</t>
-  </si>
-  <si>
-    <t>R-MC-012</t>
-  </si>
-  <si>
-    <t>对智能体账号按业务目标/平台/地区/风险等级分层分组，形成可控账号层级结构，并管理智能体账号作业生命周期（待激活/活跃/休眠/受限/封禁/回收）的自动与人工流转。</t>
-  </si>
-  <si>
-    <t>M-MC-13</t>
-  </si>
-  <si>
-    <t>智能体账号绑定与资产迁移（四元作战单元）</t>
-  </si>
-  <si>
-    <t>R-MC-013</t>
-  </si>
-  <si>
-    <t>维护账号与智能体定义（agent_id）严格 1:1 绑定，叠加账号-终端-代理绑定形成四元作战单元（agent_id:account_id:终端:代理 IP = 1:1:1:1）；账号被封后支持资产迁移整体继承人格（人设标签/提示词版本/记忆）。</t>
-  </si>
-  <si>
-    <t>M-MC-14</t>
-  </si>
-  <si>
-    <t>智能体执行宿主与同步（智能体执行宿主）</t>
-  </si>
-  <si>
-    <t>R-MC-014</t>
-  </si>
-  <si>
-    <t>作为智能体执行宿主，接收并持存 SWM 同步来的智能体定义（以 agent_id 为标识，含人设标签/提示词/记忆/作业策略），任务执行时调用这些定义驱动设备作业，执行前校验人设一致性（不一致拒绝执行）；确立「SWM 定义中心、MC 执行宿主」分工。</t>
-  </si>
-  <si>
-    <t>M-OM-00</t>
-  </si>
-  <si>
-    <t>OM</t>
-  </si>
-  <si>
-    <t>R-OM-001~002</t>
-  </si>
-  <si>
-    <t>汇聚全系统日志与指标，形成统一运维数据底座，支撑常态化运维与告警。</t>
-  </si>
-  <si>
-    <t>M-OM-01</t>
-  </si>
-  <si>
-    <t>日志汇聚与检索（日志数据底座）</t>
-  </si>
-  <si>
-    <t>R-OM-001(日志)</t>
-  </si>
-  <si>
-    <t>通过日志采集将各子系统日志汇聚至统一日志库，支持全文检索。</t>
-  </si>
-  <si>
-    <t>M-OM-02</t>
-  </si>
-  <si>
-    <t>指标采集与时序存储（指标数据底座）</t>
-  </si>
-  <si>
-    <t>R-OM-001(指标)</t>
-  </si>
-  <si>
-    <t>通过指标采集器采集设备在线率、任务成功率、爬虫吞吐量、队列积压等指标，形成时序数据存储，供告警与看板消费。</t>
-  </si>
-  <si>
-    <t>M-OM-03</t>
-  </si>
-  <si>
-    <t>告警引擎（告警大脑）</t>
-  </si>
-  <si>
-    <t>R-OM-002(告警)</t>
-  </si>
-  <si>
-    <t>基于指标与规则产生告警，支持阈值告警与异常检测告警，通过多渠道通知，含告警风暴聚合去重。</t>
-  </si>
-  <si>
-    <t>M-OM-04</t>
-  </si>
-  <si>
-    <t>运维可视化与作业（运维作业台）</t>
-  </si>
-  <si>
-    <t>R-OM-002(看板+运维)</t>
-  </si>
-  <si>
-    <t>提供多维可视化看板，并支持日志查询、故障定位、巡检与容量观测等常态化运维操作。</t>
-  </si>
-  <si>
-    <t>M-COM-00</t>
-  </si>
-  <si>
-    <t>COM</t>
-  </si>
-  <si>
-    <t>2个</t>
-  </si>
-  <si>
-    <t>R-COM-001</t>
-  </si>
-  <si>
-    <t>为各子系统提供统一的用户认证、基于角色的访问控制与组织管理，支持多组织数据隔离。</t>
-  </si>
-  <si>
-    <t>M-COM-01</t>
-  </si>
-  <si>
-    <t>身份认证（身份守门人）</t>
-  </si>
-  <si>
-    <t>R-COM-001(AuthN)</t>
-  </si>
-  <si>
-    <t>提供统一的登录认证与双因素认证，签发认证令牌。</t>
-  </si>
-  <si>
-    <t>M-COM-02</t>
-  </si>
-  <si>
-    <t>权限与组织管理（权限决策与组织隔离）</t>
-  </si>
-  <si>
-    <t>R-COM-001(AuthZ)</t>
-  </si>
-  <si>
-    <t>基于角色访问控制进行权限决策，管理组织与成员，并对多组织/多租户进行数据隔离。</t>
-  </si>
-  <si>
-    <t>M-SWM-00</t>
-  </si>
-  <si>
-    <t>SWM</t>
-  </si>
-  <si>
-    <t>6个</t>
-  </si>
-  <si>
-    <t>R-SWM-001~004</t>
-  </si>
-  <si>
-    <t>执行层的「智能体定义与记忆中心」：根据人设(画像/账号属性)编写驱动智能体作业的提示词与记忆，将智能体定义(人设标签/提示词/记忆/作业策略)以 agent_id 同步下发至 MC 持存；承担智能体构建、评测、提示词与人设管理、记忆管理；不直接操作设备。</t>
-  </si>
-  <si>
-    <t>M-SWM-01</t>
-  </si>
-  <si>
-    <t>人设标签管理（智能体人格定义中心）</t>
-  </si>
-  <si>
-    <t>R-SWM-001(人设)</t>
-  </si>
-  <si>
-    <t>为每个 agent_id 绑定人设标签(身份特征/立场倾向/语言风格/兴趣领域等画像属性)；人设挂 agent_id，经 agent_id↔account_id 1:1 绑定间接对应账号；不复制账号主数据。</t>
-  </si>
-  <si>
-    <t>M-SWM-02</t>
-  </si>
-  <si>
-    <t>提示词模板库与版本管理（提示词资产管理）</t>
-  </si>
-  <si>
-    <t>R-SWM-001(资产)</t>
-  </si>
-  <si>
-    <t>建立提示词模板库并按用途/平台/目标分类管理；对提示词进行版本管理，以 agent_id 为主键索引，支持版本对比/回滚/变更记录。</t>
-  </si>
-  <si>
-    <t>M-SWM-03</t>
-  </si>
-  <si>
-    <t>提示词场景适配与动态调用（提示词运行时引擎）</t>
-  </si>
-  <si>
-    <t>R-SWM-001(运行时)</t>
-  </si>
-  <si>
-    <t>按作业场景(人设标签/目标受众/当前态势)适配提示词，作业时动态调用并填充生成最终作业指令。</t>
-  </si>
-  <si>
-    <t>M-SWM-04</t>
-  </si>
-  <si>
-    <t>蜂群记忆管理（智能体记忆中枢）</t>
-  </si>
-  <si>
-    <t>R-SWM-002</t>
-  </si>
-  <si>
-    <t>实现智能体作业记忆的存储、场景沉淀、历史复用与个性化状态延续，使智能体长期行为符合人设且不断演进。</t>
-  </si>
-  <si>
-    <t>M-SWM-05</t>
-  </si>
-  <si>
-    <t>智能体构建与定义下发（智能体装配工厂）</t>
-  </si>
-  <si>
-    <t>R-SWM-003</t>
-  </si>
-  <si>
-    <t>根据人设标签编写提示词与记忆初值、配置作业策略，组装为完整智能体定义并以 agent_id 为标识，经 II-14 同步至 MC 持存、供 OCC 作战编排引用。</t>
-  </si>
-  <si>
-    <t>M-SWM-06</t>
-  </si>
-  <si>
-    <t>智能体评测与迭代决策（智能体质量裁判）</t>
-  </si>
-  <si>
-    <t>R-SWM-004</t>
-  </si>
-  <si>
-    <t>对构建出的智能体采用「线上效果 + 离线数据集」双轨评测范式评估有效性/稳定性/合规性；离线评测以『评测集、评估器、实验』三类实体组织，淘汰低效定义、迭代优化高价值定义，形成「构建→评测→迭代」闭环。</t>
-  </si>
-  <si>
-    <t>M-IRS-00</t>
-  </si>
-  <si>
-    <t>IRS</t>
-  </si>
-  <si>
-    <t>1个</t>
-  </si>
-  <si>
-    <t>R-IRS-001</t>
-  </si>
-  <si>
-    <t>系统底层推理基础设施(非业务子系统)：部署本地大模型并提供推理调用，使全系统 AI 推理不依赖外部公有云。</t>
-  </si>
-  <si>
-    <t>M-IRS-01</t>
-  </si>
-  <si>
-    <t>本地大模型部署（底座推理能力提供者）</t>
-  </si>
-  <si>
-    <t>在私有化环境中部署本地大模型，完成模型加载与服务实例化，对外提供统一推理调用接口。</t>
-  </si>
-  <si>
-    <t>M-OCC-00</t>
-  </si>
-  <si>
-    <t>OCC</t>
-  </si>
-  <si>
-    <t>9个</t>
-  </si>
-  <si>
-    <t>R-OCC-001~009</t>
-  </si>
-  <si>
-    <t>全链路指挥大脑：构建「目标识别→数据分析与情报→作战编排→效果评估」作战闭环，并承担内容资源统一管理(唯一权威源)；基于 DC 采集的原始舆情/传播数据（经 II-13）与 IRS 推理产出作战方案，在本子系统内完成数据分析与情报研判（V3.3 起由 DC 移入），以作战编排直接编排 MC 中智能体节点与自动化脚本节点形成执行流程落地。</t>
-  </si>
-  <si>
-    <t>M-OCC-01</t>
-  </si>
-  <si>
-    <t>目标档案与状态管理（目标数据管家）</t>
-  </si>
-  <si>
-    <t>R-OCC-001(实体)</t>
-  </si>
-  <si>
-    <t>识别舆情事件目标要素并建档为数据对象，支持建档、属性修改、状态流转与删除；目标即数据，可随事件演进而更新；本期以人工识别为主、系统提供数据维护支撑。</t>
-  </si>
-  <si>
-    <t>M-OCC-02</t>
-  </si>
-  <si>
-    <t>数据分析与情报（情报分析大脑）</t>
-  </si>
-  <si>
-    <t>R-OCC-002~005</t>
-  </si>
-  <si>
-    <t>V3.3 起由 DC 移入。对 DC 采集与 ETL 加工的数据（经 II-13）进行分析，提供从群体到个体的下钻筛选、关系图谱与图查询、实体检索与全维度档案、文本智能分析能力，支撑目标识别与内容研判；分析产出供 M-OCC-01 目标识别融合，并经 II-15 反向驱动 DC 情报回注采集（R-DC-007）。</t>
-  </si>
-  <si>
-    <t>M-OCC-03</t>
-  </si>
-  <si>
-    <t>目标关联网络（目标关系图谱）</t>
-  </si>
-  <si>
-    <t>R-OCC-001(图结构)</t>
-  </si>
-  <si>
-    <t>目标之间建立关联关系（如一个事件主体关联多个传播源头、一个干预目标关联多个薄弱点），形成目标关系网络，支持关系网络查询。</t>
-  </si>
-  <si>
-    <t>M-OCC-04</t>
-  </si>
-  <si>
-    <t>作战方案规划（作战参谋）</t>
-  </si>
-  <si>
-    <t>R-OCC-006(决策)</t>
-  </si>
-  <si>
-    <t>根据目标档案中的干预切入点匹配干预策略，生成具体的作业方案（含内容/账号/时间/节奏）；本期以人工匹配为主。</t>
-  </si>
-  <si>
-    <t>M-OCC-05</t>
-  </si>
-  <si>
-    <t>编排执行引擎（编排执行引擎）</t>
-  </si>
-  <si>
-    <t>R-OCC-006(建模+运行)</t>
-  </si>
-  <si>
-    <t>将作业方案编排为执行流程：以 MC 中智能体节点/自动化脚本节点为编排实体，按内容/账号/时间/节奏组织节点前后序/并行/分支关系形成可执行流程图；编排落地后由 MC 统一执行网关收口，节点失败按定义回滚/跳过/转人工。</t>
-  </si>
-  <si>
-    <t>M-OCC-06</t>
-  </si>
-  <si>
-    <t>效果评估（作战复盘官）</t>
-  </si>
-  <si>
-    <t>R-OCC-007</t>
-  </si>
-  <si>
-    <t>完成单轮干预成效统计、舆论走势修正、策略迭代反馈与作业复盘，支持中短期与长期效果评估；数据来源于 DC 采集分析结果与 MC 可观测性作业数据，不自行重复采集。</t>
-  </si>
-  <si>
-    <t>M-OCC-07</t>
-  </si>
-  <si>
-    <t>舆论作业策略库（策略资产库）</t>
-  </si>
-  <si>
-    <t>R-OCC-008</t>
-  </si>
-  <si>
-    <t>搭建并迭代多语种/多场景/多风格舆论作业策略库，为作战提供可复用、可演进的策略资产。</t>
-  </si>
-  <si>
-    <t>M-OCC-08</t>
-  </si>
-  <si>
-    <t>内容主数据与排期（内容资源权威源）</t>
-  </si>
-  <si>
-    <t>R-OCC-009(资产+调度)</t>
-  </si>
-  <si>
-    <t>唯一维护内容主数据(原始素材/分类/审核状态/来源)，content_id 全局唯一引用；管理素材分类与平台适配；按素材/账号/时间制定发布排期；向各使用方主动分发 content_id。</t>
-  </si>
-  <si>
-    <t>M-OCC-09</t>
-  </si>
-  <si>
-    <t>内容审核与敏感词风控（内容合规守门人）</t>
-  </si>
-  <si>
-    <t>R-OCC-009(合规)</t>
-  </si>
-  <si>
-    <t>发布前对内容进行审核与敏感词检测；敏感词命中拦截并标记待人工复核；素材上传失败时支持断点续传。</t>
-  </si>
-  <si>
-    <t>层级</t>
-  </si>
-  <si>
-    <t>编号</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>关键能力点（功能）</t>
-  </si>
-  <si>
-    <t>来源依据</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>①子系统</t>
-  </si>
-  <si>
-    <t>数据爬取子系统</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>SRS §引言/DC</t>
-  </si>
-  <si>
-    <t>V3.3：原「数据分析与情报」(R-DC-007~010) 已移至 OCC 子系统（重编号 R-OCC-002~005），原 R-DC-011/012 情报回注与目标扩散顺延为 R-DC-007/008，DC 需求连续编号 R-DC-001~008；共 4 模块。原独立采集监控告警模块已删除——系统级监控收口至 OM（R-OM-001），DC 采集健康度指标经 II-04 上报 OM。</t>
-  </si>
-  <si>
-    <t>②模块</t>
-  </si>
-  <si>
-    <t>F-DC-01-01 采集任务池与多来源接入；F-DC-01-02 入池目标级去重；F-DC-01-03 调度队列分发；F-DC-01-04 配额限流</t>
-  </si>
-  <si>
-    <t>SRS R-DC-003</t>
-  </si>
-  <si>
-    <t>对应 R-DC-003，任务去重、调度分发与配额限流是调度大脑的三类紧耦合关注点（配额依赖资源水位、去重避免重复采），故合并为一模块；采集执行与策略自优化另列 M-DC-02。</t>
-  </si>
-  <si>
-    <t>③功能</t>
-  </si>
-  <si>
-    <t>F-DC-01-01</t>
-  </si>
-  <si>
-    <t>采集任务池与多来源接入</t>
-  </si>
-  <si>
-    <t>接收人工（REST/文件）、情报回注（F-DC-04-01，来自 OCC 分析经 II-15）等多来源注入的采集任务，统一落入任务池。</t>
-  </si>
-  <si>
-    <t>REST API 批量注入；CSV/Excel 导入；情报回注回调注入；task_pool 结构</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>F-DC-01-02</t>
-  </si>
-  <si>
-    <t>入池目标级去重</t>
-  </si>
-  <si>
-    <t>任务入池时基于 Redis 对 URL 与任务做目标级去重、调度队列与分布式锁；命中已采集目标转 recheck。</t>
-  </si>
-  <si>
-    <t>目标规范化(URL/账号/话题/时间/策略)；Redis 调度队列+分布式锁；命中转 recheck</t>
-  </si>
-  <si>
-    <t>支撑 II-15 情报回注去重</t>
-  </si>
-  <si>
-    <t>F-DC-01-03</t>
-  </si>
-  <si>
-    <t>调度队列分发</t>
-  </si>
-  <si>
-    <t>消费任务池，按优先级从调度队列批量领取任务，经 Kafka 分发到爬虫 Pod 执行。</t>
-  </si>
-  <si>
-    <t>Redis ZSet 优先级队列；Kafka 分发；分布式调度</t>
-  </si>
-  <si>
-    <t>F-DC-01-04</t>
-  </si>
-  <si>
-    <t>配额限流</t>
-  </si>
-  <si>
-    <t>对采集范围、频率、并发设配额上限；基于账号池/IP 池水位动态调节消费并发，超限自动限流。</t>
-  </si>
-  <si>
-    <t>范围/频率/并发配额上限；水位校验；动态并发调节；超限自动限流</t>
-  </si>
-  <si>
-    <t>任务队列积压时告警</t>
-  </si>
-  <si>
-    <t>F-DC-02-01 多平台采集适配；F-DC-02-02 采集手段切换与容错；F-DC-02-03 代理与维护账号应用；F-DC-02-04 代理 IP 池管理；F-DC-02-05 采集策略自优化</t>
-  </si>
-  <si>
-    <t>SRS R-DC-001,004</t>
-  </si>
-  <si>
-    <t>R-DC-001 的『采集执行』与 R-DC-003 的『调度分发』是两种关注点（执行器 vs 调度大脑），故拆出；R-DC-002 代理池管理是采集执行的网络出口（执行器直接消费代理），紧耦合故内聚进本模块；R-DC-004 策略自优化是执行器的学习闭环能力。</t>
-  </si>
-  <si>
-    <t>F-DC-02-01</t>
-  </si>
-  <si>
-    <t>多平台采集适配</t>
-  </si>
-  <si>
-    <t>R-DC-001</t>
-  </si>
-  <si>
-    <t>各平台采集适配器，按平台采用不同手段采集推荐/人物/Reels 等数据。</t>
-  </si>
-  <si>
-    <t>逆向采集(IG/TikTok/FB/X)；官方 API；模拟点击；网页解析</t>
-  </si>
-  <si>
-    <t>SRS R-DC-001</t>
-  </si>
-  <si>
-    <t>对接 EI-01</t>
-  </si>
-  <si>
-    <t>F-DC-02-02</t>
-  </si>
-  <si>
-    <t>采集手段切换与容错</t>
-  </si>
-  <si>
-    <t>逆向接口失效或改版时告警并切换备用采集方式；API 限流按限额退避重试；账号被封自动切换备用账号。</t>
-  </si>
-  <si>
-    <t>手段可切换；限流退避重试；被封自动切换备用账号</t>
-  </si>
-  <si>
-    <t>F-DC-02-03</t>
-  </si>
-  <si>
-    <t>代理与维护账号应用</t>
-  </si>
-  <si>
-    <t>采集过程使用代理 IP 与维护账号（来自 II-01），应对平台访问限制。</t>
-  </si>
-  <si>
-    <t>采集绑定代理 IP；使用维护账号；应对访问限制</t>
-  </si>
-  <si>
-    <t>F-DC-02-04</t>
-  </si>
-  <si>
-    <t>代理 IP 池管理</t>
-  </si>
-  <si>
-    <t>R-DC-002</t>
-  </si>
-  <si>
-    <t>对接 VPS 代理链路，按平台与地区分配代理 IP 并定时轮换，进行可用性检测与失效剔除；全失效时告警暂停受影响采集。</t>
-  </si>
-  <si>
-    <t>按平台/地区分配；定时轮换；可用性检测；失效剔除；全失效告警暂停</t>
-  </si>
-  <si>
-    <t>SRS R-DC-002</t>
-  </si>
-  <si>
-    <t>对接 EI-02</t>
-  </si>
-  <si>
-    <t>F-DC-02-05</t>
-  </si>
-  <si>
-    <t>采集策略自优化</t>
-  </si>
-  <si>
-    <t>R-DC-004</t>
-  </si>
-  <si>
-    <t>基于历史采集指标（封禁率/成功率/反爬升级信号/各手段有效率）对采集手段优先级、请求频率与并发、代理与账号选择策略主动调整，随平台反爬强度自适应演进；指标不足或波动过大时维持上一稳定策略并告警。</t>
-  </si>
-  <si>
-    <t>手段优先级排序；频率/并发调节；代理账号选择优化；指标不足维持稳定告警</t>
-  </si>
-  <si>
-    <t>SRS R-DC-004</t>
-  </si>
-  <si>
-    <t>主动学习闭环，区别于 F-DC-02-02 被动切换</t>
-  </si>
-  <si>
-    <t>F-DC-03-01 分布式 ETL 加工；F-DC-03-02 多模型持久化存储</t>
-  </si>
-  <si>
-    <t>SRS R-DC-005,006</t>
-  </si>
-  <si>
-    <t>对应 R-DC-005 清洗加工与 R-DC-006 多模型存储，清洗与存储是 ETL 流水线的前后两环（清洗产干净数据、存储按特征落库），紧耦合故合并。</t>
-  </si>
-  <si>
-    <t>F-DC-03-01</t>
-  </si>
-  <si>
-    <t>分布式 ETL 加工</t>
-  </si>
-  <si>
-    <t>R-DC-005</t>
-  </si>
-  <si>
-    <t>基于 Spark/MapReduce 分布式批处理完成清洗、字段提取、格式标准化、去重与关联；节点失败自动重试或转移，数据格式异常时隔离坏数据并记录。</t>
-  </si>
-  <si>
-    <t>Spark/MapReduce；清洗/提取/标准化/去重/关联；失败重试转移；坏数据隔离记录</t>
-  </si>
-  <si>
-    <t>SRS R-DC-005</t>
-  </si>
-  <si>
-    <t>对接 II-05 Kafka 总线</t>
-  </si>
-  <si>
-    <t>F-DC-03-02</t>
-  </si>
-  <si>
-    <t>多模型持久化存储</t>
-  </si>
-  <si>
-    <t>R-DC-006</t>
-  </si>
-  <si>
-    <t>将清洗后结构化数据按特征持久化：明细入 HBase 列式库、元数据/索引入关系库、关系数据入图库；写入失败时数据进入重试队列。</t>
-  </si>
-  <si>
-    <t>HBase(列式明细)；PG/MySQL(元数据索引)；图数据库(关系数据)；写入失败重试队列</t>
-  </si>
-  <si>
-    <t>SRS R-DC-006</t>
-  </si>
-  <si>
-    <t>DR-06</t>
-  </si>
-  <si>
-    <t>F-DC-04-01 情报回注采集；F-DC-04-02 目标扩散采集</t>
-  </si>
-  <si>
-    <t>SRS R-DC-007,008</t>
-  </si>
-  <si>
-    <t>对应 R-DC-007 情报回注与 R-DC-008 目标扩散，是 DC 从单向采集管道升级为情报驱动闭环的关键；回注入池经 M-DC-01 同一去重与配额约束。原「数据分析与情报」(R-DC-007~010) V3.3 起移至 OCC 子系统（重编号 R-OCC-002~005），本模块顺延为 M-DC-04。</t>
-  </si>
-  <si>
-    <t>F-DC-04-01</t>
-  </si>
-  <si>
-    <t>情报回注采集</t>
-  </si>
-  <si>
-    <t>R-DC-007</t>
-  </si>
-  <si>
-    <t>将 OCC 分析产出的高价值目标/关联实体/传播节点按规则自动或经人工确认生成定向采集任务回注任务池，经目标级去重（命中已采集转 recheck）；高扩散/批量/敏感回注经人工确认闸门；全程审计。</t>
-  </si>
-  <si>
-    <t>情报→任务自动/人工回注；目标级去重转 recheck；人工确认闸门；全程审计</t>
-  </si>
-  <si>
-    <t>SRS R-DC-007</t>
-  </si>
-  <si>
-    <t>跨子系统回注接口 II-15（OCC 分析→DC 任务池）</t>
-  </si>
-  <si>
-    <t>F-DC-04-02</t>
-  </si>
-  <si>
-    <t>目标扩散采集</t>
-  </si>
-  <si>
-    <t>R-DC-008</t>
-  </si>
-  <si>
-    <t>以已采集目标为起点按关系类型(关注/粉丝/互动/转发链/评论链)与扩散层数做 BFS 图扩展式采集，每层新节点经去重生成新任务，受配额与层数上限约束，新目标回流后可再次触发回注形成迭代扩散。</t>
-  </si>
-  <si>
-    <t>按关系+层数 BFS 扩散；新节点去重生成任务；层数/节点数/总数上限；迭代扩散回流；超限停止告警</t>
-  </si>
-  <si>
-    <t>SRS R-DC-008</t>
-  </si>
-  <si>
-    <t>受 R-DC-003 配额约束；区别于 OCC 扩散趋势预判(本期暂不实现)</t>
-  </si>
-  <si>
-    <t>多设备矩阵自动化群控子系统</t>
-  </si>
-  <si>
-    <t>SRS §引言/MC</t>
-  </si>
-  <si>
-    <t>新 SRS V3.2 将 MC 需求从 R-MC-001~008 扩展为 R-MC-001~014：执行网关(R-MC-005)与双执行模式(R-MC-006)拆为两个独立需求；账号资源管理从 1 模块拆为 3 模块（主数据 R-MC-011/分层分组 R-MC-012/绑定迁移 R-MC-013）；自动化编排(R-MC-008)与养号(R-MC-009)拆为两模块；共 14 模块。</t>
-  </si>
-  <si>
-    <t>F-MC-01-01 移动端终端接入与台账；F-MC-01-02 浏览器 Profile 创建与 CDP 接入；F-MC-01-03 终端分组与标签；F-MC-01-04 终端批量操作</t>
-  </si>
-  <si>
-    <t>SRS R-MC-001</t>
-  </si>
-  <si>
-    <t>对应 R-MC-001 执行终端接入与管理；R-MC-001 含『终端作为资源进入系统』『让终端像真人且互不关联(R-MC-002)』『终端风控分级与代理绑定(R-MC-003)』三类异构关注点，故拆 3 模块，本模块聚焦终端接入与台账。</t>
-  </si>
-  <si>
-    <t>F-MC-01-01</t>
-  </si>
-  <si>
-    <t>移动端终端接入与台账</t>
-  </si>
-  <si>
-    <t>移动端 Agent 启动后注册并建立长连接，记录设备类型(真机/云手机/ARM 板卡/虚拟化真机)、版本、型号、分组与标签，形成执行终端台账。</t>
-  </si>
-  <si>
-    <t>Agent 注册+长连接；设备类型区分虚拟/实体；台账记录</t>
-  </si>
-  <si>
-    <t>对接 II-02</t>
-  </si>
-  <si>
-    <t>F-MC-01-02</t>
-  </si>
-  <si>
-    <t>浏览器 Profile 创建与 CDP 接入</t>
-  </si>
-  <si>
-    <t>经商用指纹浏览器 API 创建浏览器 Profile（下发指纹模板、代理、分组、标签），商用产品返回 Profile 标识与调试端口；记录 Profile 标识、内核版本、调试端口、分组与标签。</t>
-  </si>
-  <si>
-    <t>调用商用 API 创建 Profile；指纹模板/代理下发；返回调试端口(CDP)；记录 Profile 台账</t>
-  </si>
-  <si>
-    <t>SRS R-MC-001；CON-12</t>
-  </si>
-  <si>
-    <t>对接 EI-06 指纹浏览器服务接口</t>
-  </si>
-  <si>
-    <t>F-MC-01-03</t>
-  </si>
-  <si>
-    <t>终端分组与标签</t>
-  </si>
-  <si>
-    <t>按业务目标、平台、地区等维度对执行终端分组与打标，支撑任务调度按分组选终端。</t>
-  </si>
-  <si>
-    <t>多维度分组；标签管理；按分组选终端</t>
-  </si>
-  <si>
-    <t>F-MC-01-04</t>
-  </si>
-  <si>
-    <t>终端批量操作</t>
-  </si>
-  <si>
-    <t>对终端集合批量操作：移动端批量安装/卸载 App、重启、截图；浏览器 Profile 批量创建/启动/关闭/截图；经对象存储临时链接上传下载。</t>
-  </si>
-  <si>
-    <t>移动端批量(安装/卸载/重启/截图)；Profile 批量(创建/启动/关闭/截图)；对象存储临时链接</t>
-  </si>
-  <si>
-    <t>对接 EI-04</t>
-  </si>
-  <si>
-    <t>F-MC-02-01 浏览器 Profile 指纹固化；F-MC-02-02 移动端设备指纹管理；F-MC-02-03 终端间环境隔离</t>
-  </si>
-  <si>
-    <t>SRS R-MC-002</t>
-  </si>
-  <si>
-    <t>对应 R-MC-002 终端身份与环境隔离；与 R-MC-001 接入台账、R-MC-003 风控分级是不同关注点；指纹固化是『让终端像真人』的核心。</t>
-  </si>
-  <si>
-    <t>F-MC-02-01</t>
-  </si>
-  <si>
-    <t>浏览器 Profile 指纹固化（经商用 API）</t>
-  </si>
-  <si>
-    <t>经商用指纹浏览器 API 配置 Profile 指纹模板（Canvas/WebGL/字体/时区/Audio/UA 等 20+ 维），由商用产品生成并固化指纹，使 Profile 长期呈现一致的设备身份；一 Profile 对应一套固化指纹与一账号身份。</t>
-  </si>
-  <si>
-    <t>20+ 维指纹模板经 API 下发；商用产品生成固化；指纹长期一致；一 Profile 一身份</t>
-  </si>
-  <si>
-    <t>SRS R-MC-002；CON-12</t>
-  </si>
-  <si>
-    <t>指纹生成与固化由商用产品负责</t>
-  </si>
-  <si>
-    <t>F-MC-02-02</t>
-  </si>
-  <si>
-    <t>移动端设备指纹管理</t>
-  </si>
-  <si>
-    <t>管理真机/云手机/ARM 板卡/虚拟化真机等移动端设备的硬件与软件指纹，支持按需配置。</t>
-  </si>
-  <si>
-    <t>移动端硬件/软件指纹管理；按需配置</t>
-  </si>
-  <si>
-    <t>F-MC-02-03</t>
-  </si>
-  <si>
-    <t>终端间环境隔离</t>
-  </si>
-  <si>
-    <t>对终端间指纹、网络、账号、Cookie/缓存相互隔离；浏览器 Profile 间 Cookie/LocalStorage/缓存独立隔离。</t>
-  </si>
-  <si>
-    <t>指纹/网络/账号/Cookie 隔离；Profile 间独立隔离</t>
-  </si>
-  <si>
-    <t>F-MC-03-01 终端状态与指标监控；F-MC-03-02 设备风控分级；F-MC-03-03 风控信号识别与规避；F-MC-03-04 代理分配与固定绑定</t>
-  </si>
-  <si>
-    <t>SRS R-MC-003</t>
-  </si>
-  <si>
-    <t>对应 R-MC-003 终端风控分级与代理绑定；风控分级、风控信号规避与代理绑定共同决定『终端能否安全承载作业』，紧耦合故合并。</t>
-  </si>
-  <si>
-    <t>F-MC-03-01</t>
-  </si>
-  <si>
-    <t>终端状态与指标监控</t>
-  </si>
-  <si>
-    <t>持续采集并监控移动端在线/离线状态、电量、CPU、内存、存储、网络，以及浏览器 Profile 运行状态与资源占用。</t>
-  </si>
-  <si>
-    <t>移动端多指标监控；Profile 运行状态监控</t>
-  </si>
-  <si>
-    <t>F-MC-03-02</t>
-  </si>
-  <si>
-    <t>设备风控分级</t>
-  </si>
-  <si>
-    <t>按指纹真实度对终端风控分级：真机与 ARM 板卡(高)、虚拟化真机(中高)、云手机与浏览器 Profile(中)；养号等敏感场景优先选用高真实度终端。</t>
-  </si>
-  <si>
-    <t>按指纹真实度分级；养号优先高真实度终端</t>
-  </si>
-  <si>
-    <t>SRS R-MC-003；CON-09</t>
-  </si>
-  <si>
-    <t>F-MC-03-03</t>
-  </si>
-  <si>
-    <t>风控信号识别与规避</t>
-  </si>
-  <si>
-    <t>识别平台风控信号并采取规避与应对策略（覆盖移动端与桌面端），风控信号持续触发时降级或暂停该终端任务。</t>
-  </si>
-  <si>
-    <t>风控信号识别；规避策略；持续触发降级/暂停</t>
-  </si>
-  <si>
-    <t>F-MC-03-04</t>
-  </si>
-  <si>
-    <t>代理分配与固定绑定</t>
-  </si>
-  <si>
-    <t>为每个执行终端/Profile 分配独立代理 IP 并固定绑定（一终端/Profile 一 IP），实现网络环境隔离；代理默认固定，仅失效时切换并重新固定。</t>
-  </si>
-  <si>
-    <t>一终端一 IP；代理固定绑定；失效时切换重新固定</t>
-  </si>
-  <si>
-    <t>F-MC-04-01 移动端 WebRTC 远控；F-MC-04-02 桌面端商用 API 画面远控；F-MC-04-03 多终端宫格监控；F-MC-04-04 剪贴板双向同步</t>
-  </si>
-  <si>
-    <t>SRS R-MC-004</t>
-  </si>
-  <si>
-    <t>对应 R-MC-004 远程控制；远控通道与任务执行通道相互分离（CON-07）。</t>
-  </si>
-  <si>
-    <t>F-MC-04-01</t>
-  </si>
-  <si>
-    <t>移动端 WebRTC 远控</t>
-  </si>
-  <si>
-    <t>移动端屏幕画面基于 WebRTC 传输，鼠标键盘事件映射为触摸/点击/滑动/输入及返回/Home/多任务键；支持截图与录屏；弱网自动降帧。</t>
-  </si>
-  <si>
-    <t>WebRTC 画面传输；事件映射；截图录屏；端到端≤300ms；弱网降帧</t>
-  </si>
-  <si>
-    <t>SRS R-MC-004；NR-P-01/05</t>
-  </si>
-  <si>
-    <t>对接 II-03</t>
-  </si>
-  <si>
-    <t>F-MC-04-02</t>
-  </si>
-  <si>
-    <t>桌面端商用 API 画面远控</t>
-  </si>
-  <si>
-    <t>桌面端指纹浏览器 Profile 经商用产品 API 获取页面/窗口画面预览流；鼠标点击与键盘输入经 CDP 注入为页面事件；远控通道与任务执行通道相互分离。</t>
-  </si>
-  <si>
-    <t>商用 API 画面预览流；CDP 注入页面事件；远控与执行通道分离</t>
-  </si>
-  <si>
-    <t>对接 EI-06</t>
-  </si>
-  <si>
-    <t>F-MC-04-03</t>
-  </si>
-  <si>
-    <t>多终端宫格监控</t>
-  </si>
-  <si>
-    <t>以低码率同屏预览多台终端，供监控人员宫格监控。</t>
-  </si>
-  <si>
-    <t>低码率宫格同屏预览</t>
-  </si>
-  <si>
-    <t>F-MC-04-04</t>
-  </si>
-  <si>
-    <t>剪贴板双向同步</t>
-  </si>
-  <si>
-    <t>剪贴板在操作端与终端间双向同步。</t>
-  </si>
-  <si>
-    <t>F-MC-05-01 动作收口与转发；F-MC-05-02 动作鉴权；F-MC-05-03 动作记录与上报；F-MC-05-04 异常熔断；F-MC-05-05 控制通道适配</t>
-  </si>
-  <si>
-    <t>SRS R-MC-005</t>
-  </si>
-  <si>
-    <t>对应 R-MC-005，是 MC 的核心枢纽；动作收口（CON-07）的落地；与 R-MC-006 双执行模式是『收口通道』与『执行引擎』两类不同职责，新 SRS 拆为两个独立需求。</t>
-  </si>
-  <si>
-    <t>F-MC-05-01</t>
-  </si>
-  <si>
-    <t>动作收口与转发</t>
-  </si>
-  <si>
-    <t>所有执行终端动作（移动端与桌面端）均经统一执行网关落地转发，禁止任何子系统或 Agent 绕过。</t>
-  </si>
-  <si>
-    <t>动作唯一收口；禁止绕过；转发落地</t>
-  </si>
-  <si>
-    <t>SRS R-MC-005；CON-07</t>
-  </si>
-  <si>
-    <t>对接 II-07</t>
-  </si>
-  <si>
-    <t>F-MC-05-02</t>
-  </si>
-  <si>
-    <t>动作鉴权</t>
-  </si>
-  <si>
-    <t>执行网关对动作鉴权，校验动作来源与目标终端的合法性。</t>
-  </si>
-  <si>
-    <t>动作来源校验；目标合法性校验</t>
-  </si>
-  <si>
-    <t>F-MC-05-03</t>
-  </si>
-  <si>
-    <t>动作记录与上报</t>
-  </si>
-  <si>
-    <t>执行网关对动作记录，写入动作日志并全量上报运维监控子系统。</t>
-  </si>
-  <si>
-    <t>动作日志写入；全量上报 OM</t>
-  </si>
-  <si>
-    <t>对接 II-11</t>
-  </si>
-  <si>
-    <t>F-MC-05-04</t>
-  </si>
-  <si>
-    <t>异常熔断</t>
-  </si>
-  <si>
-    <t>执行网关对异常动作熔断，在检测到风控信号或异常频率时停止后续动作；网关过载时按优先级限流。</t>
-  </si>
-  <si>
-    <t>风控信号/异常频率熔断；过载优先级限流</t>
-  </si>
-  <si>
-    <t>F-MC-05-05</t>
-  </si>
-  <si>
-    <t>控制通道适配</t>
-  </si>
-  <si>
-    <t>移动端终端采用 ADB、无障碍服务通道，桌面端 Profile 采用 CDP 通道；控制通道对上层透明。</t>
-  </si>
-  <si>
-    <t>移动端 ADB/无障碍；桌面端 CDP；对上层透明</t>
-  </si>
-  <si>
-    <t>F-MC-06-01 脚本模式执行引擎；F-MC-06-02 智能体模式执行引擎；F-MC-06-03 三类执行目标</t>
-  </si>
-  <si>
-    <t>SRS R-MC-006</t>
-  </si>
-  <si>
-    <t>对应 R-MC-006；脚本模式与智能体模式是两种决策驱动的执行引擎，动作落地均经 R-MC-005 网关；推理执行分离（CON-10）。</t>
-  </si>
-  <si>
-    <t>F-MC-06-01</t>
-  </si>
-  <si>
-    <t>脚本模式执行引擎</t>
-  </si>
-  <si>
-    <t>由预先编写的固定流程驱动终端动作，适用于流程确定、高频、批量作业。</t>
-  </si>
-  <si>
-    <t>固定流程驱动；适配移动端与桌面端</t>
-  </si>
-  <si>
-    <t>SRS R-MC-006；CON-08</t>
-  </si>
-  <si>
-    <t>F-MC-06-02</t>
-  </si>
-  <si>
-    <t>智能体模式执行引擎</t>
-  </si>
-  <si>
-    <t>由终端 Agent 调用 IRS 本地大模型进行视觉推理与规划自主决策动作；推理不经网关，产出的动作指令再经网关落地。</t>
-  </si>
-  <si>
-    <t>大模型视觉推理决策；推理不经网关；动作经网关落地</t>
-  </si>
-  <si>
-    <t>SRS R-MC-006；CON-10</t>
-  </si>
-  <si>
-    <t>对接 EI-05/II-08</t>
-  </si>
-  <si>
-    <t>F-MC-06-03</t>
-  </si>
-  <si>
-    <t>三类执行目标</t>
-  </si>
-  <si>
-    <t>支撑群控(多台终端同步控制统一投放)、养号(认知作战账号经 ADB/无障碍、爬虫账号经 CDP，拟人化节奏由 R-MC-009 内置)、内容投放(下发发布素材到目标账号)三类执行目标。</t>
-  </si>
-  <si>
-    <t>群控；养号(移动端 ADB/桌面端 CDP)；内容投放</t>
-  </si>
-  <si>
-    <t>养号节奏见 R-MC-009</t>
-  </si>
-  <si>
-    <t>F-MC-07-01 任务创建与实例化；F-MC-07-02 多任务类型；F-MC-07-03 任务状态机流转；F-MC-07-04 失败重试与超时配置；F-MC-07-05 计划任务与定时调度</t>
-  </si>
-  <si>
-    <t>SRS R-MC-007</t>
-  </si>
-  <si>
-    <t>对应 R-MC-007 任务管理。</t>
-  </si>
-  <si>
-    <t>F-MC-07-01</t>
-  </si>
-  <si>
-    <t>任务创建与实例化</t>
-  </si>
-  <si>
-    <t>按任务定义选择设备或设备组，生成任务实例并入消息队列，由调度器分发到设备 Agent 执行。</t>
-  </si>
-  <si>
-    <t>任务定义→实例化→入队→分发</t>
-  </si>
-  <si>
-    <t>F-MC-07-02</t>
-  </si>
-  <si>
-    <t>多任务类型</t>
-  </si>
-  <si>
-    <t>支持 App 安装启动、文件分发、内容发布、截图、数据采集、自动化脚本、设备巡检、账号状态检查等任务类型。</t>
-  </si>
-  <si>
-    <t>八类任务类型</t>
-  </si>
-  <si>
-    <t>F-MC-07-03</t>
-  </si>
-  <si>
-    <t>任务状态机流转</t>
-  </si>
-  <si>
-    <t>任务在待执行/排队中/执行中/成功/失败/已取消/超时/部分成功等状态间流转。</t>
-  </si>
-  <si>
-    <t>八态状态机流转</t>
-  </si>
-  <si>
-    <t>F-MC-07-04</t>
-  </si>
-  <si>
-    <t>失败重试与超时配置</t>
-  </si>
-  <si>
-    <t>支持失败重试、重试次数与超时配置；队列积压时按优先级调度并告警。</t>
-  </si>
-  <si>
-    <t>失败重试；重试次数/超时可配；优先级调度</t>
-  </si>
-  <si>
-    <t>任务入队到分发≤2s NR-P-04</t>
-  </si>
-  <si>
-    <t>F-MC-07-05</t>
-  </si>
-  <si>
-    <t>计划任务与定时调度</t>
-  </si>
-  <si>
-    <t>支持一次性、每日、每周与自定义 Cron 计划任务，支持最大并发数与任务优先级控制。</t>
-  </si>
-  <si>
-    <t>Cron 定时(一次性/每日/每周/自定义)；最大并发；优先级</t>
-  </si>
-  <si>
-    <t>F-MC-08-01 模板化任务（第一阶段）；F-MC-08-02 可视化工作流编排（第二阶段）；F-MC-08-03 脚本开发与调试（第三阶段）；F-MC-08-04 模拟点击自动化</t>
-  </si>
-  <si>
-    <t>SRS R-MC-008</t>
-  </si>
-  <si>
-    <t>对应 R-MC-008 自动化编排能力；与 R-MC-009 账号操作编排与养号是『通用编排能力』与『账号域编排』两类，新 SRS 拆为两个需求。</t>
-  </si>
-  <si>
-    <t>F-MC-08-01</t>
-  </si>
-  <si>
-    <t>模板化任务（第一阶段）</t>
-  </si>
-  <si>
-    <t>提供打开 App/等待页面/点击/输入/上传文件/截图/返回/滑动/关闭 App/设备巡检/App 状态检测等模板化任务。</t>
-  </si>
-  <si>
-    <t>十二类模板化任务</t>
-  </si>
-  <si>
-    <t>F-MC-08-02</t>
-  </si>
-  <si>
-    <t>可视化工作流编排（第二阶段）</t>
-  </si>
-  <si>
-    <t>节点包括开始/设备选择/启动 App/等待/点击/输入/滑动/截图/文件上传/条件判断/循环/HTTP 请求/日志/审批/结束等，可视化编排。</t>
-  </si>
-  <si>
-    <t>十五类节点；可视化编排</t>
-  </si>
-  <si>
-    <t>F-MC-08-03</t>
-  </si>
-  <si>
-    <t>脚本开发与调试（第三阶段）</t>
-  </si>
-  <si>
-    <t>支持脚本编辑、调试设备、执行日志、截图回放与版本管理；脚本运行于沙箱并配置权限白名单。</t>
-  </si>
-  <si>
-    <t>脚本编辑/调试/回放/版本管理；沙箱+权限白名单</t>
-  </si>
-  <si>
-    <t>SRS R-MC-008；NR-S-05</t>
-  </si>
-  <si>
-    <t>F-MC-08-04</t>
-  </si>
-  <si>
-    <t>模拟点击自动化</t>
-  </si>
-  <si>
-    <t>针对 TikTok/Facebook 等平台实现模拟点击自动化。</t>
-  </si>
-  <si>
-    <t>目标平台模拟点击</t>
-  </si>
-  <si>
-    <t>F-MC-09-01 养号自动化与拟人化节奏；F-MC-09-02 账号-终端-代理绑定自动化；F-MC-09-03 终端侧登录状态维护；F-MC-09-04 状态变更联动</t>
-  </si>
-  <si>
-    <t>SRS R-MC-009</t>
-  </si>
-  <si>
-    <t>对应 R-MC-009；账号操作依赖 R-MC-008 编排产出动作，但养号拟人化节奏是账号域专属策略，新 SRS 拆为独立需求；动作均经 R-MC-005 网关落地。</t>
-  </si>
-  <si>
-    <t>F-MC-09-01</t>
-  </si>
-  <si>
-    <t>养号自动化与拟人化节奏</t>
-  </si>
-  <si>
-    <t>养号动作(发帖/关注/浏览)由本功能编排并经执行网关落地（认知作战账号经 ADB/无障碍、爬虫账号经 CDP）；拟人化节奏由本功能内置（注入随机浏览/停留/互动、打散时间间隔与频率），不依赖蜂群智能体。</t>
-  </si>
-  <si>
-    <t>养号经网关落地；拟人化节奏内置；认知作战账号 ADB/爬虫账号 CDP</t>
-  </si>
-  <si>
-    <t>F-MC-09-02</t>
-  </si>
-  <si>
-    <t>账号-终端-代理绑定自动化</t>
-  </si>
-  <si>
-    <t>按差异化绑定规则绑定：真机/云手机/虚拟化真机「一设备一账号一 IP」(未解绑前不可再绑)；指纹浏览器 Profile「一 Profile 一账号一 IP」(实例可多开)；联动代理绑定记录。</t>
-  </si>
-  <si>
-    <t>一设备一账号一 IP；一 Profile 一账号一 IP；未解绑不可再绑；联动代理绑定</t>
-  </si>
-  <si>
-    <t>SRS R-MC-009；CON-13</t>
-  </si>
-  <si>
-    <t>F-MC-09-03</t>
-  </si>
-  <si>
-    <t>终端侧登录状态维护</t>
-  </si>
-  <si>
-    <t>记录账号在终端上的登录状态及其变化。</t>
-  </si>
-  <si>
-    <t>登录状态记录与变化</t>
-  </si>
-  <si>
-    <t>F-MC-09-04</t>
-  </si>
-  <si>
-    <t>状态变更联动</t>
-  </si>
-  <si>
-    <t>账号状态变更(封禁/受限)时停止养号任务并解绑。</t>
-  </si>
-  <si>
-    <t>状态变更停止任务解绑</t>
-  </si>
-  <si>
-    <t>F-MC-10-01 动作留痕；F-MC-10-02 任务日志与截图回传；F-MC-10-03 异常告警；F-MC-10-04 审计日志；F-MC-10-05 任务完成率统计；F-MC-10-06 内容触达与互动统计；F-MC-10-07 账号健康度统计；F-MC-10-08 任务复盘归因；F-MC-10-09 效果回调回传上游</t>
-  </si>
-  <si>
-    <t>SRS R-MC-010</t>
-  </si>
-  <si>
-    <t>对应 R-MC-010，动作留痕与作业统计同源，避免重复采集原始动作数据；多维统计按任务/内容效果/账号健康三维度拆功能。</t>
-  </si>
-  <si>
-    <t>F-MC-10-01</t>
-  </si>
-  <si>
-    <t>动作留痕</t>
-  </si>
-  <si>
-    <t>每一个终端动作(点击/输入/安装/发布等)均留痕，记录时间、终端、账号与结果。</t>
-  </si>
-  <si>
-    <t>动作留痕；记录时间/终端/账号/结果</t>
-  </si>
-  <si>
-    <t>F-MC-10-02</t>
-  </si>
-  <si>
-    <t>任务日志与截图回传</t>
-  </si>
-  <si>
-    <t>Agent 回传任务执行日志与关键步骤截图。</t>
-  </si>
-  <si>
-    <t>任务日志回传；关键步骤截图</t>
-  </si>
-  <si>
-    <t>F-MC-10-03</t>
-  </si>
-  <si>
-    <t>异常告警</t>
-  </si>
-  <si>
-    <t>任务失败、终端掉线、账号异常等异常事件触发告警通知。</t>
-  </si>
-  <si>
-    <t>异常事件告警通知</t>
-  </si>
-  <si>
-    <t>F-MC-10-04</t>
-  </si>
-  <si>
-    <t>审计日志</t>
-  </si>
-  <si>
-    <t>对用户与系统操作记录审计日志，记录谁在何时对哪台终端或账号做了什么。</t>
-  </si>
-  <si>
-    <t>操作审计；可追溯</t>
-  </si>
-  <si>
-    <t>SRS R-MC-010；NR-S-06</t>
-  </si>
-  <si>
-    <t>F-MC-10-05</t>
-  </si>
-  <si>
-    <t>任务完成率统计</t>
-  </si>
-  <si>
-    <t>基于动作日志与任务日志统计蜂群作业的任务完成率、成功率、失败率、平均耗时等任务维度指标。</t>
-  </si>
-  <si>
-    <t>任务完成率/成功率/失败率/平均耗时；基于动作日志与任务日志</t>
-  </si>
-  <si>
-    <t>F-MC-10-06</t>
-  </si>
-  <si>
-    <t>内容触达与互动统计</t>
-  </si>
-  <si>
-    <t>统计内容投放的触达量、曝光、互动（点赞/评论/转发）等内容效果维度指标。</t>
-  </si>
-  <si>
-    <t>触达量/曝光/互动(点赞/评论/转发)；内容效果维度</t>
-  </si>
-  <si>
-    <t>F-MC-10-07</t>
-  </si>
-  <si>
-    <t>账号健康度统计</t>
-  </si>
-  <si>
-    <t>统计智能体账号的健康度指标（活跃度、风控触发频次、封禁率、作业稳定性等）。</t>
-  </si>
-  <si>
-    <t>活跃度/风控触发频次/封禁率/作业稳定性；账号健康度维度</t>
-  </si>
-  <si>
-    <t>F-MC-10-08</t>
-  </si>
-  <si>
-    <t>任务复盘归因</t>
-  </si>
-  <si>
-    <t>对失败任务、异常账号、低效作业进行归因分析。</t>
-  </si>
-  <si>
-    <t>归因分析复盘</t>
-  </si>
-  <si>
-    <t>F-MC-10-09</t>
-  </si>
-  <si>
-    <t>效果回调回传上游</t>
-  </si>
-  <si>
-    <t>将投送效果数据通过回调机制联动回传至 OCC，供效果评估闭环使用。</t>
-  </si>
-  <si>
-    <t>效果数据回调回传 OCC</t>
-  </si>
-  <si>
-    <t>对接 II-10</t>
-  </si>
-  <si>
-    <t>F-MC-11-01 账号主数据维护；F-MC-11-02 注册方式与流程编排；F-MC-11-03 注册结果判定与状态落地；F-MC-11-04 账号验证与风险识别；F-MC-11-05 账号生命周期状态机；F-MC-11-06 账号状态变更事件广播</t>
-  </si>
-  <si>
-    <t>SRS R-MC-011</t>
-  </si>
-  <si>
-    <t>对应 R-MC-011；账号实体主数据 CRUD 与智能体账号组织(R-MC-012 分层分组、R-MC-013 绑定迁移)是不同关注点，新 SRS 拆为三个需求，本模块聚焦主数据维护。</t>
-  </si>
-  <si>
-    <t>F-MC-11-01</t>
-  </si>
-  <si>
-    <t>账号主数据维护</t>
-  </si>
-  <si>
-    <t>唯一维护账号主数据(凭据/平台/全局状态/生命周期/风险评估/账号分类)，凭据加密存储；其它子系统仅引用 account_id 不复制主数据。</t>
-  </si>
-  <si>
-    <t>主数据唯一维护；凭据加密不落明文；使用方仅引用 account_id</t>
-  </si>
-  <si>
-    <t>SRS R-MC-011；NR-S-03</t>
-  </si>
-  <si>
-    <t>权威源；对接 II-01</t>
-  </si>
-  <si>
-    <t>F-MC-11-02</t>
-  </si>
-  <si>
-    <t>注册方式与流程编排</t>
-  </si>
-  <si>
-    <t>承担注册入口，支持邮箱/手机接码/虚拟号注册方式路由；编排注册流程（填写注册信息、接收验证码、完成登录探测），注册动作经统一执行网关执行（爬虫账号 CDP/认知作战账号 ADB）。</t>
-  </si>
-  <si>
-    <t>邮箱/接码/虚拟号注册方式路由；注册流程编排；注册动作经执行网关</t>
-  </si>
-  <si>
-    <t>对接 EI-03</t>
-  </si>
-  <si>
-    <t>F-MC-11-03</t>
-  </si>
-  <si>
-    <t>注册结果判定与状态落地</t>
-  </si>
-  <si>
-    <t>接收执行网关回传的注册执行结果，判定账号状态与风险等级，落地账号主数据（凭据加密存储），生成 account_id。</t>
-  </si>
-  <si>
-    <t>注册结果判定；状态与风险等级落地；凭据加密存储；生成 account_id</t>
-  </si>
-  <si>
-    <t>F-MC-11-04</t>
-  </si>
-  <si>
-    <t>账号验证与风险识别</t>
-  </si>
-  <si>
-    <t>通过登录探测与状态识别检测可用性，识别封禁/限制/需验证等风险点，输出风险等级。</t>
-  </si>
-  <si>
-    <t>登录探测；状态识别；风险等级输出</t>
-  </si>
-  <si>
-    <t>F-MC-11-05</t>
-  </si>
-  <si>
-    <t>账号生命周期状态机</t>
-  </si>
-  <si>
-    <t>账号在待登录/正常/受限/需验证/封禁/归档等状态间流转，由本子系统判定与维护。</t>
-  </si>
-  <si>
-    <t>六态生命周期状态机</t>
-  </si>
-  <si>
-    <t>F-MC-11-06</t>
-  </si>
-  <si>
-    <t>账号状态变更事件广播</t>
-  </si>
-  <si>
-    <t>账号状态变更(封禁/受限等)经事件总线广播 account.status.changed 事件，使用方订阅后立即响应，保证被封账号全网即时失效。</t>
-  </si>
-  <si>
-    <t>account.status.changed 事件广播；使用方订阅即时响应</t>
-  </si>
-  <si>
-    <t>对接 II-01a</t>
-  </si>
-  <si>
-    <t>F-MC-12-01 智能体账号分层分组；F-MC-12-02 智能体账号作业生命周期</t>
-  </si>
-  <si>
-    <t>SRS R-MC-012</t>
-  </si>
-  <si>
-    <t>对应 R-MC-012；账号组织（分层分组+作业生命周期）与账号主数据 CRUD 是不同关注点，新 SRS 拆为独立需求。</t>
-  </si>
-  <si>
-    <t>F-MC-12-01</t>
-  </si>
-  <si>
-    <t>智能体账号分层分组</t>
-  </si>
-  <si>
-    <t>对智能体账号按业务目标/平台/地区/风险等级等维度分层分组，形成可控账号层级结构。</t>
-  </si>
-  <si>
-    <t>多维度分层分组</t>
-  </si>
-  <si>
-    <t>F-MC-12-02</t>
-  </si>
-  <si>
-    <t>智能体账号作业生命周期</t>
-  </si>
-  <si>
-    <t>管理智能体账号作业生命周期(待激活/活跃/休眠/受限/封禁/回收)，支持自动与人工流转。</t>
-  </si>
-  <si>
-    <t>六态作业生命周期；自动与人工流转</t>
-  </si>
-  <si>
-    <t>F-MC-13-01 智能体-账号绑定维护；F-MC-13-02 四元绑定关系维护；F-MC-13-03 迁移资产抽取；F-MC-13-04 迁移目标账号校验；F-MC-13-05 继承写入与绑定切换</t>
-  </si>
-  <si>
-    <t>SRS R-MC-013</t>
-  </si>
-  <si>
-    <t>对应 R-MC-013；绑定关系维护与封号资产迁移是账号资源的『关联治理』关注点，与主数据 CRUD、分层分组分离，新 SRS 拆为独立需求。</t>
-  </si>
-  <si>
-    <t>F-MC-13-01</t>
-  </si>
-  <si>
-    <t>智能体-账号绑定维护</t>
-  </si>
-  <si>
-    <t>记录并维护 agent_id↔account_id 严格 1:1 绑定关系；agent_id 由 SWM 分配经 II-14 同步至本子系统持存。</t>
-  </si>
-  <si>
-    <t>agent_id↔account_id 严格 1:1；记录维护</t>
-  </si>
-  <si>
-    <t>对接 II-14</t>
-  </si>
-  <si>
-    <t>F-MC-13-02</t>
-  </si>
-  <si>
-    <t>四元绑定关系维护</t>
-  </si>
-  <si>
-    <t>记录并维护 agent_id↔account_id↔终端↔代理 IP 四元绑定关系，形成 1:1:1:1 作战单元。</t>
-  </si>
-  <si>
-    <t>四元绑定；1:1:1:1 作战单元</t>
-  </si>
-  <si>
-    <t>F-MC-13-03</t>
-  </si>
-  <si>
-    <t>迁移资产抽取</t>
-  </si>
-  <si>
-    <t>从被封禁账号绑定的原 agent_id 智能体定义中抽取待迁移资产：人设标签、提示词版本、记忆数据。</t>
-  </si>
-  <si>
-    <t>抽取人设标签/提示词版本/记忆数据；资产完整性校验</t>
-  </si>
-  <si>
-    <t>F-MC-13-04</t>
-  </si>
-  <si>
-    <t>迁移目标账号校验</t>
-  </si>
-  <si>
-    <t>校验目标账号（新注册且未绑定 agent_id）是否满足迁移条件：未绑定、状态正常、满足账号-终端绑定规则；不满足则拒绝并提示。</t>
-  </si>
-  <si>
-    <t>目标账号未绑定校验；账号状态正常校验；终端绑定规则校验；不满足拒绝提示</t>
-  </si>
-  <si>
-    <t>F-MC-13-05</t>
-  </si>
-  <si>
-    <t>继承写入与绑定切换</t>
-  </si>
-  <si>
-    <t>将抽取的资产整体继承写入目标账号的新 agent_id，激活新绑定；旧 agent_id↔旧账号解绑并休眠，保证人格连贯性。</t>
-  </si>
-  <si>
-    <t>资产整体继承写入新 agent_id；新绑定激活；旧绑定解绑休眠；人格连贯</t>
-  </si>
-  <si>
-    <t>F-MC-14-01 智能体定义接收与持存；F-MC-14-02 人设一致性校验；F-MC-14-03 智能体定义调用执行；F-MC-14-04 智能体定义更新生效；F-MC-14-05 OCC 编排智能体节点来源</t>
-  </si>
-  <si>
-    <t>SRS R-MC-014</t>
-  </si>
-  <si>
-    <t>对应 R-MC-014，智能体执行宿主职责；确立 SWM 为定义与记忆中心、MC 为执行宿主的分工。</t>
-  </si>
-  <si>
-    <t>F-MC-14-01</t>
-  </si>
-  <si>
-    <t>智能体定义接收与持存</t>
-  </si>
-  <si>
-    <t>以 agent_id 为主键接收 SWM 同步的智能体定义(人设标签/提示词/记忆/作业策略)并持存，作为任务执行调用依据。</t>
-  </si>
-  <si>
-    <t>agent_id 主键接收持存</t>
-  </si>
-  <si>
-    <t>F-MC-14-02</t>
-  </si>
-  <si>
-    <t>人设一致性校验</t>
-  </si>
-  <si>
-    <t>智能体模式下任务执行前校验「当前 account_id 绑定的人设标签」与「agent_id 定义中的人设标签」是否一致，一致方可调用并经网关落地，不一致拒绝执行并告警。</t>
-  </si>
-  <si>
-    <t>执行前人设一致性校验；不一致拒绝并告警</t>
-  </si>
-  <si>
-    <t>F-MC-14-03</t>
-  </si>
-  <si>
-    <t>智能体定义调用执行</t>
-  </si>
-  <si>
-    <t>任务执行时按智能体定义中的提示词/记忆/作业策略调用 IRS 本地大模型视觉推理，产出动作指令再经执行网关落地。</t>
-  </si>
-  <si>
-    <t>按定义调用 IRS 推理；动作经网关落地</t>
-  </si>
-  <si>
-    <t>F-MC-14-04</t>
-  </si>
-  <si>
-    <t>智能体定义更新生效</t>
-  </si>
-  <si>
-    <t>智能体定义更新时(SWM 以同一 agent_id 重新同步)更新持存版本，保证执行使用最新定义。</t>
-  </si>
-  <si>
-    <t>更新持存版本；使用最新定义</t>
-  </si>
-  <si>
-    <t>F-MC-14-05</t>
-  </si>
-  <si>
-    <t>OCC 编排智能体节点来源</t>
-  </si>
-  <si>
-    <t>作为 OCC 作战编排的执行节点来源——编排中智能体节点以 agent_id 引用本子系统持存的智能体。</t>
-  </si>
-  <si>
-    <t>以 agent_id 供 OCC 编排引用</t>
-  </si>
-  <si>
-    <t>运维监控子系统</t>
-  </si>
-  <si>
-    <t>SRS §引言/OM</t>
-  </si>
-  <si>
-    <t>R-OM-001(日志与指标汇聚)含日志、指标两种异构数据管道，拆 2 模块；R-OM-002(告警与运维)含告警引擎、可视化看板、运维作业三类关注点，看板与作业合并故拆 2 模块。</t>
-  </si>
-  <si>
-    <t>F-OM-01-01 日志采集与汇聚；F-OM-01-02 全文检索</t>
-  </si>
-  <si>
-    <t>SRS R-OM-001(日志)</t>
-  </si>
-  <si>
-    <t>R-OM-001 的日志(半结构化文本/全文检索/日志库)与指标(时序数值/时序 DB)是两种异构数据管道，故拆。</t>
-  </si>
-  <si>
-    <t>F-OM-01-01</t>
-  </si>
-  <si>
-    <t>日志采集与汇聚</t>
-  </si>
-  <si>
-    <t>R-OM-001</t>
-  </si>
-  <si>
-    <t>通过日志采集 Agent 将各子系统日志汇聚至统一日志库。</t>
-  </si>
-  <si>
-    <t>日志采集 Agent；统一日志库汇聚</t>
-  </si>
-  <si>
-    <t>SRS R-OM-001</t>
-  </si>
-  <si>
-    <t>对接 II-04/II-11</t>
-  </si>
-  <si>
-    <t>F-OM-01-02</t>
-  </si>
-  <si>
-    <t>全文检索</t>
-  </si>
-  <si>
-    <t>支持对统一日志库的全文检索；近 7 日日志检索响应≤3 秒。</t>
-  </si>
-  <si>
-    <t>全文检索；检索≤3 秒</t>
-  </si>
-  <si>
-    <t>SRS R-OM-001；NR-P-06</t>
-  </si>
-  <si>
-    <t>F-OM-02-01 指标采集；F-OM-02-02 时序数据存储</t>
-  </si>
-  <si>
-    <t>SRS R-OM-001(指标)</t>
-  </si>
-  <si>
-    <t>R-OM-001 的指标采集与时序存储是独立于日志的关注点。</t>
-  </si>
-  <si>
-    <t>F-OM-02-01</t>
-  </si>
-  <si>
-    <t>指标采集</t>
-  </si>
-  <si>
-    <t>通过指标采集器采集设备在线率/任务成功率/爬虫吞吐量/队列积压等系统运行指标。</t>
-  </si>
-  <si>
-    <t>多维指标采集器</t>
-  </si>
-  <si>
-    <t>F-OM-02-02</t>
-  </si>
-  <si>
-    <t>时序数据存储</t>
-  </si>
-  <si>
-    <t>将采集的指标形成时序数据存储，供告警与看板消费。</t>
-  </si>
-  <si>
-    <t>时序数据库存储</t>
-  </si>
-  <si>
-    <t>F-OM-03-01 阈值与异常检测告警；F-OM-03-02 告警风暴聚合去重</t>
-  </si>
-  <si>
-    <t>SRS R-OM-002(告警)</t>
-  </si>
-  <si>
-    <t>R-OM-002 的告警引擎(监测→告警)与可视化/运维作业是不同职责域，故拆。</t>
-  </si>
-  <si>
-    <t>F-OM-03-01</t>
-  </si>
-  <si>
-    <t>阈值与异常检测告警</t>
-  </si>
-  <si>
-    <t>R-OM-002</t>
-  </si>
-  <si>
-    <t>支持阈值告警与异常检测告警，通过多渠道通知。</t>
-  </si>
-  <si>
-    <t>阈值/异常检测告警；多渠道通知</t>
-  </si>
-  <si>
-    <t>SRS R-OM-002</t>
-  </si>
-  <si>
-    <t>F-OM-03-02</t>
-  </si>
-  <si>
-    <t>告警风暴聚合去重</t>
-  </si>
-  <si>
-    <t>告警风暴时按规则聚合去重，避免告警轰炸；通知渠道失效时降级为备用渠道。</t>
-  </si>
-  <si>
-    <t>告警聚合去重；备用渠道降级</t>
-  </si>
-  <si>
-    <t>F-OM-04-01 可视化看板；F-OM-04-02 常态化运维操作</t>
-  </si>
-  <si>
-    <t>SRS R-OM-002(看板+运维)</t>
-  </si>
-  <si>
-    <t>R-OM-002 的可视化看板与运维作业均面向人工作业，紧耦合故合并。</t>
-  </si>
-  <si>
-    <t>F-OM-04-01</t>
-  </si>
-  <si>
-    <t>可视化看板</t>
-  </si>
-  <si>
-    <t>提供总览/设备/任务/爬虫/异常等多维可视化看板；数据加载超时时降级展示缓存。</t>
-  </si>
-  <si>
-    <t>多维可视化看板；缓存降级展示</t>
-  </si>
-  <si>
-    <t>F-OM-04-02</t>
-  </si>
-  <si>
-    <t>常态化运维操作</t>
-  </si>
-  <si>
-    <t>支持日志查询、故障定位、巡检与容量观测等常态化运维操作。</t>
-  </si>
-  <si>
-    <t>日志查询/故障定位/巡检/容量观测</t>
-  </si>
-  <si>
-    <t>公共功能</t>
-  </si>
-  <si>
-    <t>SRS §引言/COM</t>
-  </si>
-  <si>
-    <t>R-COM-001 含认证(AuthN，你是谁)与授权(AuthZ+数据隔离，你能访问什么)两个 IAM 经典异构问题，故拆 2 模块。</t>
-  </si>
-  <si>
-    <t>F-COM-01-01 登录认证；F-COM-01-02 双因素认证；F-COM-01-03 认证令牌签发</t>
-  </si>
-  <si>
-    <t>SRS R-COM-001(AuthN)</t>
-  </si>
-  <si>
-    <t>R-COM-001 的认证(身份验证)与授权(权限决策)是两个经典不同问题，故拆。</t>
-  </si>
-  <si>
-    <t>F-COM-01-01</t>
-  </si>
-  <si>
-    <t>登录认证</t>
-  </si>
-  <si>
-    <t>进行登录认证；登录密码错误超限时锁定账号。</t>
-  </si>
-  <si>
-    <t>登录认证；超限锁定</t>
-  </si>
-  <si>
-    <t>SRS R-COM-001；NR-S-01</t>
-  </si>
-  <si>
-    <t>F-COM-01-02</t>
-  </si>
-  <si>
-    <t>双因素认证</t>
-  </si>
-  <si>
-    <t>支持双因素认证；双因素验证失败时拒绝并记录。</t>
-  </si>
-  <si>
-    <t>双因素认证；失败拒绝记录</t>
-  </si>
-  <si>
-    <t>SRS R-COM-001</t>
-  </si>
-  <si>
-    <t>F-COM-01-03</t>
-  </si>
-  <si>
-    <t>认证令牌签发</t>
-  </si>
-  <si>
-    <t>认证通过后签发认证令牌，供各子系统统一鉴权。</t>
-  </si>
-  <si>
-    <t>令牌签发；统一鉴权</t>
-  </si>
-  <si>
-    <t>F-COM-02-01 RBAC 权限决策；F-COM-02-02 组织与成员管理；F-COM-02-03 多组织数据隔离</t>
-  </si>
-  <si>
-    <t>SRS R-COM-001(AuthZ)</t>
-  </si>
-  <si>
-    <t>授权(RBAC 决策)与组织数据隔离都决定『数据可见边界』，紧耦合故合并。</t>
-  </si>
-  <si>
-    <t>F-COM-02-01</t>
-  </si>
-  <si>
-    <t>RBAC 权限决策</t>
-  </si>
-  <si>
-    <t>基于角色访问控制进行权限决策，角色含超级管理员/运营主管/运营人员/脚本开发者/审核人员/只读观察员等；越权访问拦截并审计。</t>
-  </si>
-  <si>
-    <t>RBAC 决策；多角色；越权拦截审计</t>
-  </si>
-  <si>
-    <t>F-COM-02-02</t>
-  </si>
-  <si>
-    <t>组织与成员管理</t>
-  </si>
-  <si>
-    <t>管理组织结构与成员信息。</t>
-  </si>
-  <si>
-    <t>组织结构管理；成员管理</t>
-  </si>
-  <si>
-    <t>F-COM-02-03</t>
-  </si>
-  <si>
-    <t>多组织数据隔离</t>
-  </si>
-  <si>
-    <t>对多组织或多租户进行数据隔离，禁止跨组织访问。</t>
-  </si>
-  <si>
-    <t>多组织/多租户隔离；禁止跨组织访问</t>
-  </si>
-  <si>
-    <t>SRS R-COM-001；NR-C-01/02</t>
-  </si>
-  <si>
-    <t>蜂群智能体子系统</t>
-  </si>
-  <si>
-    <t>SRS §引言/SWM</t>
-  </si>
-  <si>
-    <t>R-SWM-001(提示词与人设管理)含人设标签、提示词模板库、场景适配调用三个异构关注点(元数据/文本资产/运行时决策)，故拆 3 模块；智能体定义组装与同步下发归构建模块(M-SWM-05)，迭代优化决策归评测模块(M-SWM-06)。</t>
-  </si>
-  <si>
-    <t>F-SWM-01-01 人设标签绑定；F-SWM-01-02 人设标签体系维护</t>
-  </si>
-  <si>
-    <t>SRS R-SWM-001(人设)</t>
-  </si>
-  <si>
-    <t>R-SWM-001 的人设标签(元数据体系)与提示词(文本资产)、运行时选择是不同职责域，故拆。</t>
-  </si>
-  <si>
-    <t>F-SWM-01-01</t>
-  </si>
-  <si>
-    <t>人设标签绑定</t>
-  </si>
-  <si>
-    <t>R-SWM-001</t>
-  </si>
-  <si>
-    <t>为每个 agent_id 绑定人设标签，标签涵盖身份特征、立场倾向、语言风格、兴趣领域等画像属性。</t>
-  </si>
-  <si>
-    <t>人设绑 agent_id；画像属性涵盖</t>
-  </si>
-  <si>
-    <t>SRS R-SWM-001</t>
-  </si>
-  <si>
-    <t>F-SWM-01-02</t>
-  </si>
-  <si>
-    <t>人设标签体系维护</t>
-  </si>
-  <si>
-    <t>维护人设标签体系定义；人设标签冲突时提示人工裁定。</t>
-  </si>
-  <si>
-    <t>标签体系维护；冲突人工裁定</t>
-  </si>
-  <si>
-    <t>F-SWM-02-01 提示词模板库分类管理；F-SWM-02-02 提示词版本管理；F-SWM-02-03 Playground 试运行调试；F-SWM-02-04 版本输出对比</t>
-  </si>
-  <si>
-    <t>SRS R-SWM-001(资产)</t>
-  </si>
-  <si>
-    <t>R-SWM-001 的提示词模板库(文本资产)是独立关注点；版本管理横切于人设与提示词。</t>
-  </si>
-  <si>
-    <t>F-SWM-02-01</t>
-  </si>
-  <si>
-    <t>提示词模板库分类管理</t>
-  </si>
-  <si>
-    <t>建立提示词模板库并按用途、平台、目标进行分类管理。</t>
-  </si>
-  <si>
-    <t>模板库；按用途/平台/目标分类</t>
-  </si>
-  <si>
-    <t>F-SWM-02-02</t>
-  </si>
-  <si>
-    <t>提示词版本管理</t>
-  </si>
-  <si>
-    <t>对提示词进行版本管理，以 agent_id 为主键索引，支持版本对比、回滚与变更记录；版本回滚失败时告警。</t>
-  </si>
-  <si>
-    <t>agent_id 主键版本管理；对比/回滚/变更记录</t>
-  </si>
-  <si>
-    <t>F-SWM-02-03</t>
-  </si>
-  <si>
-    <t>Playground 试运行调试</t>
-  </si>
-  <si>
-    <t>提供 Playground 试运行环境，对提示词进行调试与效果验证。</t>
-  </si>
-  <si>
-    <t>Playground 试运行；效果验证调试</t>
-  </si>
-  <si>
-    <t>F-SWM-02-04</t>
-  </si>
-  <si>
-    <t>版本输出对比</t>
-  </si>
-  <si>
-    <t>对不同版本提示词的输出结果进行对比，支撑迭代优化决策。</t>
-  </si>
-  <si>
-    <t>版本输出对比；迭代优化支撑</t>
-  </si>
-  <si>
-    <t>F-SWM-03-01 场景适配；F-SWM-03-02 动态调用与指令生成</t>
-  </si>
-  <si>
-    <t>SRS R-SWM-001(运行时)</t>
-  </si>
-  <si>
-    <t>R-SWM-001 的场景适配与动态调用是运行时决策关注点，与模板库资产管理分离。</t>
-  </si>
-  <si>
-    <t>F-SWM-03-01</t>
-  </si>
-  <si>
-    <t>场景适配</t>
-  </si>
-  <si>
-    <t>按作业场景(人设标签/目标受众/当前态势)选择合适模板；模板填充失败时降级为默认模板。</t>
-  </si>
-  <si>
-    <t>场景适配模板；填充失败降级默认</t>
-  </si>
-  <si>
-    <t>F-SWM-03-02</t>
-  </si>
-  <si>
-    <t>动态调用与指令生成</t>
-  </si>
-  <si>
-    <t>智能体作业时动态调用并填充提示词，生成最终作业指令。</t>
-  </si>
-  <si>
-    <t>动态调用填充；生成作业指令</t>
-  </si>
-  <si>
-    <t>对接 II-09</t>
-  </si>
-  <si>
-    <t>F-SWM-04-01 作业记忆存储；F-SWM-04-02 场景记忆沉淀；F-SWM-04-03 历史记忆复用；F-SWM-04-04 个性化状态延续</t>
-  </si>
-  <si>
-    <t>SRS R-SWM-002</t>
-  </si>
-  <si>
-    <t>对应 R-SWM-002，记忆存储/沉淀/复用/延续是同一记忆对象的生命周期环节，内聚不拆。</t>
-  </si>
-  <si>
-    <t>F-SWM-04-01</t>
-  </si>
-  <si>
-    <t>作业记忆存储</t>
-  </si>
-  <si>
-    <t>对智能体作业过程中的关键信息(已完成任务/互动对象/立场表达等)进行记忆存储。</t>
-  </si>
-  <si>
-    <t>关键信息记忆存储</t>
-  </si>
-  <si>
-    <t>F-SWM-04-02</t>
-  </si>
-  <si>
-    <t>场景记忆沉淀</t>
-  </si>
-  <si>
-    <t>将重复场景下的经验沉淀为场景记忆，形成可复用行为模式。</t>
-  </si>
-  <si>
-    <t>场景经验沉淀为模式</t>
-  </si>
-  <si>
-    <t>F-SWM-04-03</t>
-  </si>
-  <si>
-    <t>历史记忆复用</t>
-  </si>
-  <si>
-    <t>在相似作业中复用历史记忆，提升作业连贯性与效率。</t>
-  </si>
-  <si>
-    <t>相似作业复用历史记忆</t>
-  </si>
-  <si>
-    <t>F-SWM-04-04</t>
-  </si>
-  <si>
-    <t>个性化状态延续</t>
-  </si>
-  <si>
-    <t>基于记忆维持智能体个性化状态延续，使其长期行为符合人设且不断演进。</t>
-  </si>
-  <si>
-    <t>个性化状态延续；符合人设演进</t>
-  </si>
-  <si>
-    <t>F-SWM-05-01 智能体定义构建；F-SWM-05-02 账号绑定引用；F-SWM-05-03 同步至 MC 持存；F-SWM-05-04 OCC 智能体节点定义来源</t>
-  </si>
-  <si>
-    <t>SRS R-SWM-003</t>
-  </si>
-  <si>
-    <t>对应 R-SWM-003，构建是装配链(编写初值+配置策略+组装+下发)，内聚不拆；吸收 R-SWM-001 中『组装与同步下发』能力作为定义交付出口。</t>
-  </si>
-  <si>
-    <t>F-SWM-05-01</t>
-  </si>
-  <si>
-    <t>智能体定义构建</t>
-  </si>
-  <si>
-    <t>按人设标签编写提示词初值与记忆初值并配置作业策略(目标/场景/边界)，组装为完整智能体定义，以全局唯一 agent_id 为标识。</t>
-  </si>
-  <si>
-    <t>人设+提示词初值+记忆初值+作业策略；agent_id 标识</t>
-  </si>
-  <si>
-    <t>F-SWM-05-02</t>
-  </si>
-  <si>
-    <t>账号绑定引用</t>
-  </si>
-  <si>
-    <t>智能体定义与账号严格 1:1 绑定(agent_id↔account_id)，绑定关系由 MC 维护，本子系统构建时引用 account_id。</t>
-  </si>
-  <si>
-    <t>agent_id↔account_id 1:1；构建时引用 account_id</t>
-  </si>
-  <si>
-    <t>绑定关系归 MC R-MC-013</t>
-  </si>
-  <si>
-    <t>F-SWM-05-03</t>
-  </si>
-  <si>
-    <t>同步至 MC 持存</t>
-  </si>
-  <si>
-    <t>构建完成的智能体定义经 II-14 同步至 MC 持存，取得持存版本号；定义更新时以同一 agent_id 重新同步。</t>
-  </si>
-  <si>
-    <t>经 II-14 同步；取得版本号；更新重同步</t>
-  </si>
-  <si>
-    <t>F-SWM-05-04</t>
-  </si>
-  <si>
-    <t>OCC 智能体节点定义来源</t>
-  </si>
-  <si>
-    <t>构建出的智能体定义是 OCC 作战编排中智能体节点的定义来源。</t>
-  </si>
-  <si>
-    <t>作为 OCC 编排智能体节点定义来源</t>
-  </si>
-  <si>
-    <t>F-SWM-06-01 有效性评测；F-SWM-06-02 评测数据集管理；F-SWM-06-03 批量跑题执行；F-SWM-06-04 答案对比与打分；F-SWM-06-05 评分汇总与报告；F-SWM-06-06 迭代/淘汰决策与反馈闭环</t>
-  </si>
-  <si>
-    <t>SRS R-SWM-004</t>
-  </si>
-  <si>
-    <t>对应 R-SWM-004。06-01 为线上效果统计(触达/互动/完成率)；06-02~05 为离线数据集评测流程(录入题集→跑题→打分→汇总)，按流程环节拆 4 个功能；一在线一离线互补评估；06-06 综合双轨结论做决策与反馈。</t>
-  </si>
-  <si>
-    <t>F-SWM-06-01</t>
-  </si>
-  <si>
-    <t>有效性评测</t>
-  </si>
-  <si>
-    <t>基于 MC 可观测性上报的作业效果数据(触达/互动/任务完成率)评测智能体有效性。</t>
-  </si>
-  <si>
-    <t>基于 MC 作业效果评测有效性</t>
-  </si>
-  <si>
-    <t>数据来自 R-MC-010</t>
-  </si>
-  <si>
-    <t>F-SWM-06-02</t>
-  </si>
-  <si>
-    <t>评测数据集管理</t>
-  </si>
-  <si>
-    <t>管理智能体评测用的标准数据集：提示词工程师编辑测试用例集，每条用例含问题、预期答案、评分标准（规则匹配/关键词/LLM 裁判/人工评判）、权重与所属评分维度（稳定性/合规性/人设一致性）；支持数据集创建、用例录入/批量导入/修改/删除与版本管理。</t>
-  </si>
-  <si>
-    <t>数据集创建与元信息；用例录入(问题/预期答案/评分标准/权重/维度)；批量导入；用例增删改查；数据集版本管理</t>
-  </si>
-  <si>
-    <t>数据集是离线评测的可复现基准</t>
-  </si>
-  <si>
-    <t>F-SWM-06-03</t>
-  </si>
-  <si>
-    <t>批量跑题执行</t>
-  </si>
-  <si>
-    <t>对指定 agent_id 按数据集逐题执行评测：系统将每题问题连同智能体定义（提示词+人设+记忆）交由 IRS 本地大模型推理（不经执行网关），收集智能体的实际回答；支持异步批量执行、进度跟踪与失败重跑。</t>
-  </si>
-  <si>
-    <t>逐题调 IRS 推理收集实际回答；推理不经执行网关(CON-10)；异步批量执行；进度跟踪；失败题重跑</t>
-  </si>
-  <si>
-    <t>对接 II-08/EI-05</t>
-  </si>
-  <si>
-    <t>F-SWM-06-04</t>
-  </si>
-  <si>
-    <t>答案对比与打分</t>
-  </si>
-  <si>
-    <t>将跑题收集的实际回答与用例预期答案按评分标准对比打分，支持规则匹配、LLM 裁判（LLM-as-judge）与人工评判三种模式，按用例逐题配置；LLM 裁判置信度低时标记待人工评判。</t>
-  </si>
-  <si>
-    <t>规则匹配(精确/关键词)；LLM-as-judge(本地模型裁判)；人工评判；逐题配置评分模式；置信度低转人工</t>
-  </si>
-  <si>
-    <t>F-SWM-06-05</t>
-  </si>
-  <si>
-    <t>评分汇总与报告</t>
-  </si>
-  <si>
-    <t>按评分维度（稳定性/合规性/人设一致性）汇总各维度得分、通过率、人设漂移维度，对比历史基线与上次同题集得分，输出评测报告；报告含质量等级、薄弱用例与改进建议。</t>
-  </si>
-  <si>
-    <t>维度得分汇总(稳定性/合规性/人设一致性)；通过率/人设漂移维度；历史基线对比；版本演进对比；评测报告输出</t>
-  </si>
-  <si>
-    <t>供 F-SWM-06-06 决策消费</t>
-  </si>
-  <si>
-    <t>F-SWM-06-06</t>
-  </si>
-  <si>
-    <t>迭代/淘汰决策与反馈闭环</t>
-  </si>
-  <si>
-    <t>综合 F-SWM-06-01 线上有效性统计与 F-SWM-06-05 离线数据集评测报告，对低效定义提出淘汰、对高价值定义提出迭代优化，形成评测决策；反馈至 M-SWM-02（驱动模板迭代）与 M-SWM-05（驱动定义重建）形成闭环。</t>
-  </si>
-  <si>
-    <t>综合线上+离线双轨结论；淘汰/迭代决策；反馈 M-SWM-02 模板迭代；反馈 M-SWM-05 定义重建；闭环</t>
-  </si>
-  <si>
-    <t>私有化大模型部署</t>
-  </si>
-  <si>
-    <t>SRS §引言/IRS</t>
-  </si>
-  <si>
-    <t>IRS 仅一条 FR 且定义为单一基础设施，部署管理与推理服务紧耦合，保持 1 模块不拆（对齐轻量子系统粒度）。</t>
-  </si>
-  <si>
-    <t>F-IRS-01-01 私有化部署与模型加载；F-IRS-01-02 统一推理调用接口；F-IRS-01-03 部署独立性</t>
-  </si>
-  <si>
-    <t>SRS R-IRS-001</t>
-  </si>
-  <si>
-    <t>对应 R-IRS-001，部署加载与推理接口同属本地推理服务，内聚不拆。</t>
-  </si>
-  <si>
-    <t>F-IRS-01-01</t>
-  </si>
-  <si>
-    <t>私有化部署与模型加载</t>
-  </si>
-  <si>
-    <t>在私有化 GPU 算力环境部署本地大模型，完成模型加载与服务实例化；模型加载失败回退上一可用版本。</t>
-  </si>
-  <si>
-    <t>私有化部署；模型加载实例化；失败回退</t>
-  </si>
-  <si>
-    <t>SRS R-IRS-001；CON-06</t>
-  </si>
-  <si>
-    <t>F-IRS-01-02</t>
-  </si>
-  <si>
-    <t>统一推理调用接口</t>
-  </si>
-  <si>
-    <t>对外提供统一推理调用接口，供数据爬取/蜂群智能体/舆情作战等子系统调用；算力资源不足时拒绝新请求并排队。</t>
-  </si>
-  <si>
-    <t>统一推理接口；供各子系统调用；算力不足排队</t>
-  </si>
-  <si>
-    <t>F-IRS-01-03</t>
-  </si>
-  <si>
-    <t>部署独立性</t>
-  </si>
-  <si>
-    <t>部署不依赖外部公有云模型服务。</t>
-  </si>
-  <si>
-    <t>不依赖公有云</t>
-  </si>
-  <si>
-    <t>舆情作战业务子系统</t>
-  </si>
-  <si>
-    <t>SRS §引言/OCC</t>
-  </si>
-  <si>
-    <t>V3.3：原 DC「数据分析与情报」(R-DC-007~010) 移入本子系统，重编号为 R-OCC-002~005，原 R-OCC-002~005 顺延为 R-OCC-006~009，OCC 需求连续编号 R-OCC-001~009；共 9 模块。R-OCC-001(目标识别)含目标实体 CRUD 与目标关联网络(图结构)两个异构关注点，拆 2；数据分析与情报(R-OCC-002~005)四项分析能力内聚为 1 模块；R-OCC-006(作战编排)含方案规划与编排执行引擎两类，拆 2；R-OCC-009(内容管理)含主数据排期与审核风控两类，拆 2。</t>
-  </si>
-  <si>
-    <t>F-OCC-01-01 目标建档与标识；F-OCC-01-02 目标属性维护；F-OCC-01-03 目标状态生命周期；F-OCC-01-04 目标多维信息融合；F-OCC-01-05 目标变更事件广播</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-001(实体)</t>
-  </si>
-  <si>
-    <t>R-OCC-001 的目标实体 CRUD/状态机与目标关联网络(图结构建模)是不同数据范式，故拆。</t>
-  </si>
-  <si>
-    <t>F-OCC-01-01</t>
-  </si>
-  <si>
-    <t>目标建档与标识</t>
-  </si>
-  <si>
-    <t>R-OCC-001</t>
-  </si>
-  <si>
-    <t>每个识别出的目标建档为一条目标数据，赋予全局唯一 target_id。</t>
-  </si>
-  <si>
-    <t>目标建档；全局唯一 target_id</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-001</t>
-  </si>
-  <si>
-    <t>F-OCC-01-02</t>
-  </si>
-  <si>
-    <t>目标属性维护</t>
-  </si>
-  <si>
-    <t>目标档案各属性(事件主体/争议点/画像属性/干预切入点等)支持新增/修改/删除，可随事件演进更新。</t>
-  </si>
-  <si>
-    <t>属性增删改；可随事件演进更新</t>
-  </si>
-  <si>
-    <t>F-OCC-01-03</t>
-  </si>
-  <si>
-    <t>目标状态生命周期</t>
-  </si>
-  <si>
-    <t>目标具备状态生命周期(待核实/已确认/已锁定/已处置/已归档)，支持状态流转。</t>
-  </si>
-  <si>
-    <t>目标状态机流转</t>
-  </si>
-  <si>
-    <t>F-OCC-01-04</t>
-  </si>
-  <si>
-    <t>目标多维信息融合</t>
-  </si>
-  <si>
-    <t>识别过程综合事件主体/传播源头与链路/事件群体账号传播画像/干预切入点与薄弱点，形成完整目标档案；融合本子系统数据分析与情报（M-OCC-02）的产出。</t>
-  </si>
-  <si>
-    <t>多维信息融合；本期人工识别+系统维护</t>
-  </si>
-  <si>
-    <t>依赖 OCC 分析(M-OCC-02)/IRS</t>
-  </si>
-  <si>
-    <t>F-OCC-01-05</t>
-  </si>
-  <si>
-    <t>目标变更事件广播</t>
-  </si>
-  <si>
-    <t>目标变更经事件总线广播 target.changed 事件，使用方(作战编排/效果评估)订阅响应。</t>
-  </si>
-  <si>
-    <t>target.changed 事件广播；使用方订阅</t>
-  </si>
-  <si>
-    <t>F-OCC-02-01 群体-个体下钻筛选；F-OCC-02-02 关系图谱与图查询；F-OCC-02-03 实体检索与档案；F-OCC-02-04 文本智能分析</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-002~005</t>
-  </si>
-  <si>
-    <t>对应 R-OCC-002~005 四项分析需求（V3.3 由 DC R-DC-007~010 移入并重编号），均属分析研判能力域（筛选/图谱/检索/文本），内聚不拆；原始数据经 II-13 从 DC 获取，分析产出供目标识别(M-OCC-01)与情报回注(DC R-DC-007)。</t>
-  </si>
-  <si>
-    <t>F-OCC-02-01</t>
-  </si>
-  <si>
-    <t>群体-个体下钻筛选</t>
-  </si>
-  <si>
-    <t>R-OCC-002</t>
-  </si>
-  <si>
-    <t>结合 AI 算法实现从群体到个体的逐层下钻筛选，使分析人员能从大范围群体按特征逐步缩小范围定位目标个体。</t>
-  </si>
-  <si>
-    <t>AI 算法逐层下钻；群体→个体定位</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-002</t>
-  </si>
-  <si>
-    <t>依赖 IRS</t>
-  </si>
-  <si>
-    <t>F-OCC-02-02</t>
-  </si>
-  <si>
-    <t>关系图谱与图查询</t>
-  </si>
-  <si>
-    <t>R-OCC-003</t>
-  </si>
-  <si>
-    <t>基于实体与关联数据绘制关系图谱并支持图查询，对给定实体输出关联拓扑与情报标签形成关联网络；数据量过大时分页或限流。</t>
-  </si>
-  <si>
-    <t>关系图谱绘制；图查询；关联拓扑与情报标签；分页/限流</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-003</t>
-  </si>
-  <si>
-    <t>F-OCC-02-03</t>
-  </si>
-  <si>
-    <t>实体检索与档案</t>
-  </si>
-  <si>
-    <t>R-OCC-004</t>
-  </si>
-  <si>
-    <t>提供基础信息检索（按账号/昵称/标识），并聚合多来源信息形成实体全维度档案；检索超时时降级返回部分结果。</t>
-  </si>
-  <si>
-    <t>实体检索；全维度档案；检索超时降级</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-004</t>
-  </si>
-  <si>
-    <t>F-OCC-02-04</t>
-  </si>
-  <si>
-    <t>文本智能分析</t>
-  </si>
-  <si>
-    <t>R-OCC-005</t>
-  </si>
-  <si>
-    <t>对文本内容结合文本模型（调 IRS 本地大模型）与关键词库进行规则匹配与分类筛选（立场/情感/观点），用于内容研判与目标识别；模型不可用回退关键词规则。</t>
-  </si>
-  <si>
-    <t>文本模型+关键词库；规则匹配与分类筛选；降级回退关键词</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-005</t>
-  </si>
-  <si>
-    <t>对接 EI-05；模型不可用回退关键词</t>
-  </si>
-  <si>
-    <t>F-OCC-03-01 目标关联关系建模；F-OCC-03-02 关系网络查询</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-001(图结构)</t>
-  </si>
-  <si>
-    <t>R-OCC-001 的目标关联是图结构建模(关系类型/网络查询)，与目标实体 CRUD 是不同数据范式，故拆。</t>
-  </si>
-  <si>
-    <t>F-OCC-03-01</t>
-  </si>
-  <si>
-    <t>目标关联关系建模</t>
-  </si>
-  <si>
-    <t>目标之间建立关联关系，形成目标关系网络。</t>
-  </si>
-  <si>
-    <t>关联关系建模；关系网络</t>
-  </si>
-  <si>
-    <t>F-OCC-03-02</t>
-  </si>
-  <si>
-    <t>关系网络查询</t>
-  </si>
-  <si>
-    <t>支持对目标关系网络的查询与探索；目标关联断裂时标注断点。</t>
-  </si>
-  <si>
-    <t>关系网络查询；断点标注</t>
-  </si>
-  <si>
-    <t>F-OCC-04-01 干预策略匹配；F-OCC-04-02 作业方案生成</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-006(决策)</t>
-  </si>
-  <si>
-    <t>R-OCC-006 的方案规划(业务决策域)与编排执行(工作流建模+运行域)是不同职责域，故拆。</t>
-  </si>
-  <si>
-    <t>F-OCC-04-01</t>
-  </si>
-  <si>
-    <t>干预策略匹配</t>
-  </si>
-  <si>
-    <t>R-OCC-006</t>
-  </si>
-  <si>
-    <t>根据目标档案中的干预切入点匹配干预策略(本期以人工匹配为主)。</t>
-  </si>
-  <si>
-    <t>切入点→策略匹配；本期人工为主</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-006</t>
-  </si>
-  <si>
-    <t>F-OCC-04-02</t>
-  </si>
-  <si>
-    <t>作业方案生成</t>
-  </si>
-  <si>
-    <t>生成具体作业方案(含内容/账号/时间/节奏)。</t>
-  </si>
-  <si>
-    <t>内容/账号/时间/节奏方案</t>
-  </si>
-  <si>
-    <t>F-OCC-05-01 编排建模；F-OCC-05-02 节点参数填充；F-OCC-05-03 编排落地与执行跟踪</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-006(建模+运行)</t>
-  </si>
-  <si>
-    <t>R-OCC-006 的流程编排(DAG 建模)与执行调度(落地跟踪/回滚)紧耦合，合并为编排执行引擎。</t>
-  </si>
-  <si>
-    <t>F-OCC-05-01</t>
-  </si>
-  <si>
-    <t>编排建模</t>
-  </si>
-  <si>
-    <t>将作业方案编排为执行流程图（DAG）：以 MC 中智能体节点/自动化脚本节点为编排实体，定义节点间的前后序、并行与分支关系；节点类型后续可扩充。</t>
-  </si>
-  <si>
-    <t>DAG 流程图建模；智能体节点+脚本节点；前后序/并行/分支关系；节点类型可扩充</t>
-  </si>
-  <si>
-    <t>F-OCC-05-02</t>
-  </si>
-  <si>
-    <t>节点参数填充</t>
-  </si>
-  <si>
-    <t>为编排流程图中的各节点填充具体执行参数：智能体节点的 agent_id 引用、脚本节点的通道与目标、内容/账号/时间/节奏等作业参数。</t>
-  </si>
-  <si>
-    <t>智能体节点 agent_id 引用；脚本节点通道与目标；内容/账号/时间/节奏参数填充</t>
-  </si>
-  <si>
-    <t>F-OCC-05-03</t>
-  </si>
-  <si>
-    <t>编排落地与执行跟踪</t>
-  </si>
-  <si>
-    <t>编排落地后由 MC 统一执行网关收口所有节点动作；节点执行失败时按编排定义回滚/跳过/转人工。</t>
-  </si>
-  <si>
-    <t>经 MC 执行网关落地；失败回滚/跳过/转人工</t>
-  </si>
-  <si>
-    <t>F-OCC-06-01 单轮成效统计；F-OCC-06-02 舆论走势修正评估；F-OCC-06-03 策略迭代反馈；F-OCC-06-04 作业复盘；F-OCC-06-05 中短期与长期效果评估</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-007</t>
-  </si>
-  <si>
-    <t>对应 R-OCC-007，各评估维度同属评估分析能力域，内聚不拆。</t>
-  </si>
-  <si>
-    <t>F-OCC-06-01</t>
-  </si>
-  <si>
-    <t>单轮成效统计</t>
-  </si>
-  <si>
-    <t>基于 DC 舆情数据与 MC 作业数据完成单轮干预成效统计(触达/互动/立场变化等)。</t>
-  </si>
-  <si>
-    <t>DC 舆情+MC 作业数据；成效统计</t>
-  </si>
-  <si>
-    <t>数据来自 DC/MC(R-MC-010)</t>
-  </si>
-  <si>
-    <t>F-OCC-06-02</t>
-  </si>
-  <si>
-    <t>舆论走势修正评估</t>
-  </si>
-  <si>
-    <t>基于 DC 前后舆情对比对舆论走势进行修正评估。</t>
-  </si>
-  <si>
-    <t>前后舆情对比；走势修正</t>
-  </si>
-  <si>
-    <t>F-OCC-06-03</t>
-  </si>
-  <si>
-    <t>策略迭代反馈</t>
-  </si>
-  <si>
-    <t>将评估结果反馈至策略库以迭代优化。</t>
-  </si>
-  <si>
-    <t>评估反馈策略库迭代</t>
-  </si>
-  <si>
-    <t>F-OCC-06-04</t>
-  </si>
-  <si>
-    <t>作业复盘</t>
-  </si>
-  <si>
-    <t>结合 MC 作业执行记录进行作业复盘总结经验。</t>
-  </si>
-  <si>
-    <t>MC 作业记录复盘</t>
-  </si>
-  <si>
-    <t>F-OCC-06-05</t>
-  </si>
-  <si>
-    <t>中短期与长期效果评估</t>
-  </si>
-  <si>
-    <t>提供中短期实网绩效评估与长期舆论塑造效果评估接口，实现效果联动。</t>
-  </si>
-  <si>
-    <t>中短期绩效+长期塑造效果评估接口</t>
-  </si>
-  <si>
-    <t>F-OCC-07-01 多语种多场景多风格策略库；F-OCC-07-02 策略分类管理与版本控制；F-OCC-07-03 策略迭代优化；F-OCC-07-04 策略场景适配与动态调用</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-008</t>
-  </si>
-  <si>
-    <t>对应 R-OCC-008，单一策略资产的治理(组织/版本/迭代/适配)内聚不拆。</t>
-  </si>
-  <si>
-    <t>F-OCC-07-01</t>
-  </si>
-  <si>
-    <t>多语种多场景多风格策略库</t>
-  </si>
-  <si>
-    <t>按多语种/多场景/多风格组织舆论作业策略库。</t>
-  </si>
-  <si>
-    <t>多语种/多场景/多风格</t>
-  </si>
-  <si>
-    <t>F-OCC-07-02</t>
-  </si>
-  <si>
-    <t>策略分类管理与版本控制</t>
-  </si>
-  <si>
-    <t>对策略进行分类管理与版本控制。</t>
-  </si>
-  <si>
-    <t>分类管理；版本控制</t>
-  </si>
-  <si>
-    <t>F-OCC-07-03</t>
-  </si>
-  <si>
-    <t>策略迭代优化</t>
-  </si>
-  <si>
-    <t>根据作业效果反馈对策略进行迭代优化。</t>
-  </si>
-  <si>
-    <t>效果反馈迭代优化</t>
-  </si>
-  <si>
-    <t>F-OCC-07-04</t>
-  </si>
-  <si>
-    <t>策略场景适配与动态调用</t>
-  </si>
-  <si>
-    <t>支持策略的场景适配与动态调用。</t>
-  </si>
-  <si>
-    <t>场景适配；动态调用</t>
-  </si>
-  <si>
-    <t>F-OCC-08-01 内容主数据维护；F-OCC-08-02 素材分类与平台适配；F-OCC-08-03 发布排期；F-OCC-08-04 内容变更事件与分发</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-009(资产+调度)</t>
-  </si>
-  <si>
-    <t>R-OCC-009 的内容主数据(CMS 资产域)与审核风控(合规域)是异构关注点，故拆；排期是主数据的时间调度，归入主数据管理。</t>
-  </si>
-  <si>
-    <t>F-OCC-08-01</t>
-  </si>
-  <si>
-    <t>内容主数据维护</t>
-  </si>
-  <si>
-    <t>R-OCC-009</t>
-  </si>
-  <si>
-    <t>唯一维护内容主数据（原始素材、分类、审核状态、来源）的 CRUD；content_id 为全局唯一引用，使用方不复制主数据。</t>
-  </si>
-  <si>
-    <t>主数据 CRUD；content_id 全局唯一；使用方不复制主数据</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-009</t>
-  </si>
-  <si>
-    <t>权威源主数据 CRUD</t>
-  </si>
-  <si>
-    <t>F-OCC-08-02</t>
-  </si>
-  <si>
-    <t>素材分类与平台适配</t>
-  </si>
-  <si>
-    <t>对素材分类管理，支持标签/平台分类与账号适配。</t>
-  </si>
-  <si>
-    <t>素材分类；标签/平台分类/账号适配</t>
-  </si>
-  <si>
-    <t>F-OCC-08-03</t>
-  </si>
-  <si>
-    <t>发布排期</t>
-  </si>
-  <si>
-    <t>支持按素材/账号/时间制定定时发布排期；排期冲突时提示调整。</t>
-  </si>
-  <si>
-    <t>定时发布排期；冲突提示</t>
-  </si>
-  <si>
-    <t>F-OCC-08-04</t>
-  </si>
-  <si>
-    <t>内容变更事件与分发</t>
-  </si>
-  <si>
-    <t>内容新增或状态变更经事件总线广播 content.changed 事件，使用方订阅响应；作为权威源向使用方主动分发 content_id。</t>
-  </si>
-  <si>
-    <t>content.changed 事件广播；主动分发 content_id</t>
-  </si>
-  <si>
-    <t>对接 II-12a</t>
-  </si>
-  <si>
-    <t>F-OCC-09-01 发布前内容审核；F-OCC-09-02 敏感词检测与拦截</t>
-  </si>
-  <si>
-    <t>SRS R-OCC-009(合规)</t>
-  </si>
-  <si>
-    <t>R-OCC-009 的审核与敏感词检测是合规风控域(敏感词库+拦截策略)，与主数据 CRUD 异构，故拆。</t>
-  </si>
-  <si>
-    <t>F-OCC-09-01</t>
-  </si>
-  <si>
-    <t>发布前内容审核</t>
-  </si>
-  <si>
-    <t>发布前对内容进行审核。</t>
-  </si>
-  <si>
-    <t>发布前审核</t>
-  </si>
-  <si>
-    <t>F-OCC-09-02</t>
-  </si>
-  <si>
-    <t>敏感词检测与拦截</t>
-  </si>
-  <si>
-    <t>对内容进行敏感词检测；敏感词命中时拦截并标记待人工复核。</t>
-  </si>
-  <si>
-    <t>敏感词检测；命中拦截待复核</t>
-  </si>
-</sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="1023">
+  <x:si>
+    <x:t>子系统(一级软部件)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>代号</x:t>
+  </x:si>
+  <x:si>
+    <x:t>模块数</x:t>
+  </x:si>
+  <x:si>
+    <x:t>模块编号</x:t>
+  </x:si>
+  <x:si>
+    <x:t>模块名称(二级软部件)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应需求</x:t>
+  </x:si>
+  <x:si>
+    <x:t>职责简述</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-DC-00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4个</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-DC-001~008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基础设施层的数据采集与 ETL 处理底座，采用「任务驱动采集」范式：采集任务由人工/OCC 情报回注注入任务池，爬虫作为执行器消费任务、按目标定向抓取；通过情报回注与目标扩散形成「OCC 分析→DC 采集」跨子系统反向闭环。原「数据分析与情报」V3.3 起移至 OCC。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-DC-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>采集调度与限流（输入闸门与调度大脑）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-DC-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>消费人工与情报回注注入的采集任务，管理任务池、目标级去重、调度队列与配额限流，使采得不重复、不丢失、不失控；支撑情报回注入池去重与配额约束。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-DC-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多平台数据采集与策略自优化（爬虫执行器）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-DC-001,004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>消费任务池下发的任务，按任务目标从 TikTok/Instagram/Facebook/YouTube/X 等海外社交平台采集原始数据（用户/内容/互动/关系），使用代理 IP 与维护账号应对反爬，并面向海外社交平台提供代理网络出口（按平台/地区分配、定时轮换、可用性检测、失效剔除），基于历史指标自适应优化采集策略。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-DC-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>数据处理与存储（ETL 数据加工厂）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-DC-005,006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对经 Kafka 流入的原始数据做分布式批处理清洗（字段提取、格式标准化、去重、关联），产出结构化干净数据，并按数据特征持久化到不同存储模型（明细入 HBase、元数据/索引入关系库、关系数据入图库），供分析与检索按需读取。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-DC-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>情报驱动采集与目标扩散（反向驱动大脑）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-DC-007,008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>打通「OCC 分析→DC 采集」跨子系统反向驱动链路，使 OCC 数据分析与情报（R-OCC-002~005）产出的目标个体/关联实体/传播节点回注任务池并按关系扩散采集，形成「发现线索→定向扩散采集→锁定目标」的情报驱动闭环。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14个</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-001~014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>统一自动化执行引擎与多终端执行网关：统一管理移动端（真机/云手机/ARM 板卡/虚拟化真机）与桌面端（指纹浏览器 Profile）两类执行终端；收口所有终端动作（可观测/可审计/可熔断）；承担账号资源平台级权威源与智能体执行宿主两项职责。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>执行终端接入与台账（终端资源池管理者）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>统一管理四类执行终端（移动端真机/云手机/ARM 板卡/虚拟化真机、桌面端指纹浏览器 Profile）的接入注册、台账维护、分组标签、实时状态监控与批量操作，提供终端资源池。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>终端身份与环境隔离（终端身份伪造与隔离底座）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>通过终端指纹固化（移动端硬件/软件指纹、桌面端 Profile 渲染层指纹 20+ 维），使终端长期呈现一致真人设备身份；终端间环境（指纹、网络、账号、Cookie/缓存）相互隔离，降低被风控识别概率。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>终端风控分级与代理绑定（终端健康哨兵与风控对抗）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按指纹真实度对终端风控分级（养号优先选高真实度）；识别平台风控信号主动规避、持续触发时降级；为每终端/Profile 分配独立固定代理 IP 并绑定（仅失效时切换重新固定）。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>远程控制（人机交互窗口）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对单台及多台终端提供低延迟实时画面预览与输入控制，支持多终端同屏监控；移动端用 WebRTC 通道、桌面端指纹浏览器 Profile 用商用 API 画面预览。远控通道与任务执行通道相互分离。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>统一执行网关（动作收口核心）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>以统一执行网关作为所有执行终端动作的唯一收口，对动作鉴权（校验来源/目标合法性）、记录（写动作日志并全量上报 OM）、熔断（检测风控信号或异常频率时停止后续动作）、转发落地；保证每一个动作可观测、可审计、可熔断、动作不裸奔。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>双执行模式与执行目标（执行引擎）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提供脚本模式与智能体模式两种执行引擎，分别承载固定流程驱动与大模型实时决策驱动的作业，覆盖移动端终端与桌面端 Profile，支持群控、养号与内容投放三类执行目标；所有动作经 R-MC-005 统一执行网关落地。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务管理（任务调度中枢）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>把操作意图转换为设备可执行的任务并调度，支撑各类作业的排队、分发、重试与定时执行。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>自动化编排能力（自动化能力中枢）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提供自动化能力的中枢，覆盖从模板任务到可视化工作流再到脚本开发的递进式编排，支持 ADB/CDP 等多种自动化通道，针对 TikTok/Facebook 等平台实现模拟点击自动化；产出动作均经执行网关落地，不直接操作设备。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>账号操作编排与养号（账号自动化编排）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>承载养号、账号-终端-代理绑定、登录状态维护等可自动化的账号操作的执行编排，以及养号拟人化节奏策略（内置）。认知作战账号经移动端 ADB/无障碍通道养号、爬虫账号经桌面端 CDP 通道养护。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>可观测性与作业统计复盘（全链路可观测与复盘大脑）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>使终端、账号、任务的每个动作可知可追溯，支撑记录、回传、告警、审计，并完成蜂群作业数据统计与任务复盘、将投送效果联动回传上游供效果评估闭环；动作留痕与作业统计统一收口于本功能（避免重复采集）。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>账号主数据管理（账号资源权威源）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>平台级权威源，唯一维护社交媒体账号主数据（注册、凭据、验证、风险评估、生命周期、账号分类），经事件总线向 DC/SWM/OCC 分发 account_id，保证全网一致、凭据加密、被封账号全网即时失效；账号分爬虫账号(桌面端)与认知作战账号(移动端)两类。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体账号分层分组（账号组织）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对智能体账号按业务目标/平台/地区/风险等级分层分组，形成可控账号层级结构，并管理智能体账号作业生命周期（待激活/活跃/休眠/受限/封禁/回收）的自动与人工流转。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体账号绑定与资产迁移（四元作战单元）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>维护账号与智能体定义（agent_id）严格 1:1 绑定，叠加账号-终端-代理绑定形成四元作战单元（agent_id:account_id:终端:代理 IP = 1:1:1:1）；账号被封后支持资产迁移整体继承人格（人设标签/提示词版本/记忆）。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-MC-14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体执行宿主与同步（智能体执行宿主）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-MC-014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>作为智能体执行宿主，接收并持存 SWM 同步来的智能体定义（以 agent_id 为标识，含人设标签/提示词/记忆/作业策略），任务执行时调用这些定义驱动设备作业，执行前校验人设一致性（不一致拒绝执行）；确立「SWM 定义中心、MC 执行宿主」分工。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OM-00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OM-001~002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>汇聚全系统日志与指标，形成统一运维数据底座，支撑常态化运维与告警。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OM-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>日志汇聚与检索（日志数据底座）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OM-001(日志)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>通过日志采集将各子系统日志汇聚至统一日志库，支持全文检索。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OM-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>指标采集与时序存储（指标数据底座）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OM-001(指标)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>通过指标采集器采集设备在线率、任务成功率、爬虫吞吐量、队列积压等指标，形成时序数据存储，供告警与看板消费。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OM-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>告警引擎（告警大脑）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OM-002(告警)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基于指标与规则产生告警，支持阈值告警与异常检测告警，通过多渠道通知，含告警风暴聚合去重。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OM-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>运维可视化与作业（运维作业台）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OM-002(看板+运维)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提供多维可视化看板，并支持日志查询、故障定位、巡检与容量观测等常态化运维操作。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-COM-00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2个</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-COM-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>为各子系统提供统一的用户认证、基于角色的访问控制与组织管理，支持多组织数据隔离。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-COM-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>身份认证（身份守门人）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-COM-001(AuthN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提供统一的登录认证与双因素认证，签发认证令牌。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-COM-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>权限与组织管理（权限决策与组织隔离）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-COM-001(AuthZ)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基于角色访问控制进行权限决策，管理组织与成员，并对多组织/多租户进行数据隔离。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-SWM-00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SWM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6个</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-SWM-001~004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>执行层的「智能体定义与记忆中心」：根据人设(画像/账号属性)编写驱动智能体作业的提示词与记忆，将智能体定义(人设标签/提示词/记忆/作业策略)以 agent_id 同步下发至 MC 持存；承担智能体构建、评测、提示词与人设管理、记忆管理；不直接操作设备。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-SWM-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>人设标签管理（智能体人格定义中心）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-SWM-001(人设)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>为每个 agent_id 绑定人设标签(身份特征/立场倾向/语言风格/兴趣领域等画像属性)；人设挂 agent_id，经 agent_id↔account_id 1:1 绑定间接对应账号；不复制账号主数据。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-SWM-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提示词模板库与版本管理（提示词资产管理）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-SWM-001(资产)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>建立提示词模板库并按用途/平台/目标分类管理；对提示词进行版本管理，以 agent_id 为主键索引，支持版本对比/回滚/变更记录。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-SWM-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提示词场景适配与动态调用（提示词运行时引擎）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-SWM-001(运行时)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按作业场景(人设标签/目标受众/当前态势)适配提示词，作业时动态调用并填充生成最终作业指令。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-SWM-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>蜂群记忆管理（智能体记忆中枢）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-SWM-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>实现智能体作业记忆的存储、场景沉淀、历史复用与个性化状态延续，使智能体长期行为符合人设且不断演进。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-SWM-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体构建与定义下发（智能体装配工厂）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-SWM-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>根据人设标签编写提示词与记忆初值、配置作业策略，组装为完整智能体定义并以 agent_id 为标识，经 II-14 同步至 MC 持存、供 OCC 作战编排引用。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-SWM-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体评测与迭代决策（智能体质量裁判）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-SWM-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对构建出的智能体采用「线上效果 + 离线数据集」双轨评测范式评估有效性/稳定性/合规性；离线评测以『评测集、评估器、实验』三类实体组织，淘汰低效定义、迭代优化高价值定义，形成「构建→评测→迭代」闭环。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-IRS-00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1个</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-IRS-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>系统底层推理基础设施(非业务子系统)：部署本地大模型并提供推理调用，使全系统 AI 推理不依赖外部公有云。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-IRS-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>本地大模型部署（底座推理能力提供者）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>在私有化环境中部署本地大模型，完成模型加载与服务实例化，对外提供统一推理调用接口。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OCC-00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OCC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9个</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-001~009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>全链路指挥大脑：构建「目标识别→数据分析与情报→作战编排→效果评估」作战闭环，并承担内容资源统一管理(唯一权威源)；基于 DC 采集的原始舆情/传播数据（经 II-13）与 IRS 推理产出作战方案，在本子系统内完成数据分析与情报研判（V3.3 起由 DC 移入），以作战编排直接编排 MC 中智能体节点与自动化脚本节点形成执行流程落地。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OCC-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标档案与状态管理（目标数据管家）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-001(实体)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>识别舆情事件目标要素并建档为数据对象，支持建档、属性修改、状态流转与删除；目标即数据，可随事件演进而更新；本期以人工识别为主、系统提供数据维护支撑。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OCC-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>数据分析与情报（情报分析大脑）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-002~005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>V3.3 起由 DC 移入。对 DC 采集与 ETL 加工的数据（经 II-13）进行分析，提供从群体到个体的下钻筛选、关系图谱与图查询、实体检索与全维度档案、文本智能分析能力，支撑目标识别与内容研判；分析产出供 M-OCC-01 目标识别融合，并经 II-15 反向驱动 DC 情报回注采集（R-DC-007）。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OCC-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标关联网络（目标关系图谱）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-001(图结构)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标之间建立关联关系（如一个事件主体关联多个传播源头、一个干预目标关联多个薄弱点），形成目标关系网络，支持关系网络查询。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OCC-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>作战方案规划（作战参谋）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-006(决策)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>根据目标档案中的干预切入点匹配干预策略，生成具体的作业方案（含内容/账号/时间/节奏）；本期以人工匹配为主。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OCC-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>编排执行引擎（编排执行引擎）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-006(建模+运行)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>将作业方案编排为执行流程：以 MC 中智能体节点/自动化脚本节点为编排实体，按内容/账号/时间/节奏组织节点前后序/并行/分支关系形成可执行流程图；编排落地后由 MC 统一执行网关收口，节点失败按定义回滚/跳过/转人工。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OCC-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>效果评估（作战复盘官）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>完成单轮干预成效统计、舆论走势修正、策略迭代反馈与作业复盘，支持中短期与长期效果评估；数据来源于 DC 采集分析结果与 MC 可观测性作业数据，不自行重复采集。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OCC-07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>舆论作业策略库（策略资产库）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>搭建并迭代多语种/多场景/多风格舆论作业策略库，为作战提供可复用、可演进的策略资产。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OCC-08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>内容主数据与排期（内容资源权威源）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-009(资产+调度)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>唯一维护内容主数据(原始素材/分类/审核状态/来源)，content_id 全局唯一引用；管理素材分类与平台适配；按素材/账号/时间制定发布排期；向各使用方主动分发 content_id。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M-OCC-09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>内容审核与敏感词风控（内容合规守门人）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-009(合规)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>发布前对内容进行审核与敏感词检测；敏感词命中拦截并标记待人工复核；素材上传失败时支持断点续传。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>层级</x:t>
+  </x:si>
+  <x:si>
+    <x:t>编号</x:t>
+  </x:si>
+  <x:si>
+    <x:t>名称</x:t>
+  </x:si>
+  <x:si>
+    <x:t>关键能力点（功能）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>来源依据</x:t>
+  </x:si>
+  <x:si>
+    <x:t>备注</x:t>
+  </x:si>
+  <x:si>
+    <x:t>①子系统</x:t>
+  </x:si>
+  <x:si>
+    <x:t>数据爬取子系统</x:t>
+  </x:si>
+  <x:si>
+    <x:t>—</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS §引言/DC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>V3.3：原「数据分析与情报」(R-DC-007~010) 已移至 OCC 子系统（重编号 R-OCC-002~005），原 R-DC-011/012 情报回注与目标扩散顺延为 R-DC-007/008，DC 需求连续编号 R-DC-001~008；共 4 模块。原独立采集监控告警模块已删除——系统级监控收口至 OM（R-OM-001），DC 采集健康度指标经 II-04 上报 OM。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>②模块</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-01-01 采集任务池与多来源接入；F-DC-01-02 入池目标级去重；F-DC-01-03 调度队列分发；F-DC-01-04 配额限流</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-DC-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-DC-003，任务去重、调度分发与配额限流是调度大脑的三类紧耦合关注点（配额依赖资源水位、去重避免重复采），故合并为一模块；采集执行与策略自优化另列 M-DC-02。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>③功能</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-01-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>采集任务池与多来源接入</x:t>
+  </x:si>
+  <x:si>
+    <x:t>接收人工（REST/文件）、情报回注（F-DC-04-01，来自 OCC 分析经 II-15）等多来源注入的采集任务，统一落入任务池。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REST API 批量注入；CSV/Excel 导入；情报回注回调注入；task_pool 结构</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-01-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>入池目标级去重</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务入池时基于 Redis 对 URL 与任务做目标级去重、调度队列与分布式锁；命中已采集目标转 recheck。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标规范化(URL/账号/话题/时间/策略)；Redis 调度队列+分布式锁；命中转 recheck</x:t>
+  </x:si>
+  <x:si>
+    <x:t>支撑 II-15 情报回注去重</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-01-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>调度队列分发</x:t>
+  </x:si>
+  <x:si>
+    <x:t>消费任务池，按优先级从调度队列批量领取任务，经 Kafka 分发到爬虫 Pod 执行。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redis ZSet 优先级队列；Kafka 分发；分布式调度</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-01-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>配额限流</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对采集范围、频率、并发设配额上限；基于账号池/IP 池水位动态调节消费并发，超限自动限流。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>范围/频率/并发配额上限；水位校验；动态并发调节；超限自动限流</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务队列积压时告警</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-02-01 多平台采集适配；F-DC-02-02 采集手段切换与容错；F-DC-02-03 代理与维护账号应用；F-DC-02-04 代理 IP 池管理；F-DC-02-05 采集策略自优化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-DC-001,004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-DC-001 的『采集执行』与 R-DC-003 的『调度分发』是两种关注点（执行器 vs 调度大脑），故拆出；R-DC-002 代理池管理是采集执行的网络出口（执行器直接消费代理），紧耦合故内聚进本模块；R-DC-004 策略自优化是执行器的学习闭环能力。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-02-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多平台采集适配</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-DC-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>各平台采集适配器，按平台采用不同手段采集推荐/人物/Reels 等数据。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>逆向采集(IG/TikTok/FB/X)；官方 API；模拟点击；网页解析</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-DC-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 EI-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-02-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>采集手段切换与容错</x:t>
+  </x:si>
+  <x:si>
+    <x:t>逆向接口失效或改版时告警并切换备用采集方式；API 限流按限额退避重试；账号被封自动切换备用账号。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>手段可切换；限流退避重试；被封自动切换备用账号</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-02-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>代理与维护账号应用</x:t>
+  </x:si>
+  <x:si>
+    <x:t>采集过程使用代理 IP 与维护账号（来自 II-01），应对平台访问限制。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>采集绑定代理 IP；使用维护账号；应对访问限制</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-02-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>代理 IP 池管理</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-DC-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 VPS 代理链路，按平台与地区分配代理 IP 并定时轮换，进行可用性检测与失效剔除；全失效时告警暂停受影响采集。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按平台/地区分配；定时轮换；可用性检测；失效剔除；全失效告警暂停</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-DC-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 EI-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-02-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>采集策略自优化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-DC-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基于历史采集指标（封禁率/成功率/反爬升级信号/各手段有效率）对采集手段优先级、请求频率与并发、代理与账号选择策略主动调整，随平台反爬强度自适应演进；指标不足或波动过大时维持上一稳定策略并告警。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>手段优先级排序；频率/并发调节；代理账号选择优化；指标不足维持稳定告警</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-DC-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>主动学习闭环，区别于 F-DC-02-02 被动切换</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-03-01 分布式 ETL 加工；F-DC-03-02 多模型持久化存储</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-DC-005,006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-DC-005 清洗加工与 R-DC-006 多模型存储，清洗与存储是 ETL 流水线的前后两环（清洗产干净数据、存储按特征落库），紧耦合故合并。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-03-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>分布式 ETL 加工</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-DC-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基于 Spark/MapReduce 分布式批处理完成清洗、字段提取、格式标准化、去重与关联；节点失败自动重试或转移，数据格式异常时隔离坏数据并记录。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Spark/MapReduce；清洗/提取/标准化/去重/关联；失败重试转移；坏数据隔离记录</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-DC-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 II-05 Kafka 总线</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-03-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多模型持久化存储</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-DC-006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>将清洗后结构化数据按特征持久化：明细入 HBase 列式库、元数据/索引入关系库、关系数据入图库；写入失败时数据进入重试队列。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HBase(列式明细)；PG/MySQL(元数据索引)；图数据库(关系数据)；写入失败重试队列</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-DC-006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DR-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-04-01 情报回注采集；F-DC-04-02 目标扩散采集</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-DC-007,008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-DC-007 情报回注与 R-DC-008 目标扩散，是 DC 从单向采集管道升级为情报驱动闭环的关键；回注入池经 M-DC-01 同一去重与配额约束。原「数据分析与情报」(R-DC-007~010) V3.3 起移至 OCC 子系统（重编号 R-OCC-002~005），本模块顺延为 M-DC-04。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-04-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>情报回注采集</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-DC-007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>将 OCC 分析产出的高价值目标/关联实体/传播节点按规则自动或经人工确认生成定向采集任务回注任务池，经目标级去重（命中已采集转 recheck）；高扩散/批量/敏感回注经人工确认闸门；全程审计。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>情报→任务自动/人工回注；目标级去重转 recheck；人工确认闸门；全程审计</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-DC-007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>跨子系统回注接口 II-15（OCC 分析→DC 任务池）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-DC-04-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标扩散采集</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-DC-008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>以已采集目标为起点按关系类型(关注/粉丝/互动/转发链/评论链)与扩散层数做 BFS 图扩展式采集，每层新节点经去重生成新任务，受配额与层数上限约束，新目标回流后可再次触发回注形成迭代扩散。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按关系+层数 BFS 扩散；新节点去重生成任务；层数/节点数/总数上限；迭代扩散回流；超限停止告警</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-DC-008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>受 R-DC-003 配额约束；区别于 OCC 扩散趋势预判(本期暂不实现)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多设备矩阵自动化群控子系统</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS §引言/MC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>新 SRS V3.2 将 MC 需求从 R-MC-001~008 扩展为 R-MC-001~014：执行网关(R-MC-005)与双执行模式(R-MC-006)拆为两个独立需求；账号资源管理从 1 模块拆为 3 模块（主数据 R-MC-011/分层分组 R-MC-012/绑定迁移 R-MC-013）；自动化编排(R-MC-008)与养号(R-MC-009)拆为两模块；共 14 模块。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-01-01 移动端终端接入与台账；F-MC-01-02 浏览器 Profile 创建与 CDP 接入；F-MC-01-03 终端分组与标签；F-MC-01-04 终端批量操作</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-001 执行终端接入与管理；R-MC-001 含『终端作为资源进入系统』『让终端像真人且互不关联(R-MC-002)』『终端风控分级与代理绑定(R-MC-003)』三类异构关注点，故拆 3 模块，本模块聚焦终端接入与台账。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-01-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>移动端终端接入与台账</x:t>
+  </x:si>
+  <x:si>
+    <x:t>移动端 Agent 启动后注册并建立长连接，记录设备类型(真机/云手机/ARM 板卡/虚拟化真机)、版本、型号、分组与标签，形成执行终端台账。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agent 注册+长连接；设备类型区分虚拟/实体；台账记录</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 II-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-01-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>浏览器 Profile 创建与 CDP 接入</x:t>
+  </x:si>
+  <x:si>
+    <x:t>经商用指纹浏览器 API 创建浏览器 Profile（下发指纹模板、代理、分组、标签），商用产品返回 Profile 标识与调试端口；记录 Profile 标识、内核版本、调试端口、分组与标签。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>调用商用 API 创建 Profile；指纹模板/代理下发；返回调试端口(CDP)；记录 Profile 台账</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-001；CON-12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 EI-06 指纹浏览器服务接口</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-01-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>终端分组与标签</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按业务目标、平台、地区等维度对执行终端分组与打标，支撑任务调度按分组选终端。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多维度分组；标签管理；按分组选终端</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-01-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>终端批量操作</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对终端集合批量操作：移动端批量安装/卸载 App、重启、截图；浏览器 Profile 批量创建/启动/关闭/截图；经对象存储临时链接上传下载。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>移动端批量(安装/卸载/重启/截图)；Profile 批量(创建/启动/关闭/截图)；对象存储临时链接</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 EI-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-02-01 浏览器 Profile 指纹固化；F-MC-02-02 移动端设备指纹管理；F-MC-02-03 终端间环境隔离</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-002 终端身份与环境隔离；与 R-MC-001 接入台账、R-MC-003 风控分级是不同关注点；指纹固化是『让终端像真人』的核心。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-02-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>浏览器 Profile 指纹固化（经商用 API）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>经商用指纹浏览器 API 配置 Profile 指纹模板（Canvas/WebGL/字体/时区/Audio/UA 等 20+ 维），由商用产品生成并固化指纹，使 Profile 长期呈现一致的设备身份；一 Profile 对应一套固化指纹与一账号身份。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20+ 维指纹模板经 API 下发；商用产品生成固化；指纹长期一致；一 Profile 一身份</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-002；CON-12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>指纹生成与固化由商用产品负责</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-02-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>移动端设备指纹管理</x:t>
+  </x:si>
+  <x:si>
+    <x:t>管理真机/云手机/ARM 板卡/虚拟化真机等移动端设备的硬件与软件指纹，支持按需配置。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>移动端硬件/软件指纹管理；按需配置</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-02-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>终端间环境隔离</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对终端间指纹、网络、账号、Cookie/缓存相互隔离；浏览器 Profile 间 Cookie/LocalStorage/缓存独立隔离。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>指纹/网络/账号/Cookie 隔离；Profile 间独立隔离</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-03-01 终端状态与指标监控；F-MC-03-02 设备风控分级；F-MC-03-03 风控信号识别与规避；F-MC-03-04 代理分配与固定绑定</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-003 终端风控分级与代理绑定；风控分级、风控信号规避与代理绑定共同决定『终端能否安全承载作业』，紧耦合故合并。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-03-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>终端状态与指标监控</x:t>
+  </x:si>
+  <x:si>
+    <x:t>持续采集并监控移动端在线/离线状态、电量、CPU、内存、存储、网络，以及浏览器 Profile 运行状态与资源占用。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>移动端多指标监控；Profile 运行状态监控</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-03-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>设备风控分级</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按指纹真实度对终端风控分级：真机与 ARM 板卡(高)、虚拟化真机(中高)、云手机与浏览器 Profile(中)；养号等敏感场景优先选用高真实度终端。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按指纹真实度分级；养号优先高真实度终端</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-003；CON-09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-03-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>风控信号识别与规避</x:t>
+  </x:si>
+  <x:si>
+    <x:t>识别平台风控信号并采取规避与应对策略（覆盖移动端与桌面端），风控信号持续触发时降级或暂停该终端任务。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>风控信号识别；规避策略；持续触发降级/暂停</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-03-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>代理分配与固定绑定</x:t>
+  </x:si>
+  <x:si>
+    <x:t>为每个执行终端/Profile 分配独立代理 IP 并固定绑定（一终端/Profile 一 IP），实现网络环境隔离；代理默认固定，仅失效时切换并重新固定。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>一终端一 IP；代理固定绑定；失效时切换重新固定</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-04-01 移动端 WebRTC 远控；F-MC-04-02 桌面端商用 API 画面远控；F-MC-04-03 多终端宫格监控；F-MC-04-04 剪贴板双向同步</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-004 远程控制；远控通道与任务执行通道相互分离（CON-07）。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-04-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>移动端 WebRTC 远控</x:t>
+  </x:si>
+  <x:si>
+    <x:t>移动端屏幕画面基于 WebRTC 传输，鼠标键盘事件映射为触摸/点击/滑动/输入及返回/Home/多任务键；支持截图与录屏；弱网自动降帧。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WebRTC 画面传输；事件映射；截图录屏；端到端≤300ms；弱网降帧</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-004；NR-P-01/05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 II-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-04-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>桌面端商用 API 画面远控</x:t>
+  </x:si>
+  <x:si>
+    <x:t>桌面端指纹浏览器 Profile 经商用产品 API 获取页面/窗口画面预览流；鼠标点击与键盘输入经 CDP 注入为页面事件；远控通道与任务执行通道相互分离。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>商用 API 画面预览流；CDP 注入页面事件；远控与执行通道分离</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 EI-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-04-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多终端宫格监控</x:t>
+  </x:si>
+  <x:si>
+    <x:t>以低码率同屏预览多台终端，供监控人员宫格监控。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>低码率宫格同屏预览</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-04-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>剪贴板双向同步</x:t>
+  </x:si>
+  <x:si>
+    <x:t>剪贴板在操作端与终端间双向同步。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-05-01 动作收口与转发；F-MC-05-02 动作鉴权；F-MC-05-03 动作记录与上报；F-MC-05-04 异常熔断；F-MC-05-05 控制通道适配</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-005，是 MC 的核心枢纽；动作收口（CON-07）的落地；与 R-MC-006 双执行模式是『收口通道』与『执行引擎』两类不同职责，新 SRS 拆为两个独立需求。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-05-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>动作收口与转发</x:t>
+  </x:si>
+  <x:si>
+    <x:t>所有执行终端动作（移动端与桌面端）均经统一执行网关落地转发，禁止任何子系统或 Agent 绕过。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>动作唯一收口；禁止绕过；转发落地</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-005；CON-07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 II-07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-05-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>动作鉴权</x:t>
+  </x:si>
+  <x:si>
+    <x:t>执行网关对动作鉴权，校验动作来源与目标终端的合法性。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>动作来源校验；目标合法性校验</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-05-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>动作记录与上报</x:t>
+  </x:si>
+  <x:si>
+    <x:t>执行网关对动作记录，写入动作日志并全量上报运维监控子系统。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>动作日志写入；全量上报 OM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 II-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-05-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>异常熔断</x:t>
+  </x:si>
+  <x:si>
+    <x:t>执行网关对异常动作熔断，在检测到风控信号或异常频率时停止后续动作；网关过载时按优先级限流。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>风控信号/异常频率熔断；过载优先级限流</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-05-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>控制通道适配</x:t>
+  </x:si>
+  <x:si>
+    <x:t>移动端终端采用 ADB、无障碍服务通道，桌面端 Profile 采用 CDP 通道；控制通道对上层透明。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>移动端 ADB/无障碍；桌面端 CDP；对上层透明</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-06-01 脚本模式执行引擎；F-MC-06-02 智能体模式执行引擎；F-MC-06-03 三类执行目标</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-006；脚本模式与智能体模式是两种决策驱动的执行引擎，动作落地均经 R-MC-005 网关；推理执行分离（CON-10）。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-06-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>脚本模式执行引擎</x:t>
+  </x:si>
+  <x:si>
+    <x:t>由预先编写的固定流程驱动终端动作，适用于流程确定、高频、批量作业。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>固定流程驱动；适配移动端与桌面端</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-006；CON-08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-06-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体模式执行引擎</x:t>
+  </x:si>
+  <x:si>
+    <x:t>由终端 Agent 调用 IRS 本地大模型进行视觉推理与规划自主决策动作；推理不经网关，产出的动作指令再经网关落地。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>大模型视觉推理决策；推理不经网关；动作经网关落地</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-006；CON-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 EI-05/II-08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-06-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>三类执行目标</x:t>
+  </x:si>
+  <x:si>
+    <x:t>支撑群控(多台终端同步控制统一投放)、养号(认知作战账号经 ADB/无障碍、爬虫账号经 CDP，拟人化节奏由 R-MC-009 内置)、内容投放(下发发布素材到目标账号)三类执行目标。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>群控；养号(移动端 ADB/桌面端 CDP)；内容投放</x:t>
+  </x:si>
+  <x:si>
+    <x:t>养号节奏见 R-MC-009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-07-01 任务创建与实例化；F-MC-07-02 多任务类型；F-MC-07-03 任务状态机流转；F-MC-07-04 失败重试与超时配置；F-MC-07-05 计划任务与定时调度</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-007 任务管理。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-07-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务创建与实例化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按任务定义选择设备或设备组，生成任务实例并入消息队列，由调度器分发到设备 Agent 执行。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务定义→实例化→入队→分发</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-07-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多任务类型</x:t>
+  </x:si>
+  <x:si>
+    <x:t>支持 App 安装启动、文件分发、内容发布、截图、数据采集、自动化脚本、设备巡检、账号状态检查等任务类型。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>八类任务类型</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-07-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务状态机流转</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务在待执行/排队中/执行中/成功/失败/已取消/超时/部分成功等状态间流转。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>八态状态机流转</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-07-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>失败重试与超时配置</x:t>
+  </x:si>
+  <x:si>
+    <x:t>支持失败重试、重试次数与超时配置；队列积压时按优先级调度并告警。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>失败重试；重试次数/超时可配；优先级调度</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务入队到分发≤2s NR-P-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-07-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>计划任务与定时调度</x:t>
+  </x:si>
+  <x:si>
+    <x:t>支持一次性、每日、每周与自定义 Cron 计划任务，支持最大并发数与任务优先级控制。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cron 定时(一次性/每日/每周/自定义)；最大并发；优先级</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-08-01 模板化任务（第一阶段）；F-MC-08-02 可视化工作流编排（第二阶段）；F-MC-08-03 脚本开发与调试（第三阶段）；F-MC-08-04 模拟点击自动化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-008 自动化编排能力；与 R-MC-009 账号操作编排与养号是『通用编排能力』与『账号域编排』两类，新 SRS 拆为两个需求。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-08-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>模板化任务（第一阶段）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提供打开 App/等待页面/点击/输入/上传文件/截图/返回/滑动/关闭 App/设备巡检/App 状态检测等模板化任务。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>十二类模板化任务</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-08-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>可视化工作流编排（第二阶段）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>节点包括开始/设备选择/启动 App/等待/点击/输入/滑动/截图/文件上传/条件判断/循环/HTTP 请求/日志/审批/结束等，可视化编排。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>十五类节点；可视化编排</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-08-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>脚本开发与调试（第三阶段）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>支持脚本编辑、调试设备、执行日志、截图回放与版本管理；脚本运行于沙箱并配置权限白名单。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>脚本编辑/调试/回放/版本管理；沙箱+权限白名单</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-008；NR-S-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-08-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>模拟点击自动化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>针对 TikTok/Facebook 等平台实现模拟点击自动化。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标平台模拟点击</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-09-01 养号自动化与拟人化节奏；F-MC-09-02 账号-终端-代理绑定自动化；F-MC-09-03 终端侧登录状态维护；F-MC-09-04 状态变更联动</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-009；账号操作依赖 R-MC-008 编排产出动作，但养号拟人化节奏是账号域专属策略，新 SRS 拆为独立需求；动作均经 R-MC-005 网关落地。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-09-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>养号自动化与拟人化节奏</x:t>
+  </x:si>
+  <x:si>
+    <x:t>养号动作(发帖/关注/浏览)由本功能编排并经执行网关落地（认知作战账号经 ADB/无障碍、爬虫账号经 CDP）；拟人化节奏由本功能内置（注入随机浏览/停留/互动、打散时间间隔与频率），不依赖蜂群智能体。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>养号经网关落地；拟人化节奏内置；认知作战账号 ADB/爬虫账号 CDP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-09-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>账号-终端-代理绑定自动化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按差异化绑定规则绑定：真机/云手机/虚拟化真机「一设备一账号一 IP」(未解绑前不可再绑)；指纹浏览器 Profile「一 Profile 一账号一 IP」(实例可多开)；联动代理绑定记录。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>一设备一账号一 IP；一 Profile 一账号一 IP；未解绑不可再绑；联动代理绑定</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-009；CON-13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-09-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>终端侧登录状态维护</x:t>
+  </x:si>
+  <x:si>
+    <x:t>记录账号在终端上的登录状态及其变化。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>登录状态记录与变化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-09-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>状态变更联动</x:t>
+  </x:si>
+  <x:si>
+    <x:t>账号状态变更(封禁/受限)时停止养号任务并解绑。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>状态变更停止任务解绑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-10-01 动作留痕；F-MC-10-02 任务日志与截图回传；F-MC-10-03 异常告警；F-MC-10-04 审计日志；F-MC-10-05 任务完成率统计；F-MC-10-06 内容触达与互动统计；F-MC-10-07 账号健康度统计；F-MC-10-08 任务复盘归因；F-MC-10-09 效果回调回传上游</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-010，动作留痕与作业统计同源，避免重复采集原始动作数据；多维统计按任务/内容效果/账号健康三维度拆功能。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-10-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>动作留痕</x:t>
+  </x:si>
+  <x:si>
+    <x:t>每一个终端动作(点击/输入/安装/发布等)均留痕，记录时间、终端、账号与结果。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>动作留痕；记录时间/终端/账号/结果</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-10-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务日志与截图回传</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agent 回传任务执行日志与关键步骤截图。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务日志回传；关键步骤截图</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-10-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>异常告警</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务失败、终端掉线、账号异常等异常事件触发告警通知。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>异常事件告警通知</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-10-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>审计日志</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对用户与系统操作记录审计日志，记录谁在何时对哪台终端或账号做了什么。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>操作审计；可追溯</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-010；NR-S-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-10-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务完成率统计</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基于动作日志与任务日志统计蜂群作业的任务完成率、成功率、失败率、平均耗时等任务维度指标。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务完成率/成功率/失败率/平均耗时；基于动作日志与任务日志</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-10-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>内容触达与互动统计</x:t>
+  </x:si>
+  <x:si>
+    <x:t>统计内容投放的触达量、曝光、互动（点赞/评论/转发）等内容效果维度指标。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>触达量/曝光/互动(点赞/评论/转发)；内容效果维度</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-10-07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>账号健康度统计</x:t>
+  </x:si>
+  <x:si>
+    <x:t>统计智能体账号的健康度指标（活跃度、风控触发频次、封禁率、作业稳定性等）。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>活跃度/风控触发频次/封禁率/作业稳定性；账号健康度维度</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-10-08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务复盘归因</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对失败任务、异常账号、低效作业进行归因分析。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>归因分析复盘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-10-09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>效果回调回传上游</x:t>
+  </x:si>
+  <x:si>
+    <x:t>将投送效果数据通过回调机制联动回传至 OCC，供效果评估闭环使用。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>效果数据回调回传 OCC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 II-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-11-01 账号主数据维护；F-MC-11-02 注册方式与流程编排；F-MC-11-03 注册结果判定与状态落地；F-MC-11-04 账号验证与风险识别；F-MC-11-05 账号生命周期状态机；F-MC-11-06 账号状态变更事件广播</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-011；账号实体主数据 CRUD 与智能体账号组织(R-MC-012 分层分组、R-MC-013 绑定迁移)是不同关注点，新 SRS 拆为三个需求，本模块聚焦主数据维护。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-11-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>账号主数据维护</x:t>
+  </x:si>
+  <x:si>
+    <x:t>唯一维护账号主数据(凭据/平台/全局状态/生命周期/风险评估/账号分类)，凭据加密存储；其它子系统仅引用 account_id 不复制主数据。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>主数据唯一维护；凭据加密不落明文；使用方仅引用 account_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-011；NR-S-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>权威源；对接 II-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-11-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>注册方式与流程编排</x:t>
+  </x:si>
+  <x:si>
+    <x:t>承担注册入口，支持邮箱/手机接码/虚拟号注册方式路由；编排注册流程（填写注册信息、接收验证码、完成登录探测），注册动作经统一执行网关执行（爬虫账号 CDP/认知作战账号 ADB）。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>邮箱/接码/虚拟号注册方式路由；注册流程编排；注册动作经执行网关</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 EI-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-11-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>注册结果判定与状态落地</x:t>
+  </x:si>
+  <x:si>
+    <x:t>接收执行网关回传的注册执行结果，判定账号状态与风险等级，落地账号主数据（凭据加密存储），生成 account_id。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>注册结果判定；状态与风险等级落地；凭据加密存储；生成 account_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-11-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>账号验证与风险识别</x:t>
+  </x:si>
+  <x:si>
+    <x:t>通过登录探测与状态识别检测可用性，识别封禁/限制/需验证等风险点，输出风险等级。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>登录探测；状态识别；风险等级输出</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-11-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>账号生命周期状态机</x:t>
+  </x:si>
+  <x:si>
+    <x:t>账号在待登录/正常/受限/需验证/封禁/归档等状态间流转，由本子系统判定与维护。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>六态生命周期状态机</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-11-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>账号状态变更事件广播</x:t>
+  </x:si>
+  <x:si>
+    <x:t>账号状态变更(封禁/受限等)经事件总线广播 account.status.changed 事件，使用方订阅后立即响应，保证被封账号全网即时失效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>account.status.changed 事件广播；使用方订阅即时响应</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 II-01a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-12-01 智能体账号分层分组；F-MC-12-02 智能体账号作业生命周期</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-012；账号组织（分层分组+作业生命周期）与账号主数据 CRUD 是不同关注点，新 SRS 拆为独立需求。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-12-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体账号分层分组</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对智能体账号按业务目标/平台/地区/风险等级等维度分层分组，形成可控账号层级结构。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多维度分层分组</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-12-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体账号作业生命周期</x:t>
+  </x:si>
+  <x:si>
+    <x:t>管理智能体账号作业生命周期(待激活/活跃/休眠/受限/封禁/回收)，支持自动与人工流转。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>六态作业生命周期；自动与人工流转</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-13-01 智能体-账号绑定维护；F-MC-13-02 四元绑定关系维护；F-MC-13-03 迁移资产抽取；F-MC-13-04 迁移目标账号校验；F-MC-13-05 继承写入与绑定切换</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-013；绑定关系维护与封号资产迁移是账号资源的『关联治理』关注点，与主数据 CRUD、分层分组分离，新 SRS 拆为独立需求。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-13-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体-账号绑定维护</x:t>
+  </x:si>
+  <x:si>
+    <x:t>记录并维护 agent_id↔account_id 严格 1:1 绑定关系；agent_id 由 SWM 分配经 II-14 同步至本子系统持存。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>agent_id↔account_id 严格 1:1；记录维护</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 II-14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-13-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>四元绑定关系维护</x:t>
+  </x:si>
+  <x:si>
+    <x:t>记录并维护 agent_id↔account_id↔终端↔代理 IP 四元绑定关系，形成 1:1:1:1 作战单元。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>四元绑定；1:1:1:1 作战单元</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-13-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>迁移资产抽取</x:t>
+  </x:si>
+  <x:si>
+    <x:t>从被封禁账号绑定的原 agent_id 智能体定义中抽取待迁移资产：人设标签、提示词版本、记忆数据。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>抽取人设标签/提示词版本/记忆数据；资产完整性校验</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-13-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>迁移目标账号校验</x:t>
+  </x:si>
+  <x:si>
+    <x:t>校验目标账号（新注册且未绑定 agent_id）是否满足迁移条件：未绑定、状态正常、满足账号-终端绑定规则；不满足则拒绝并提示。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标账号未绑定校验；账号状态正常校验；终端绑定规则校验；不满足拒绝提示</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-13-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>继承写入与绑定切换</x:t>
+  </x:si>
+  <x:si>
+    <x:t>将抽取的资产整体继承写入目标账号的新 agent_id，激活新绑定；旧 agent_id↔旧账号解绑并休眠，保证人格连贯性。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>资产整体继承写入新 agent_id；新绑定激活；旧绑定解绑休眠；人格连贯</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-14-01 智能体定义接收与持存；F-MC-14-02 人设一致性校验；F-MC-14-03 智能体定义调用执行；F-MC-14-04 智能体定义更新生效；F-MC-14-05 OCC 编排智能体节点来源</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-MC-014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-MC-014，智能体执行宿主职责；确立 SWM 为定义与记忆中心、MC 为执行宿主的分工。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-14-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体定义接收与持存</x:t>
+  </x:si>
+  <x:si>
+    <x:t>以 agent_id 为主键接收 SWM 同步的智能体定义(人设标签/提示词/记忆/作业策略)并持存，作为任务执行调用依据。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>agent_id 主键接收持存</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-14-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>人设一致性校验</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体模式下任务执行前校验「当前 account_id 绑定的人设标签」与「agent_id 定义中的人设标签」是否一致，一致方可调用并经网关落地，不一致拒绝执行并告警。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>执行前人设一致性校验；不一致拒绝并告警</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-14-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体定义调用执行</x:t>
+  </x:si>
+  <x:si>
+    <x:t>任务执行时按智能体定义中的提示词/记忆/作业策略调用 IRS 本地大模型视觉推理，产出动作指令再经执行网关落地。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按定义调用 IRS 推理；动作经网关落地</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-14-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体定义更新生效</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体定义更新时(SWM 以同一 agent_id 重新同步)更新持存版本，保证执行使用最新定义。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>更新持存版本；使用最新定义</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-MC-14-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OCC 编排智能体节点来源</x:t>
+  </x:si>
+  <x:si>
+    <x:t>作为 OCC 作战编排的执行节点来源——编排中智能体节点以 agent_id 引用本子系统持存的智能体。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>以 agent_id 供 OCC 编排引用</x:t>
+  </x:si>
+  <x:si>
+    <x:t>运维监控子系统</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS §引言/OM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OM-001(日志与指标汇聚)含日志、指标两种异构数据管道，拆 2 模块；R-OM-002(告警与运维)含告警引擎、可视化看板、运维作业三类关注点，看板与作业合并故拆 2 模块。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OM-01-01 日志采集与汇聚；F-OM-01-02 全文检索</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OM-001(日志)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OM-001 的日志(半结构化文本/全文检索/日志库)与指标(时序数值/时序 DB)是两种异构数据管道，故拆。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OM-01-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>日志采集与汇聚</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OM-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>通过日志采集 Agent 将各子系统日志汇聚至统一日志库。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>日志采集 Agent；统一日志库汇聚</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OM-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 II-04/II-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OM-01-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>全文检索</x:t>
+  </x:si>
+  <x:si>
+    <x:t>支持对统一日志库的全文检索；近 7 日日志检索响应≤3 秒。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>全文检索；检索≤3 秒</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OM-001；NR-P-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OM-02-01 指标采集；F-OM-02-02 时序数据存储</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OM-001(指标)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OM-001 的指标采集与时序存储是独立于日志的关注点。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OM-02-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>指标采集</x:t>
+  </x:si>
+  <x:si>
+    <x:t>通过指标采集器采集设备在线率/任务成功率/爬虫吞吐量/队列积压等系统运行指标。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多维指标采集器</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OM-02-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>时序数据存储</x:t>
+  </x:si>
+  <x:si>
+    <x:t>将采集的指标形成时序数据存储，供告警与看板消费。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>时序数据库存储</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OM-03-01 阈值与异常检测告警；F-OM-03-02 告警风暴聚合去重</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OM-002(告警)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OM-002 的告警引擎(监测→告警)与可视化/运维作业是不同职责域，故拆。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OM-03-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>阈值与异常检测告警</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OM-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>支持阈值告警与异常检测告警，通过多渠道通知。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>阈值/异常检测告警；多渠道通知</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OM-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OM-03-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>告警风暴聚合去重</x:t>
+  </x:si>
+  <x:si>
+    <x:t>告警风暴时按规则聚合去重，避免告警轰炸；通知渠道失效时降级为备用渠道。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>告警聚合去重；备用渠道降级</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OM-04-01 可视化看板；F-OM-04-02 常态化运维操作</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OM-002(看板+运维)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OM-002 的可视化看板与运维作业均面向人工作业，紧耦合故合并。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OM-04-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>可视化看板</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提供总览/设备/任务/爬虫/异常等多维可视化看板；数据加载超时时降级展示缓存。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多维可视化看板；缓存降级展示</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OM-04-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>常态化运维操作</x:t>
+  </x:si>
+  <x:si>
+    <x:t>支持日志查询、故障定位、巡检与容量观测等常态化运维操作。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>日志查询/故障定位/巡检/容量观测</x:t>
+  </x:si>
+  <x:si>
+    <x:t>公共功能</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS §引言/COM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-COM-001 含认证(AuthN，你是谁)与授权(AuthZ+数据隔离，你能访问什么)两个 IAM 经典异构问题，故拆 2 模块。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-COM-01-01 登录认证；F-COM-01-02 双因素认证；F-COM-01-03 认证令牌签发</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-COM-001(AuthN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-COM-001 的认证(身份验证)与授权(权限决策)是两个经典不同问题，故拆。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-COM-01-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>登录认证</x:t>
+  </x:si>
+  <x:si>
+    <x:t>进行登录认证；登录密码错误超限时锁定账号。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>登录认证；超限锁定</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-COM-001；NR-S-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-COM-01-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>双因素认证</x:t>
+  </x:si>
+  <x:si>
+    <x:t>支持双因素认证；双因素验证失败时拒绝并记录。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>双因素认证；失败拒绝记录</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-COM-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-COM-01-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>认证令牌签发</x:t>
+  </x:si>
+  <x:si>
+    <x:t>认证通过后签发认证令牌，供各子系统统一鉴权。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>令牌签发；统一鉴权</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-COM-02-01 RBAC 权限决策；F-COM-02-02 组织与成员管理；F-COM-02-03 多组织数据隔离</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-COM-001(AuthZ)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>授权(RBAC 决策)与组织数据隔离都决定『数据可见边界』，紧耦合故合并。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-COM-02-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RBAC 权限决策</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基于角色访问控制进行权限决策，角色含超级管理员/运营主管/运营人员/脚本开发者/审核人员/只读观察员等；越权访问拦截并审计。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RBAC 决策；多角色；越权拦截审计</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-COM-02-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>组织与成员管理</x:t>
+  </x:si>
+  <x:si>
+    <x:t>管理组织结构与成员信息。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>组织结构管理；成员管理</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-COM-02-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多组织数据隔离</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对多组织或多租户进行数据隔离，禁止跨组织访问。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多组织/多租户隔离；禁止跨组织访问</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-COM-001；NR-C-01/02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>蜂群智能体子系统</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS §引言/SWM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-SWM-001(提示词与人设管理)含人设标签、提示词模板库、场景适配调用三个异构关注点(元数据/文本资产/运行时决策)，故拆 3 模块；智能体定义组装与同步下发归构建模块(M-SWM-05)，迭代优化决策归评测模块(M-SWM-06)。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-01-01 人设标签绑定；F-SWM-01-02 人设标签体系维护</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-SWM-001(人设)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-SWM-001 的人设标签(元数据体系)与提示词(文本资产)、运行时选择是不同职责域，故拆。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-01-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>人设标签绑定</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-SWM-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>为每个 agent_id 绑定人设标签，标签涵盖身份特征、立场倾向、语言风格、兴趣领域等画像属性。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>人设绑 agent_id；画像属性涵盖</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-SWM-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-01-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>人设标签体系维护</x:t>
+  </x:si>
+  <x:si>
+    <x:t>维护人设标签体系定义；人设标签冲突时提示人工裁定。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>标签体系维护；冲突人工裁定</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-02-01 提示词模板库分类管理；F-SWM-02-02 提示词版本管理；F-SWM-02-03 Playground 试运行调试；F-SWM-02-04 版本输出对比</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-SWM-001(资产)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-SWM-001 的提示词模板库(文本资产)是独立关注点；版本管理横切于人设与提示词。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-02-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提示词模板库分类管理</x:t>
+  </x:si>
+  <x:si>
+    <x:t>建立提示词模板库并按用途、平台、目标进行分类管理。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>模板库；按用途/平台/目标分类</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-02-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提示词版本管理</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对提示词进行版本管理，以 agent_id 为主键索引，支持版本对比、回滚与变更记录；版本回滚失败时告警。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>agent_id 主键版本管理；对比/回滚/变更记录</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-02-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Playground 试运行调试</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提供 Playground 试运行环境，对提示词进行调试与效果验证。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Playground 试运行；效果验证调试</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-02-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>版本输出对比</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对不同版本提示词的输出结果进行对比，支撑迭代优化决策。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>版本输出对比；迭代优化支撑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-03-01 场景适配；F-SWM-03-02 动态调用与指令生成</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-SWM-001(运行时)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-SWM-001 的场景适配与动态调用是运行时决策关注点，与模板库资产管理分离。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-03-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>场景适配</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按作业场景(人设标签/目标受众/当前态势)选择合适模板；模板填充失败时降级为默认模板。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>场景适配模板；填充失败降级默认</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-03-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>动态调用与指令生成</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体作业时动态调用并填充提示词，生成最终作业指令。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>动态调用填充；生成作业指令</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 II-09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-04-01 作业记忆存储；F-SWM-04-02 场景记忆沉淀；F-SWM-04-03 历史记忆复用；F-SWM-04-04 个性化状态延续</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-SWM-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-SWM-002，记忆存储/沉淀/复用/延续是同一记忆对象的生命周期环节，内聚不拆。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-04-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>作业记忆存储</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对智能体作业过程中的关键信息(已完成任务/互动对象/立场表达等)进行记忆存储。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>关键信息记忆存储</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-04-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>场景记忆沉淀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>将重复场景下的经验沉淀为场景记忆，形成可复用行为模式。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>场景经验沉淀为模式</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-04-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>历史记忆复用</x:t>
+  </x:si>
+  <x:si>
+    <x:t>在相似作业中复用历史记忆，提升作业连贯性与效率。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>相似作业复用历史记忆</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-04-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>个性化状态延续</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基于记忆维持智能体个性化状态延续，使其长期行为符合人设且不断演进。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>个性化状态延续；符合人设演进</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-05-01 智能体定义构建；F-SWM-05-02 账号绑定引用；F-SWM-05-03 同步至 MC 持存；F-SWM-05-04 OCC 智能体节点定义来源</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-SWM-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-SWM-003，构建是装配链(编写初值+配置策略+组装+下发)，内聚不拆；吸收 R-SWM-001 中『组装与同步下发』能力作为定义交付出口。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-05-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体定义构建</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按人设标签编写提示词初值与记忆初值并配置作业策略(目标/场景/边界)，组装为完整智能体定义，以全局唯一 agent_id 为标识。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>人设+提示词初值+记忆初值+作业策略；agent_id 标识</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-05-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>账号绑定引用</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体定义与账号严格 1:1 绑定(agent_id↔account_id)，绑定关系由 MC 维护，本子系统构建时引用 account_id。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>agent_id↔account_id 1:1；构建时引用 account_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>绑定关系归 MC R-MC-013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-05-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>同步至 MC 持存</x:t>
+  </x:si>
+  <x:si>
+    <x:t>构建完成的智能体定义经 II-14 同步至 MC 持存，取得持存版本号；定义更新时以同一 agent_id 重新同步。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>经 II-14 同步；取得版本号；更新重同步</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-05-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OCC 智能体节点定义来源</x:t>
+  </x:si>
+  <x:si>
+    <x:t>构建出的智能体定义是 OCC 作战编排中智能体节点的定义来源。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>作为 OCC 编排智能体节点定义来源</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-06-01 有效性评测；F-SWM-06-02 评测数据集管理；F-SWM-06-03 批量跑题执行；F-SWM-06-04 答案对比与打分；F-SWM-06-05 评分汇总与报告；F-SWM-06-06 迭代/淘汰决策与反馈闭环</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-SWM-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-SWM-004。06-01 为线上效果统计(触达/互动/完成率)；06-02~05 为离线数据集评测流程(录入题集→跑题→打分→汇总)，按流程环节拆 4 个功能；一在线一离线互补评估；06-06 综合双轨结论做决策与反馈。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-06-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>有效性评测</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基于 MC 可观测性上报的作业效果数据(触达/互动/任务完成率)评测智能体有效性。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基于 MC 作业效果评测有效性</x:t>
+  </x:si>
+  <x:si>
+    <x:t>数据来自 R-MC-010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-06-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>评测数据集管理</x:t>
+  </x:si>
+  <x:si>
+    <x:t>管理智能体评测用的标准数据集：提示词工程师编辑测试用例集，每条用例含问题、预期答案、评分标准（规则匹配/关键词/LLM 裁判/人工评判）、权重与所属评分维度（稳定性/合规性/人设一致性）；支持数据集创建、用例录入/批量导入/修改/删除与版本管理。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>数据集创建与元信息；用例录入(问题/预期答案/评分标准/权重/维度)；批量导入；用例增删改查；数据集版本管理</x:t>
+  </x:si>
+  <x:si>
+    <x:t>数据集是离线评测的可复现基准</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-06-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>批量跑题执行</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对指定 agent_id 按数据集逐题执行评测：系统将每题问题连同智能体定义（提示词+人设+记忆）交由 IRS 本地大模型推理（不经执行网关），收集智能体的实际回答；支持异步批量执行、进度跟踪与失败重跑。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>逐题调 IRS 推理收集实际回答；推理不经执行网关(CON-10)；异步批量执行；进度跟踪；失败题重跑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 II-08/EI-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-06-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>答案对比与打分</x:t>
+  </x:si>
+  <x:si>
+    <x:t>将跑题收集的实际回答与用例预期答案按评分标准对比打分，支持规则匹配、LLM 裁判（LLM-as-judge）与人工评判三种模式，按用例逐题配置；LLM 裁判置信度低时标记待人工评判。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>规则匹配(精确/关键词)；LLM-as-judge(本地模型裁判)；人工评判；逐题配置评分模式；置信度低转人工</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-06-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>评分汇总与报告</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按评分维度（稳定性/合规性/人设一致性）汇总各维度得分、通过率、人设漂移维度，对比历史基线与上次同题集得分，输出评测报告；报告含质量等级、薄弱用例与改进建议。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>维度得分汇总(稳定性/合规性/人设一致性)；通过率/人设漂移维度；历史基线对比；版本演进对比；评测报告输出</x:t>
+  </x:si>
+  <x:si>
+    <x:t>供 F-SWM-06-06 决策消费</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-SWM-06-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>迭代/淘汰决策与反馈闭环</x:t>
+  </x:si>
+  <x:si>
+    <x:t>综合 F-SWM-06-01 线上有效性统计与 F-SWM-06-05 离线数据集评测报告，对低效定义提出淘汰、对高价值定义提出迭代优化，形成评测决策；反馈至 M-SWM-02（驱动模板迭代）与 M-SWM-05（驱动定义重建）形成闭环。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>综合线上+离线双轨结论；淘汰/迭代决策；反馈 M-SWM-02 模板迭代；反馈 M-SWM-05 定义重建；闭环</x:t>
+  </x:si>
+  <x:si>
+    <x:t>私有化大模型部署</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS §引言/IRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRS 仅一条 FR 且定义为单一基础设施，部署管理与推理服务紧耦合，保持 1 模块不拆（对齐轻量子系统粒度）。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-IRS-01-01 私有化部署与模型加载；F-IRS-01-02 统一推理调用接口；F-IRS-01-03 部署独立性</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-IRS-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-IRS-001，部署加载与推理接口同属本地推理服务，内聚不拆。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-IRS-01-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>私有化部署与模型加载</x:t>
+  </x:si>
+  <x:si>
+    <x:t>在私有化 GPU 算力环境部署本地大模型，完成模型加载与服务实例化；模型加载失败回退上一可用版本。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>私有化部署；模型加载实例化；失败回退</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-IRS-001；CON-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-IRS-01-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>统一推理调用接口</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对外提供统一推理调用接口，供数据爬取/蜂群智能体/舆情作战等子系统调用；算力资源不足时拒绝新请求并排队。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>统一推理接口；供各子系统调用；算力不足排队</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-IRS-01-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>部署独立性</x:t>
+  </x:si>
+  <x:si>
+    <x:t>部署不依赖外部公有云模型服务。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>不依赖公有云</x:t>
+  </x:si>
+  <x:si>
+    <x:t>舆情作战业务子系统</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS §引言/OCC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>V3.3：原 DC「数据分析与情报」(R-DC-007~010) 移入本子系统，重编号为 R-OCC-002~005，原 R-OCC-002~005 顺延为 R-OCC-006~009，OCC 需求连续编号 R-OCC-001~009；共 9 模块。R-OCC-001(目标识别)含目标实体 CRUD 与目标关联网络(图结构)两个异构关注点，拆 2；数据分析与情报(R-OCC-002~005)四项分析能力内聚为 1 模块；R-OCC-006(作战编排)含方案规划与编排执行引擎两类，拆 2；R-OCC-009(内容管理)含主数据排期与审核风控两类，拆 2。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-01-01 目标建档与标识；F-OCC-01-02 目标属性维护；F-OCC-01-03 目标状态生命周期；F-OCC-01-04 目标多维信息融合；F-OCC-01-05 目标变更事件广播</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-001(实体)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-001 的目标实体 CRUD/状态机与目标关联网络(图结构建模)是不同数据范式，故拆。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-01-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标建档与标识</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>每个识别出的目标建档为一条目标数据，赋予全局唯一 target_id。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标建档；全局唯一 target_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-01-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标属性维护</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标档案各属性(事件主体/争议点/画像属性/干预切入点等)支持新增/修改/删除，可随事件演进更新。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>属性增删改；可随事件演进更新</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-01-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标状态生命周期</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标具备状态生命周期(待核实/已确认/已锁定/已处置/已归档)，支持状态流转。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标状态机流转</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-01-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标多维信息融合</x:t>
+  </x:si>
+  <x:si>
+    <x:t>识别过程综合事件主体/传播源头与链路/事件群体账号传播画像/干预切入点与薄弱点，形成完整目标档案；融合本子系统数据分析与情报（M-OCC-02）的产出。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多维信息融合；本期人工识别+系统维护</x:t>
+  </x:si>
+  <x:si>
+    <x:t>依赖 OCC 分析(M-OCC-02)/IRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-01-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标变更事件广播</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标变更经事件总线广播 target.changed 事件，使用方(作战编排/效果评估)订阅响应。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>target.changed 事件广播；使用方订阅</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-02-01 群体-个体下钻筛选；F-OCC-02-02 关系图谱与图查询；F-OCC-02-03 实体检索与档案；F-OCC-02-04 文本智能分析</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-002~005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-OCC-002~005 四项分析需求（V3.3 由 DC R-DC-007~010 移入并重编号），均属分析研判能力域（筛选/图谱/检索/文本），内聚不拆；原始数据经 II-13 从 DC 获取，分析产出供目标识别(M-OCC-01)与情报回注(DC R-DC-007)。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-02-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>群体-个体下钻筛选</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>结合 AI 算法实现从群体到个体的逐层下钻筛选，使分析人员能从大范围群体按特征逐步缩小范围定位目标个体。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AI 算法逐层下钻；群体→个体定位</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>依赖 IRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-02-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>关系图谱与图查询</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基于实体与关联数据绘制关系图谱并支持图查询，对给定实体输出关联拓扑与情报标签形成关联网络；数据量过大时分页或限流。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>关系图谱绘制；图查询；关联拓扑与情报标签；分页/限流</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-02-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>实体检索与档案</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提供基础信息检索（按账号/昵称/标识），并聚合多来源信息形成实体全维度档案；检索超时时降级返回部分结果。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>实体检索；全维度档案；检索超时降级</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-02-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>文本智能分析</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对文本内容结合文本模型（调 IRS 本地大模型）与关键词库进行规则匹配与分类筛选（立场/情感/观点），用于内容研判与目标识别；模型不可用回退关键词规则。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>文本模型+关键词库；规则匹配与分类筛选；降级回退关键词</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 EI-05；模型不可用回退关键词</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-03-01 目标关联关系建模；F-OCC-03-02 关系网络查询</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-001(图结构)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-001 的目标关联是图结构建模(关系类型/网络查询)，与目标实体 CRUD 是不同数据范式，故拆。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-03-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标关联关系建模</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目标之间建立关联关系，形成目标关系网络。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>关联关系建模；关系网络</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-03-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>关系网络查询</x:t>
+  </x:si>
+  <x:si>
+    <x:t>支持对目标关系网络的查询与探索；目标关联断裂时标注断点。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>关系网络查询；断点标注</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-04-01 干预策略匹配；F-OCC-04-02 作业方案生成</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-006(决策)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-006 的方案规划(业务决策域)与编排执行(工作流建模+运行域)是不同职责域，故拆。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-04-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>干预策略匹配</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>根据目标档案中的干预切入点匹配干预策略(本期以人工匹配为主)。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>切入点→策略匹配；本期人工为主</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-04-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>作业方案生成</x:t>
+  </x:si>
+  <x:si>
+    <x:t>生成具体作业方案(含内容/账号/时间/节奏)。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>内容/账号/时间/节奏方案</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-05-01 编排建模；F-OCC-05-02 节点参数填充；F-OCC-05-03 编排落地与执行跟踪</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-006(建模+运行)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-006 的流程编排(DAG 建模)与执行调度(落地跟踪/回滚)紧耦合，合并为编排执行引擎。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-05-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>编排建模</x:t>
+  </x:si>
+  <x:si>
+    <x:t>将作业方案编排为执行流程图（DAG）：以 MC 中智能体节点/自动化脚本节点为编排实体，定义节点间的前后序、并行与分支关系；节点类型后续可扩充。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAG 流程图建模；智能体节点+脚本节点；前后序/并行/分支关系；节点类型可扩充</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-05-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>节点参数填充</x:t>
+  </x:si>
+  <x:si>
+    <x:t>为编排流程图中的各节点填充具体执行参数：智能体节点的 agent_id 引用、脚本节点的通道与目标、内容/账号/时间/节奏等作业参数。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>智能体节点 agent_id 引用；脚本节点通道与目标；内容/账号/时间/节奏参数填充</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-05-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>编排落地与执行跟踪</x:t>
+  </x:si>
+  <x:si>
+    <x:t>编排落地后由 MC 统一执行网关收口所有节点动作；节点执行失败时按编排定义回滚/跳过/转人工。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>经 MC 执行网关落地；失败回滚/跳过/转人工</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-06-01 单轮成效统计；F-OCC-06-02 舆论走势修正评估；F-OCC-06-03 策略迭代反馈；F-OCC-06-04 作业复盘；F-OCC-06-05 中短期与长期效果评估</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-OCC-007，各评估维度同属评估分析能力域，内聚不拆。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-06-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>单轮成效统计</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基于 DC 舆情数据与 MC 作业数据完成单轮干预成效统计(触达/互动/立场变化等)。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DC 舆情+MC 作业数据；成效统计</x:t>
+  </x:si>
+  <x:si>
+    <x:t>数据来自 DC/MC(R-MC-010)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-06-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>舆论走势修正评估</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基于 DC 前后舆情对比对舆论走势进行修正评估。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>前后舆情对比；走势修正</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-06-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>策略迭代反馈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>将评估结果反馈至策略库以迭代优化。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>评估反馈策略库迭代</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-06-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>作业复盘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>结合 MC 作业执行记录进行作业复盘总结经验。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MC 作业记录复盘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-06-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>中短期与长期效果评估</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提供中短期实网绩效评估与长期舆论塑造效果评估接口，实现效果联动。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>中短期绩效+长期塑造效果评估接口</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-07-01 多语种多场景多风格策略库；F-OCC-07-02 策略分类管理与版本控制；F-OCC-07-03 策略迭代优化；F-OCC-07-04 策略场景适配与动态调用</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对应 R-OCC-008，单一策略资产的治理(组织/版本/迭代/适配)内聚不拆。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-07-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多语种多场景多风格策略库</x:t>
+  </x:si>
+  <x:si>
+    <x:t>按多语种/多场景/多风格组织舆论作业策略库。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>多语种/多场景/多风格</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-07-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>策略分类管理与版本控制</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对策略进行分类管理与版本控制。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>分类管理；版本控制</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-07-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>策略迭代优化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>根据作业效果反馈对策略进行迭代优化。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>效果反馈迭代优化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-07-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>策略场景适配与动态调用</x:t>
+  </x:si>
+  <x:si>
+    <x:t>支持策略的场景适配与动态调用。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>场景适配；动态调用</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-08-01 内容主数据维护；F-OCC-08-02 素材分类与平台适配；F-OCC-08-03 发布排期；F-OCC-08-04 内容变更事件与分发</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-009(资产+调度)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-009 的内容主数据(CMS 资产域)与审核风控(合规域)是异构关注点，故拆；排期是主数据的时间调度，归入主数据管理。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-08-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>内容主数据维护</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>唯一维护内容主数据（原始素材、分类、审核状态、来源）的 CRUD；content_id 为全局唯一引用，使用方不复制主数据。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>主数据 CRUD；content_id 全局唯一；使用方不复制主数据</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>权威源主数据 CRUD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-08-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>素材分类与平台适配</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对素材分类管理，支持标签/平台分类与账号适配。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>素材分类；标签/平台分类/账号适配</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-08-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>发布排期</x:t>
+  </x:si>
+  <x:si>
+    <x:t>支持按素材/账号/时间制定定时发布排期；排期冲突时提示调整。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>定时发布排期；冲突提示</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-08-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>内容变更事件与分发</x:t>
+  </x:si>
+  <x:si>
+    <x:t>内容新增或状态变更经事件总线广播 content.changed 事件，使用方订阅响应；作为权威源向使用方主动分发 content_id。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>content.changed 事件广播；主动分发 content_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对接 II-12a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-09-01 发布前内容审核；F-OCC-09-02 敏感词检测与拦截</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRS R-OCC-009(合规)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R-OCC-009 的审核与敏感词检测是合规风控域(敏感词库+拦截策略)，与主数据 CRUD 异构，故拆。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-09-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>发布前内容审核</x:t>
+  </x:si>
+  <x:si>
+    <x:t>发布前对内容进行审核。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>发布前审核</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F-OCC-09-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>敏感词检测与拦截</x:t>
+  </x:si>
+  <x:si>
+    <x:t>对内容进行敏感词检测；敏感词命中时拦截并标记待人工复核。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>敏感词检测；命中拦截待复核</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7951,8 +7951,7 @@
         <x:v>220</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:8"/>
-    <x:row r="6" spans="1:8">
+    <x:row r="5" spans="1:8">
       <x:c r="A5" s="6" t="s">
         <x:v>215</x:v>
       </x:c>
@@ -7978,7 +7977,7 @@
         <x:v>220</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:8" ht="40.5">
+    <x:row r="6" spans="1:8" ht="40.5">
       <x:c r="A6" s="4" t="s">
         <x:v>211</x:v>
       </x:c>
@@ -8004,7 +8003,7 @@
         <x:v>699</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:8" ht="40.5">
+    <x:row r="7" spans="1:8" ht="40.5">
       <x:c r="A7" s="6" t="s">
         <x:v>215</x:v>
       </x:c>
@@ -8030,7 +8029,7 @@
         <x:v>220</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:8">
+    <x:row r="8" spans="1:8">
       <x:c r="A8" s="6" t="s">
         <x:v>215</x:v>
       </x:c>
@@ -8056,7 +8055,7 @@
         <x:v>220</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:8" ht="27">
+    <x:row r="9" spans="1:8" ht="27">
       <x:c r="A9" s="6" t="s">
         <x:v>215</x:v>
       </x:c>

--- a/公司项目/认知作战/文档/软件概要设计-模块功能拆分-v2.xlsx
+++ b/公司项目/认知作战/文档/软件概要设计-模块功能拆分-v2.xlsx
@@ -8139,11 +8139,11 @@
       <x:c r="C2" s="3" t="s">
         <x:v>713</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="E2" s="3" t="s">
-        <x:v>126</x:v>
+      <x:c r="D2" s="3" t="str">
+        <x:v>R-SWM-001~005</x:v>
+      </x:c>
+      <x:c r="E2" s="3" t="str">
+        <x:v>执行层的「提示词生成与记忆中心」：根据人设(画像/账号属性)生成驱动智能体作业的提示词并管理记忆，将生成的提示词包(人设标签/提示词/作业策略)以 agent_id(稳定逻辑标识)同步下发至 MC 持存，由 MC 的 agent-runtime 子模块运行；承担提示词与人设管理、提示词自动生成、记忆管理、智能体构建、智能体评测；不直接操作设备。提示词工程与评测以 coze-loop(Go)旁挂集成，其余组件用 Java(智能体域特例 CON-14)。</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
         <x:v>208</x:v>
@@ -8151,8 +8151,8 @@
       <x:c r="G2" s="3" t="s">
         <x:v>714</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="s">
-        <x:v>715</x:v>
+      <x:c r="H2" s="3" t="str">
+        <x:v>R-SWM-001(提示词与人设管理)含人设标签、提示词模板库两个异构关注点(元数据/文本资产)，故拆 2 模块；运行时(场景适配/动态调用/调IRS)移至 MC 的 agent-runtime 子模块(M-MC-06)，不在 SWM；提示词自动生成(R-SWM-005)独立成 M-SWM-07；智能体定义组装与提示词包同步归构建模块(M-SWM-05)，迭代优化决策归评测模块(M-SWM-06)。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="54">
@@ -8368,25 +8368,25 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>135</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C11" s="5" t="s">
-        <x:v>136</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D11" s="5" t="s">
-        <x:v>137</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E11" s="5" t="s">
-        <x:v>138</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F11" s="5" t="s">
-        <x:v>748</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="G11" s="5" t="s">
-        <x:v>749</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="H11" s="5" t="s">
-        <x:v>750</x:v>
+        <x:v>762</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:8" ht="27">
@@ -8394,22 +8394,22 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>751</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="C12" s="7" t="s">
-        <x:v>752</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="D12" s="7" t="s">
-        <x:v>721</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E12" s="7" t="s">
-        <x:v>753</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="F12" s="7" t="s">
-        <x:v>754</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="G12" s="7" t="s">
-        <x:v>724</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="H12" s="7" t="s">
         <x:v>220</x:v>
@@ -8420,51 +8420,51 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>755</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="C13" s="7" t="s">
-        <x:v>756</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="D13" s="7" t="s">
-        <x:v>721</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E13" s="7" t="s">
-        <x:v>757</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="F13" s="7" t="s">
-        <x:v>758</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="G13" s="7" t="s">
-        <x:v>724</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="H13" s="7" t="s">
-        <x:v>759</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:8" ht="54">
-      <x:c r="A14" s="4" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="B14" s="4" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C14" s="5" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D14" s="5" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:8">
+      <x:c r="A14" s="6" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="s">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="s">
+        <x:v>772</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="E14" s="5" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="F14" s="5" t="s">
-        <x:v>760</x:v>
-      </x:c>
-      <x:c r="G14" s="5" t="s">
+      <x:c r="E14" s="7" t="s">
+        <x:v>773</x:v>
+      </x:c>
+      <x:c r="F14" s="7" t="s">
+        <x:v>774</x:v>
+      </x:c>
+      <x:c r="G14" s="7" t="s">
         <x:v>761</x:v>
       </x:c>
-      <x:c r="H14" s="5" t="s">
-        <x:v>762</x:v>
+      <x:c r="H14" s="7" t="s">
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:8" ht="27">
@@ -8472,19 +8472,19 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
-        <x:v>763</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>764</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="D15" s="7" t="s">
         <x:v>141</x:v>
       </x:c>
       <x:c r="E15" s="7" t="s">
-        <x:v>765</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="F15" s="7" t="s">
-        <x:v>766</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="G15" s="7" t="s">
         <x:v>761</x:v>
@@ -8493,160 +8493,160 @@
         <x:v>220</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:8">
-      <x:c r="A16" s="6" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="B16" s="6" t="s">
-        <x:v>767</x:v>
-      </x:c>
-      <x:c r="C16" s="7" t="s">
-        <x:v>768</x:v>
-      </x:c>
-      <x:c r="D16" s="7" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="E16" s="7" t="s">
-        <x:v>769</x:v>
-      </x:c>
-      <x:c r="F16" s="7" t="s">
-        <x:v>770</x:v>
-      </x:c>
-      <x:c r="G16" s="7" t="s">
-        <x:v>761</x:v>
-      </x:c>
-      <x:c r="H16" s="7" t="s">
-        <x:v>220</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:8">
+    <x:row r="16" spans="1:8" ht="81">
+      <x:c r="A16" s="4" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B16" s="4" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C16" s="5" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D16" s="5" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E16" s="5" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="F16" s="5" t="s">
+        <x:v>779</x:v>
+      </x:c>
+      <x:c r="G16" s="5" t="s">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="H16" s="5" t="s">
+        <x:v>781</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:8" ht="27">
       <x:c r="A17" s="6" t="s">
         <x:v>215</x:v>
       </x:c>
       <x:c r="B17" s="6" t="s">
-        <x:v>771</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="C17" s="7" t="s">
-        <x:v>772</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="D17" s="7" t="s">
-        <x:v>141</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E17" s="7" t="s">
-        <x:v>773</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="F17" s="7" t="s">
-        <x:v>774</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="G17" s="7" t="s">
-        <x:v>761</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="H17" s="7" t="s">
         <x:v>220</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:8" ht="27">
+    <x:row r="18" spans="1:8" ht="31.5">
       <x:c r="A18" s="6" t="s">
         <x:v>215</x:v>
       </x:c>
       <x:c r="B18" s="6" t="s">
-        <x:v>775</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="C18" s="7" t="s">
-        <x:v>776</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="D18" s="7" t="s">
-        <x:v>141</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E18" s="7" t="s">
-        <x:v>777</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="F18" s="7" t="s">
-        <x:v>778</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="G18" s="7" t="s">
-        <x:v>761</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="H18" s="7" t="s">
-        <x:v>220</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:8" ht="81">
-      <x:c r="A19" s="4" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="B19" s="4" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C19" s="5" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="D19" s="5" t="s">
+        <x:v>790</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:8" ht="27">
+      <x:c r="A19" s="6" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="s">
+        <x:v>791</x:v>
+      </x:c>
+      <x:c r="C19" s="7" t="s">
+        <x:v>792</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="E19" s="5" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="F19" s="5" t="s">
-        <x:v>779</x:v>
-      </x:c>
-      <x:c r="G19" s="5" t="s">
+      <x:c r="E19" s="7" t="s">
+        <x:v>793</x:v>
+      </x:c>
+      <x:c r="F19" s="7" t="s">
+        <x:v>794</x:v>
+      </x:c>
+      <x:c r="G19" s="7" t="s">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="H19" s="5" t="s">
-        <x:v>781</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:8" ht="27">
+      <x:c r="H19" s="7" t="s">
+        <x:v>584</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:8">
       <x:c r="A20" s="6" t="s">
         <x:v>215</x:v>
       </x:c>
       <x:c r="B20" s="6" t="s">
-        <x:v>782</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="C20" s="7" t="s">
-        <x:v>783</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="D20" s="7" t="s">
         <x:v>145</x:v>
       </x:c>
       <x:c r="E20" s="7" t="s">
-        <x:v>784</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="F20" s="7" t="s">
-        <x:v>785</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="G20" s="7" t="s">
         <x:v>780</x:v>
       </x:c>
       <x:c r="H20" s="7" t="s">
-        <x:v>220</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:8" ht="31.5">
-      <x:c r="A21" s="6" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="B21" s="6" t="s">
-        <x:v>786</x:v>
-      </x:c>
-      <x:c r="C21" s="7" t="s">
-        <x:v>787</x:v>
-      </x:c>
-      <x:c r="D21" s="7" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="E21" s="7" t="s">
-        <x:v>788</x:v>
-      </x:c>
-      <x:c r="F21" s="7" t="s">
-        <x:v>789</x:v>
-      </x:c>
-      <x:c r="G21" s="7" t="s">
-        <x:v>780</x:v>
-      </x:c>
-      <x:c r="H21" s="7" t="s">
-        <x:v>790</x:v>
+        <x:v>534</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:8" ht="108">
+      <x:c r="A21" s="4" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C21" s="5" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D21" s="5" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E21" s="5" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F21" s="5" t="s">
+        <x:v>799</x:v>
+      </x:c>
+      <x:c r="G21" s="5" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="H21" s="5" t="s">
+        <x:v>801</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:8" ht="27">
@@ -8654,129 +8654,129 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="B22" s="6" t="s">
-        <x:v>791</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="C22" s="7" t="s">
-        <x:v>792</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="D22" s="7" t="s">
-        <x:v>145</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E22" s="7" t="s">
-        <x:v>793</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="F22" s="7" t="s">
-        <x:v>794</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="G22" s="7" t="s">
-        <x:v>780</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="H22" s="7" t="s">
-        <x:v>584</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:8">
+        <x:v>806</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:8" ht="67.5">
       <x:c r="A23" s="6" t="s">
         <x:v>215</x:v>
       </x:c>
       <x:c r="B23" s="6" t="s">
-        <x:v>795</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="C23" s="7" t="s">
-        <x:v>796</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="D23" s="7" t="s">
-        <x:v>145</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E23" s="7" t="s">
-        <x:v>797</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="F23" s="7" t="s">
-        <x:v>798</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="G23" s="7" t="s">
-        <x:v>780</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="H23" s="7" t="s">
-        <x:v>534</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:8" ht="108">
-      <x:c r="A24" s="4" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="B24" s="4" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C24" s="5" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D24" s="5" t="s">
+        <x:v>811</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:8" ht="54">
+      <x:c r="A24" s="6" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="s">
+        <x:v>812</x:v>
+      </x:c>
+      <x:c r="C24" s="7" t="s">
+        <x:v>813</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="E24" s="5" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="F24" s="5" t="s">
-        <x:v>799</x:v>
-      </x:c>
-      <x:c r="G24" s="5" t="s">
+      <x:c r="E24" s="7" t="s">
+        <x:v>814</x:v>
+      </x:c>
+      <x:c r="F24" s="7" t="s">
+        <x:v>815</x:v>
+      </x:c>
+      <x:c r="G24" s="7" t="s">
         <x:v>800</x:v>
       </x:c>
-      <x:c r="H24" s="5" t="s">
-        <x:v>801</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:8" ht="27">
+      <x:c r="H24" s="7" t="s">
+        <x:v>816</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:8" ht="40.5">
       <x:c r="A25" s="6" t="s">
         <x:v>215</x:v>
       </x:c>
       <x:c r="B25" s="6" t="s">
-        <x:v>802</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="C25" s="7" t="s">
-        <x:v>803</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="D25" s="7" t="s">
         <x:v>149</x:v>
       </x:c>
       <x:c r="E25" s="7" t="s">
-        <x:v>804</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="F25" s="7" t="s">
-        <x:v>805</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="G25" s="7" t="s">
         <x:v>800</x:v>
       </x:c>
       <x:c r="H25" s="7" t="s">
-        <x:v>806</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:8" ht="67.5">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:8" ht="40.5">
       <x:c r="A26" s="6" t="s">
         <x:v>215</x:v>
       </x:c>
       <x:c r="B26" s="6" t="s">
-        <x:v>807</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="C26" s="7" t="s">
-        <x:v>808</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="D26" s="7" t="s">
         <x:v>149</x:v>
       </x:c>
       <x:c r="E26" s="7" t="s">
-        <x:v>809</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="F26" s="7" t="s">
-        <x:v>810</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="G26" s="7" t="s">
         <x:v>800</x:v>
       </x:c>
       <x:c r="H26" s="7" t="s">
-        <x:v>811</x:v>
+        <x:v>825</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:8" ht="54">
@@ -8784,103 +8784,74 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="B27" s="6" t="s">
-        <x:v>812</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="C27" s="7" t="s">
-        <x:v>813</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="D27" s="7" t="s">
         <x:v>149</x:v>
       </x:c>
       <x:c r="E27" s="7" t="s">
-        <x:v>814</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="F27" s="7" t="s">
-        <x:v>815</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="G27" s="7" t="s">
         <x:v>800</x:v>
       </x:c>
       <x:c r="H27" s="7" t="s">
-        <x:v>816</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:8" ht="40.5">
-      <x:c r="A28" s="6" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="B28" s="6" t="s">
-        <x:v>817</x:v>
-      </x:c>
-      <x:c r="C28" s="7" t="s">
-        <x:v>818</x:v>
-      </x:c>
-      <x:c r="D28" s="7" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="B28" t="str">
+        <x:v>M-SWM-07</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>按账号与画像自动生成提示词（提示词自动生成引擎）</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>R-SWM-005</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>根据账号主数据(MC)与用户画像(OCC 全维度档案)经 IRS 本地大模型自动生成贴合人设的提示词，降低人工编写成本；生成结果版本化并可作为智能体构建(M-SWM-05)的提示词来源。</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>F-SWM-07-01 账号与画像拉取；F-SWM-07-02 提示词自动生成；F-SWM-07-03 生成结果版本化与纳入构建</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>SRS R-SWM-005</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>对应 R-SWM-005。07-01 从 MC 拉账号(II-01)、从 OCC 拉画像(II-18/R-OCC-004)；07-02 经 IRS(EI-05)生成；07-03 版本化回写提示词库并可纳入构建。生成推理不经执行网关(CON-10)、私有化(CON-06)。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:8" ht="108">
+      <x:c r="A28" s="4" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B28" s="4" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C28" s="5" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D28" s="5" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="E28" s="7" t="s">
-        <x:v>819</x:v>
-      </x:c>
-      <x:c r="F28" s="7" t="s">
-        <x:v>820</x:v>
-      </x:c>
-      <x:c r="G28" s="7" t="s">
+      <x:c r="E28" s="5" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F28" s="5" t="s">
+        <x:v>799</x:v>
+      </x:c>
+      <x:c r="G28" s="5" t="s">
         <x:v>800</x:v>
       </x:c>
-      <x:c r="H28" s="7" t="s">
-        <x:v>220</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:8" ht="40.5">
-      <x:c r="A29" s="6" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="B29" s="6" t="s">
-        <x:v>821</x:v>
-      </x:c>
-      <x:c r="C29" s="7" t="s">
-        <x:v>822</x:v>
-      </x:c>
-      <x:c r="D29" s="7" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="E29" s="7" t="s">
-        <x:v>823</x:v>
-      </x:c>
-      <x:c r="F29" s="7" t="s">
-        <x:v>824</x:v>
-      </x:c>
-      <x:c r="G29" s="7" t="s">
-        <x:v>800</x:v>
-      </x:c>
-      <x:c r="H29" s="7" t="s">
-        <x:v>825</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:8" ht="54">
-      <x:c r="A30" s="6" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="B30" s="6" t="s">
-        <x:v>826</x:v>
-      </x:c>
-      <x:c r="C30" s="7" t="s">
-        <x:v>827</x:v>
-      </x:c>
-      <x:c r="D30" s="7" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="E30" s="7" t="s">
-        <x:v>828</x:v>
-      </x:c>
-      <x:c r="F30" s="7" t="s">
-        <x:v>829</x:v>
-      </x:c>
-      <x:c r="G30" s="7" t="s">
-        <x:v>800</x:v>
-      </x:c>
-      <x:c r="H30" s="7" t="s">
-        <x:v>220</x:v>
+      <x:c r="H28" s="5" t="s">
+        <x:v>801</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/公司项目/认知作战/文档/软件概要设计-模块功能拆分-v2.xlsx
+++ b/公司项目/认知作战/文档/软件概要设计-模块功能拆分-v2.xlsx
@@ -4582,8 +4582,8 @@
       <x:c r="C30" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="F30" t="s">
-        <x:v>125</x:v>
+      <x:c r="F30" t="str">
+        <x:v>R-SWM-001~005</x:v>
       </x:c>
       <x:c r="G30" s="8" t="s">
         <x:v>126</x:v>
@@ -4619,55 +4619,55 @@
     </x:row>
     <x:row r="33" spans="1:7" ht="36">
       <x:c r="D33" t="s">
-        <x:v>135</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E33" t="s">
-        <x:v>136</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F33" t="s">
-        <x:v>137</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G33" s="8" t="s">
-        <x:v>138</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:7" ht="36">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:7" ht="54">
       <x:c r="D34" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="E34" t="s">
-        <x:v>140</x:v>
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>智能体构建与提示词包下发（智能体装配工厂）</x:v>
       </x:c>
       <x:c r="F34" t="s">
-        <x:v>141</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G34" s="8" t="s">
-        <x:v>142</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:7" ht="54">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:7" ht="72">
       <x:c r="D35" t="s">
-        <x:v>143</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E35" t="s">
-        <x:v>144</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F35" t="s">
-        <x:v>145</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G35" s="8" t="s">
-        <x:v>146</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7" ht="72">
-      <x:c r="D36" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="E36" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F36" t="s">
-        <x:v>149</x:v>
+      <x:c r="D36" t="str">
+        <x:v>M-SWM-07</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>按账号与画像自动生成提示词（提示词自动生成引擎）</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>R-SWM-005</x:v>
       </x:c>
       <x:c r="G36" s="8" t="s">
         <x:v>150</x:v>
@@ -6152,17 +6152,17 @@
       <x:c r="D30" s="7" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E30" s="7" t="s">
-        <x:v>421</x:v>
-      </x:c>
-      <x:c r="F30" s="7" t="s">
-        <x:v>422</x:v>
+      <x:c r="E30" s="7" t="str">
+        <x:v>由 MC 的 agent-runtime 子模块按 MC 持存的提示词包运行(场景适配/动态调用/读记忆/调 IRS 视觉推理与规划)自主决策动作；agent-runtime 与执行网关逻辑隔离，推理不经网关，产出的动作指令再经网关落地。</x:v>
+      </x:c>
+      <x:c r="F30" s="7" t="str">
+        <x:v>agent-runtime 运行提示词包；读记忆(R-SWM-002)；调 IRS 推理；动作经网关落地</x:v>
       </x:c>
       <x:c r="G30" s="7" t="s">
         <x:v>423</x:v>
       </x:c>
-      <x:c r="H30" s="7" t="s">
-        <x:v>424</x:v>
+      <x:c r="H30" s="7" t="str">
+        <x:v>对接 EI-05/II-08；agent-runtime 承接原 SWM M-SWM-03 运行时职责</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:8" ht="40.5">
@@ -8500,23 +8500,23 @@
       <x:c r="B16" s="4" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="C16" s="5" t="s">
-        <x:v>144</x:v>
+      <x:c r="C16" s="5" t="str">
+        <x:v>智能体构建与提示词包下发（智能体装配工厂）</x:v>
       </x:c>
       <x:c r="D16" s="5" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="E16" s="5" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="F16" s="5" t="s">
-        <x:v>779</x:v>
+      <x:c r="E16" s="5" t="str">
+        <x:v>根据人设标签配置提示词与作业策略，组装为提示词包(人设标签/提示词/作业策略)并以 agent_id(稳定逻辑标识)为标识，经 II-14 同步至 MC 持存、供 OCC 作战编排引用。记忆不在提示词包内，由记忆服务独立承载。</x:v>
+      </x:c>
+      <x:c r="F16" s="5" t="str">
+        <x:v>F-SWM-05-01 提示词包构建；F-SWM-05-02 账号绑定引用；F-SWM-05-03 同步至 MC 持存；F-SWM-05-04 OCC 智能体节点定义来源</x:v>
       </x:c>
       <x:c r="G16" s="5" t="s">
         <x:v>780</x:v>
       </x:c>
-      <x:c r="H16" s="5" t="s">
-        <x:v>781</x:v>
+      <x:c r="H16" s="5" t="str">
+        <x:v>对应 R-SWM-003，构建是装配链(配置策略+组装提示词包+下发)，内聚不拆；运行时(场景适配/动态调用/调IRS)移至 MC，不在 SWM。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:8" ht="27">
@@ -8526,17 +8526,17 @@
       <x:c r="B17" s="6" t="s">
         <x:v>782</x:v>
       </x:c>
-      <x:c r="C17" s="7" t="s">
-        <x:v>783</x:v>
+      <x:c r="C17" s="7" t="str">
+        <x:v>提示词包构建</x:v>
       </x:c>
       <x:c r="D17" s="7" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="E17" s="7" t="s">
-        <x:v>784</x:v>
-      </x:c>
-      <x:c r="F17" s="7" t="s">
-        <x:v>785</x:v>
+      <x:c r="E17" s="7" t="str">
+        <x:v>按人设标签配置提示词与作业策略(目标/场景/边界)，组装为提示词包，以全局唯一 agent_id(稳定逻辑标识)为标识；提示词可手动编写或由 M-SWM-07 自动生成。</x:v>
+      </x:c>
+      <x:c r="F17" s="7" t="str">
+        <x:v>人设+提示词+作业策略组装；agent_id 标识；版本子属性</x:v>
       </x:c>
       <x:c r="G17" s="7" t="s">
         <x:v>780</x:v>
@@ -8558,8 +8558,8 @@
       <x:c r="D18" s="7" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="E18" s="7" t="s">
-        <x:v>788</x:v>
+      <x:c r="E18" s="7" t="str">
+        <x:v>提示词包与账号严格 1:1 绑定(agent_id↔account_id)，绑定关系由 MC 维护，本子系统构建时引用 account_id。</x:v>
       </x:c>
       <x:c r="F18" s="7" t="s">
         <x:v>789</x:v>
@@ -8584,8 +8584,8 @@
       <x:c r="D19" s="7" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="E19" s="7" t="s">
-        <x:v>793</x:v>
+      <x:c r="E19" s="7" t="str">
+        <x:v>构建完成的提示词包经 II-14 同步至 MC 持存，取得持存版本号；提示词更新时以同一 agent_id 重新同步并升级版本号。</x:v>
       </x:c>
       <x:c r="F19" s="7" t="s">
         <x:v>794</x:v>
@@ -8604,14 +8604,14 @@
       <x:c r="B20" s="6" t="s">
         <x:v>795</x:v>
       </x:c>
-      <x:c r="C20" s="7" t="s">
-        <x:v>796</x:v>
+      <x:c r="C20" s="7" t="str">
+        <x:v>OCC 智能体节点定义来源</x:v>
       </x:c>
       <x:c r="D20" s="7" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="E20" s="7" t="s">
-        <x:v>797</x:v>
+      <x:c r="E20" s="7" t="str">
+        <x:v>构建出的提示词包是 OCC 作战编排中智能体节点的定义来源。</x:v>
       </x:c>
       <x:c r="F20" s="7" t="s">
         <x:v>798</x:v>
@@ -8828,6 +8828,66 @@
         <x:v>对应 R-SWM-005。07-01 从 MC 拉账号(II-01)、从 OCC 拉画像(II-18/R-OCC-004)；07-02 经 IRS(EI-05)生成；07-03 版本化回写提示词库并可纳入构建。生成推理不经执行网关(CON-10)、私有化(CON-06)。</x:v>
       </x:c>
     </x:row>
+    <x:row r="29">
+      <x:c r="B29" t="str">
+        <x:v>F-SWM-07-01</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>账号与画像拉取</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>R-SWM-005</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>按 account_id 从 MC 拉取账号主数据(II-01)，按目标标识从 OCC 拉取用户画像(II-18，来源于 R-OCC-004 全维度档案)。</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>账号主数据拉取；用户画像拉取；只引用标识不复制主数据</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>SRS R-SWM-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="B30" t="str">
+        <x:v>F-SWM-07-02</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>提示词自动生成</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>R-SWM-005</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>将账号属性与用户画像作为上下文，经 IRS 本地大模型推理(EI-05，不经执行网关)生成贴合人设的提示词。</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>上下文组装；IRS 生成推理；私有化约束</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>SRS R-SWM-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="B31" t="str">
+        <x:v>F-SWM-07-03</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>生成结果版本化与纳入构建</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>R-SWM-005</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>生成的提示词纳入版本管理(以 agent_id 索引)，回写提示词库，可由工程师审核微调后纳入 R-SWM-003 智能体构建。</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>版本化回写；人工审核微调；纳入构建</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>SRS R-SWM-005</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:8" ht="108">
       <x:c r="A28" s="4" t="s">
         <x:v>211</x:v>
@@ -8852,6 +8912,84 @@
       </x:c>
       <x:c r="H28" s="5" t="s">
         <x:v>801</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:8" ht="27">
+      <x:c r="A29" s="6" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="s">
+        <x:v>802</x:v>
+      </x:c>
+      <x:c r="C29" s="7" t="s">
+        <x:v>803</x:v>
+      </x:c>
+      <x:c r="D29" s="7" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E29" s="7" t="s">
+        <x:v>804</x:v>
+      </x:c>
+      <x:c r="F29" s="7" t="s">
+        <x:v>805</x:v>
+      </x:c>
+      <x:c r="G29" s="7" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="H29" s="7" t="s">
+        <x:v>806</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:8" ht="27">
+      <x:c r="A30" s="6" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="s">
+        <x:v>802</x:v>
+      </x:c>
+      <x:c r="C30" s="7" t="s">
+        <x:v>803</x:v>
+      </x:c>
+      <x:c r="D30" s="7" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E30" s="7" t="s">
+        <x:v>804</x:v>
+      </x:c>
+      <x:c r="F30" s="7" t="s">
+        <x:v>805</x:v>
+      </x:c>
+      <x:c r="G30" s="7" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="H30" s="7" t="s">
+        <x:v>806</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:8" ht="27">
+      <x:c r="A31" s="6" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="s">
+        <x:v>802</x:v>
+      </x:c>
+      <x:c r="C31" s="7" t="s">
+        <x:v>803</x:v>
+      </x:c>
+      <x:c r="D31" s="7" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="s">
+        <x:v>804</x:v>
+      </x:c>
+      <x:c r="F31" s="7" t="s">
+        <x:v>805</x:v>
+      </x:c>
+      <x:c r="G31" s="7" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="H31" s="7" t="s">
+        <x:v>806</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/公司项目/认知作战/文档/软件概要设计-模块功能拆分-v2.xlsx
+++ b/公司项目/认知作战/文档/软件概要设计-模块功能拆分-v2.xlsx
@@ -4380,8 +4380,8 @@
       <x:c r="F16" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G16" s="8" t="s">
-        <x:v>68</x:v>
+      <x:c r="G16" s="8" t="str">
+        <x:v>承载养号、账号-终端-代理绑定、登录状态维护等可自动化的账号操作的执行编排，以及养号拟人化节奏策略（内置）。认知行动账号经移动端 ADB/无障碍通道养号、爬虫账号经桌面端 CDP 通道养护。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7" ht="72">
@@ -4408,8 +4408,8 @@
       <x:c r="F18" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G18" s="8" t="s">
-        <x:v>76</x:v>
+      <x:c r="G18" s="8" t="str">
+        <x:v>平台级权威源，唯一维护社交媒体账号主数据（注册、凭据、验证、风险评估、生命周期、账号分类），经事件总线向 DC/SWM/OCC 分发 account_id，保证全网一致、凭据加密、被封账号全网即时失效；账号分爬虫账号(桌面端)与认知行动账号(移动端)两类。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7" ht="54">
@@ -4430,14 +4430,14 @@
       <x:c r="D20" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E20" t="s">
-        <x:v>82</x:v>
+      <x:c r="E20" t="str">
+        <x:v>智能体账号绑定与资产迁移（四元行动单元）</x:v>
       </x:c>
       <x:c r="F20" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G20" s="8" t="s">
-        <x:v>84</x:v>
+      <x:c r="G20" s="8" t="str">
+        <x:v>维护账号与智能体定义（agent_id）严格 1:1 绑定，叠加账号-终端-代理绑定形成四元行动单元（agent_id:account_id:终端:代理 IP = 1:1:1:1）；账号被封后支持资产迁移整体继承人格（提示词版本/记忆）。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7" ht="90">
@@ -4450,8 +4450,8 @@
       <x:c r="F21" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G21" s="8" t="s">
-        <x:v>88</x:v>
+      <x:c r="G21" s="8" t="str">
+        <x:v>作为智能体执行宿主，接收并持存 SWM 同步来的智能体定义（以 agent_id 为标识，含提示词/作业策略），任务执行时调用这些定义驱动设备作业，执行前校验行为风格一致性（不一致拒绝执行）；确立「SWM 定义中心、MC 执行宿主」分工。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7" ht="36">
@@ -4585,22 +4585,22 @@
       <x:c r="F30" t="str">
         <x:v>R-SWM-001~005</x:v>
       </x:c>
-      <x:c r="G30" s="8" t="s">
-        <x:v>126</x:v>
+      <x:c r="G30" s="8" t="str">
+        <x:v>执行层的「智能体定义与记忆中心」：编写驱动智能体作业的提示词与记忆，将提示词包(提示词/作业策略)以 agent_id 同步下发至 MC 持存；承担智能体构建、评测、提示词管理、记忆管理；不直接操作设备。</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7" ht="54">
       <x:c r="D31" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="E31" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F31" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G31" s="8" t="s">
-        <x:v>130</x:v>
+      <x:c r="E31" t="str">
+        <x:v>提示词管理（V3.9：原人设标签管理废除）</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>R-SWM-001(提示词)</x:v>
+      </x:c>
+      <x:c r="G31" s="8" t="str">
+        <x:v>V3.9 废除人设标签实体，改为提示词模板与版本管理（人设属性直接写进提示词文本）。</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7" ht="54">
@@ -4627,8 +4627,8 @@
       <x:c r="F33" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="G33" s="8" t="s">
-        <x:v>142</x:v>
+      <x:c r="G33" s="8" t="str">
+        <x:v>实现智能体作业记忆的存储、场景沉淀、历史复用与个性化状态延续，使智能体长期行为符合行为风格且不断演进。</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7" ht="54">
@@ -4641,8 +4641,8 @@
       <x:c r="F34" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G34" s="8" t="s">
-        <x:v>146</x:v>
+      <x:c r="G34" s="8" t="str">
+        <x:v>编写提示词与记忆初值、配置作业策略，组装为完整智能体定义并以 agent_id 为标识，经 II-14 同步至 MC 持存、供 OCC 行动编排引用。</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7" ht="72">
@@ -4717,8 +4717,8 @@
       <x:c r="F39" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G39" s="8" t="s">
-        <x:v>163</x:v>
+      <x:c r="G39" s="8" t="str">
+        <x:v>全链路指挥大脑：构建「目标识别→数据分析与情报→行动编排→效果评估」行动闭环，并承担内容资源统一管理(唯一权威源)；基于 DC 采集的原始舆情/传播数据（经 II-13）与 IRS 推理产出行动方案，在本子系统内完成数据分析与情报研判（V3.3 起由 DC 移入），以行动编排直接编排 MC 中智能体节点与自动化脚本节点形成执行流程落地。</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7" ht="54">
@@ -4767,8 +4767,8 @@
       <x:c r="D43" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="E43" t="s">
-        <x:v>177</x:v>
+      <x:c r="E43" t="str">
+        <x:v>行动方案规划（行动参谋）</x:v>
       </x:c>
       <x:c r="F43" t="s">
         <x:v>178</x:v>
@@ -4795,8 +4795,8 @@
       <x:c r="D45" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="E45" t="s">
-        <x:v>185</x:v>
+      <x:c r="E45" t="str">
+        <x:v>效果评估（行动复盘官）</x:v>
       </x:c>
       <x:c r="F45" t="s">
         <x:v>186</x:v>
@@ -4815,8 +4815,8 @@
       <x:c r="F46" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="G46" s="8" t="s">
-        <x:v>191</x:v>
+      <x:c r="G46" s="8" t="str">
+        <x:v>搭建并迭代多语种/多场景/多风格舆论作业策略库，为行动提供可复用、可演进的策略资产。</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7" ht="54">

--- a/公司项目/认知作战/文档/软件概要设计-模块功能拆分-v2.xlsx
+++ b/公司项目/认知作战/文档/软件概要设计-模块功能拆分-v2.xlsx
@@ -4431,13 +4431,13 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="E20" t="str">
-        <x:v>智能体账号绑定与资产迁移（四元行动单元）</x:v>
+        <x:v>智能体账号绑定与资产迁移（行动关系 1:N:1:1）</x:v>
       </x:c>
       <x:c r="F20" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="G20" s="8" t="str">
-        <x:v>维护账号与智能体定义（agent_id）严格 1:1 绑定，叠加账号-终端-代理绑定形成四元行动单元（agent_id:account_id:终端:代理 IP = 1:1:1:1）；账号被封后支持资产迁移整体继承人格（提示词版本/记忆）。</x:v>
+        <x:v>维护智能体定义（agent_id）与账号（account_id）1:N 绑定（一个agent绑多账号），账号级记忆/动态提示词按 account_id 1:1 归属；叠加账号-终端-代理绑定（1:1:1）形成行动关系（agent_id:account_id:终端:代理 IP = 1:N:1:1）；账号被封后支持账号资产迁移（账号级记忆/动态提示词迁移到新账号，agent 不变）。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7" ht="90">
@@ -4451,7 +4451,7 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="G21" s="8" t="str">
-        <x:v>作为智能体执行宿主，接收并持存 SWM 同步来的智能体定义（以 agent_id 为标识，含提示词/作业策略），任务执行时调用这些定义驱动设备作业，执行前校验行为风格一致性（不一致拒绝执行）；确立「SWM 定义中心、MC 执行宿主」分工。</x:v>
+        <x:v>作为智能体执行宿主，接收并持存 SWM 同步来的提示词包（以 agent_id+account_id 组合为标识，含提示词模板/账号级动态提示词实例/作业策略），任务执行时调用这些定义驱动设备作业，执行前校验行为风格一致性（不一致拒绝执行）；确立「SWM 提示词生成与记忆中心、MC 执行宿主」分工。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7" ht="36">
@@ -4586,7 +4586,7 @@
         <x:v>R-SWM-001~005</x:v>
       </x:c>
       <x:c r="G30" s="8" t="str">
-        <x:v>执行层的「智能体定义与记忆中心」：编写驱动智能体作业的提示词与记忆，将提示词包(提示词/作业策略)以 agent_id 同步下发至 MC 持存；承担智能体构建、评测、提示词管理、记忆管理；不直接操作设备。</x:v>
+        <x:v>执行层的「提示词生成与记忆中心」：编写驱动智能体作业的提示词模板与记忆，将提示词包(提示词模板/账号级动态提示词实例/作业策略)以 agent_id+account_id 组合同步下发至 MC 持存；承担智能体构建、评测、提示词管理、记忆管理；不直接操作设备。</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7" ht="54">
@@ -4613,8 +4613,8 @@
       <x:c r="F32" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="G32" s="8" t="s">
-        <x:v>134</x:v>
+      <x:c r="G32" s="8" t="str">
+        <x:v>建立提示词模板库并按用途/平台/目标分类管理；对提示词模板进行版本管理，以 agent_id 为主键索引（模板共性），账号级动态提示词实例按 account_id 1:1 归属，支持版本对比/回滚/变更记录。</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7" ht="36">
@@ -4628,7 +4628,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="G33" s="8" t="str">
-        <x:v>实现智能体作业记忆的存储、场景沉淀、历史复用与个性化状态延续，使智能体长期行为符合行为风格且不断演进。</x:v>
+        <x:v>实现智能体作业记忆的存储、场景沉淀、历史复用与个性化状态延续，使智能体长期行为符合行为风格且不断演进。记忆按 account_id 1:1 归属（账号级独立）。</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7" ht="54">
@@ -4642,7 +4642,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="G34" s="8" t="str">
-        <x:v>编写提示词与记忆初值、配置作业策略，组装为完整智能体定义并以 agent_id 为标识，经 II-14 同步至 MC 持存、供 OCC 行动编排引用。</x:v>
+        <x:v>编写提示词模板与记忆初值、配置作业策略，组装为完整提示词包（模板+账号级动态实例）并以 agent_id+account_id 组合为标识，经 II-14 同步至 MC 持存、供 OCC 行动编排引用。</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7" ht="72">
@@ -6153,10 +6153,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="E30" s="7" t="str">
-        <x:v>由 MC 的 agent-runtime 子模块按 MC 持存的提示词包运行(场景适配/动态调用/读记忆/调 IRS 视觉推理与规划)自主决策动作；agent-runtime 与执行网关逻辑隔离，推理不经网关，产出的动作指令再经网关落地。</x:v>
+        <x:v>由 MC 的 agent-runtime 子模块按 MC 持存的提示词包运行(场景适配/动态调用/按account_id读记忆/调 IRS 视觉推理与规划)自主决策动作；agent-runtime 与执行网关逻辑隔离，推理不经网关，产出的动作指令再经网关落地。</x:v>
       </x:c>
       <x:c r="F30" s="7" t="str">
-        <x:v>agent-runtime 运行提示词包；读记忆(R-SWM-002)；调 IRS 推理；动作经网关落地</x:v>
+        <x:v>agent-runtime 运行提示词包；按account_id读记忆(R-SWM-002)；调 IRS 推理；动作经网关落地</x:v>
       </x:c>
       <x:c r="G30" s="7" t="s">
         <x:v>423</x:v>
@@ -7134,17 +7134,17 @@
       <x:c r="B68" s="4" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="C68" s="5" t="s">
-        <x:v>82</x:v>
+      <x:c r="C68" s="5" t="str">
+        <x:v>智能体账号绑定与资产迁移（行动关系 1:N:1:1）</x:v>
       </x:c>
       <x:c r="D68" s="5" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="E68" s="5" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F68" s="5" t="s">
-        <x:v>577</x:v>
+      <x:c r="E68" s="5" t="str">
+        <x:v>维护智能体定义（agent_id）与账号（account_id）1:N 绑定（一个agent绑多账号），账号级记忆/动态提示词按 account_id 1:1 归属；叠加账号-终端-代理绑定（1:1:1）形成行动关系（agent_id:account_id:终端:代理 IP = 1:N:1:1）；账号被封后支持账号资产迁移（账号级记忆/动态提示词迁移到新账号，agent 不变）。</x:v>
+      </x:c>
+      <x:c r="F68" s="5" t="str">
+        <x:v>F-MC-13-01 智能体-账号 1:N 绑定维护；F-MC-13-02 行动关系维护；F-MC-13-03 账号资产抽取；F-MC-13-04 迁移目标账号校验；F-MC-13-05 继承写入与绑定切换</x:v>
       </x:c>
       <x:c r="G68" s="5" t="s">
         <x:v>578</x:v>
@@ -7166,11 +7166,11 @@
       <x:c r="D69" s="7" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="E69" s="7" t="s">
-        <x:v>582</x:v>
-      </x:c>
-      <x:c r="F69" s="7" t="s">
-        <x:v>583</x:v>
+      <x:c r="E69" s="7" t="str">
+        <x:v>记录并维护 agent_id↔account_id 1:N 绑定关系（一个agent绑多账号）；账号级记忆/动态提示词按 account_id 1:1 归属；agent_id 由 SWM 分配经 II-14（agent_id+account_id 组合）同步至本子系统持存。</x:v>
+      </x:c>
+      <x:c r="F69" s="7" t="str">
+        <x:v>agent_id↔account_id 1:N；账号级记忆/动态提示词 account_id 1:1；记录维护</x:v>
       </x:c>
       <x:c r="G69" s="7" t="s">
         <x:v>578</x:v>
@@ -7186,17 +7186,17 @@
       <x:c r="B70" s="6" t="s">
         <x:v>585</x:v>
       </x:c>
-      <x:c r="C70" s="7" t="s">
-        <x:v>586</x:v>
+      <x:c r="C70" s="7" t="str">
+        <x:v>行动关系维护</x:v>
       </x:c>
       <x:c r="D70" s="7" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="E70" s="7" t="s">
-        <x:v>587</x:v>
-      </x:c>
-      <x:c r="F70" s="7" t="s">
-        <x:v>588</x:v>
+      <x:c r="E70" s="7" t="str">
+        <x:v>记录并维护 agent_id↔account_id↔终端↔代理 IP 行动关系，形成 1:N:1:1（agent:账号=1:N，账号:终端:IP=1:1:1）。</x:v>
+      </x:c>
+      <x:c r="F70" s="7" t="str">
+        <x:v>行动关系；1:N:1:1</x:v>
       </x:c>
       <x:c r="G70" s="7" t="s">
         <x:v>578</x:v>
@@ -7218,11 +7218,11 @@
       <x:c r="D71" s="7" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="E71" s="7" t="s">
-        <x:v>591</x:v>
-      </x:c>
-      <x:c r="F71" s="7" t="s">
-        <x:v>592</x:v>
+      <x:c r="E71" s="7" t="str">
+        <x:v>从被封禁账号抽取待迁移的账号级资产：账号级记忆数据、账号级动态提示词实例。</x:v>
+      </x:c>
+      <x:c r="F71" s="7" t="str">
+        <x:v>抽取账号级记忆/动态提示词实例；资产完整性校验</x:v>
       </x:c>
       <x:c r="G71" s="7" t="s">
         <x:v>578</x:v>
@@ -7296,8 +7296,8 @@
       <x:c r="D74" s="5" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="E74" s="5" t="s">
-        <x:v>88</x:v>
+      <x:c r="E74" s="5" t="str">
+        <x:v>作为智能体执行宿主，接收并持存 SWM 同步来的提示词包（以 agent_id+account_id 组合为标识，含提示词模板/账号级动态提示词实例/作业策略），任务执行时调用这些定义驱动设备作业，执行前校验行为风格一致性（不一致拒绝执行）；确立「SWM 提示词生成与记忆中心、MC 执行宿主」分工。</x:v>
       </x:c>
       <x:c r="F74" s="5" t="s">
         <x:v>601</x:v>
@@ -7322,8 +7322,8 @@
       <x:c r="D75" s="7" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="E75" s="7" t="s">
-        <x:v>606</x:v>
+      <x:c r="E75" s="7" t="str">
+        <x:v>以 agent_id+account_id 组合为主键接收 SWM 同步的提示词包(提示词模板/账号级动态提示词实例/作业策略)并持存，作为任务执行调用依据。</x:v>
       </x:c>
       <x:c r="F75" s="7" t="s">
         <x:v>607</x:v>
@@ -8143,7 +8143,7 @@
         <x:v>R-SWM-001~005</x:v>
       </x:c>
       <x:c r="E2" s="3" t="str">
-        <x:v>执行层的「提示词生成与记忆中心」：根据人设(画像/账号属性)生成驱动智能体作业的提示词并管理记忆，将生成的提示词包(人设标签/提示词/作业策略)以 agent_id(稳定逻辑标识)同步下发至 MC 持存，由 MC 的 agent-runtime 子模块运行；承担提示词与人设管理、提示词自动生成、记忆管理、智能体构建、智能体评测；不直接操作设备。提示词工程与评测以 coze-loop(Go)旁挂集成，其余组件用 Java(智能体域特例 CON-14)。</x:v>
+        <x:v>执行层的「提示词生成与记忆中心」：根据画像/账号属性生成驱动智能体作业的提示词模板并管理记忆，将生成的提示词包(提示词模板/账号级动态提示词实例/作业策略)以 agent_id+account_id 组合(模板按agent_id稳定逻辑标识、动态实例按account_id)同步下发至 MC 持存，由 MC 的 agent-runtime 子模块运行；承担提示词管理、提示词自动生成、记忆管理、智能体构建、智能体评测；不直接操作设备。提示词工程与评测以 coze-loop(Go)旁挂集成，其余组件用 Java(智能体域特例 CON-14)。</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
         <x:v>208</x:v>
@@ -8246,8 +8246,8 @@
       <x:c r="D6" s="5" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="E6" s="5" t="s">
-        <x:v>134</x:v>
+      <x:c r="E6" s="5" t="str">
+        <x:v>建立提示词模板库并按用途/平台/目标分类管理；对提示词模板进行版本管理，以 agent_id 为主键索引（模板共性），账号级动态提示词实例按 account_id 1:1 归属，支持版本对比/回滚/变更记录。</x:v>
       </x:c>
       <x:c r="F6" s="5" t="s">
         <x:v>729</x:v>
@@ -8298,8 +8298,8 @@
       <x:c r="D8" s="7" t="s">
         <x:v>721</x:v>
       </x:c>
-      <x:c r="E8" s="7" t="s">
-        <x:v>738</x:v>
+      <x:c r="E8" s="7" t="str">
+        <x:v>对提示词模板进行版本管理，以 agent_id 为主键索引（模板共性），账号级动态提示词实例按 account_id 索引（账号个性），支持版本对比、回滚与变更记录；版本回滚失败时告警。</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
         <x:v>739</x:v>
@@ -8507,7 +8507,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E16" s="5" t="str">
-        <x:v>根据人设标签配置提示词与作业策略，组装为提示词包(人设标签/提示词/作业策略)并以 agent_id(稳定逻辑标识)为标识，经 II-14 同步至 MC 持存、供 OCC 作战编排引用。记忆不在提示词包内，由记忆服务独立承载。</x:v>
+        <x:v>根据画像/账号属性配置提示词模板与作业策略，组装为提示词包(提示词模板/账号级动态提示词实例/作业策略)并以 agent_id+account_id 组合为标识(模板按agent_id稳定逻辑标识、动态实例按account_id)，经 II-14 同步至 MC 持存、供 OCC 作战编排引用。一个agent可绑N个账号，每账号独立动态实例。记忆不在提示词包内，由记忆服务(account_id主键)独立承载。</x:v>
       </x:c>
       <x:c r="F16" s="5" t="str">
         <x:v>F-SWM-05-01 提示词包构建；F-SWM-05-02 账号绑定引用；F-SWM-05-03 同步至 MC 持存；F-SWM-05-04 OCC 智能体节点定义来源</x:v>
@@ -8559,7 +8559,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="E18" s="7" t="str">
-        <x:v>提示词包与账号严格 1:1 绑定(agent_id↔account_id)，绑定关系由 MC 维护，本子系统构建时引用 account_id。</x:v>
+        <x:v>提示词模板与账号 1:N 绑定(agent_id↔account_id，一个agent绑多账号)，每账号独立动态提示词实例(account_id 1:1)；绑定关系由 MC 维护，本子系统构建时引用 account_id。</x:v>
       </x:c>
       <x:c r="F18" s="7" t="s">
         <x:v>789</x:v>
@@ -8979,8 +8979,8 @@
       <x:c r="D31" s="7" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="E31" s="7" t="s">
-        <x:v>804</x:v>
+      <x:c r="E31" s="7" t="str">
+        <x:v>生成的提示词模板纳入版本管理(以 agent_id 索引，模板共性)，回写提示词库，账号级动态实例由 R-SWM-003 构建时基于模板结合账号属性生成；可由工程师审核微调后纳入 R-SWM-003 智能体构建。</x:v>
       </x:c>
       <x:c r="F31" s="7" t="s">
         <x:v>805</x:v>

--- a/公司项目/认知作战/文档/软件概要设计-模块功能拆分-v2.xlsx
+++ b/公司项目/认知作战/文档/软件概要设计-模块功能拆分-v2.xlsx
@@ -3115,7 +3115,7 @@
     <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </x:numFmts>
-  <x:fonts count="24">
+  <x:fonts count="26">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -3293,6 +3293,21 @@
       <x:name val="宋体"/>
       <x:charset val="0"/>
       <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="宋体"/>
+      <x:charset xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" val="134"/>
+      <x:scheme xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color theme="1"/>
+      <x:name val="宋体"/>
+      <x:charset xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" val="134"/>
+      <x:scheme xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" val="minor"/>
     </x:font>
   </x:fonts>
   <x:fills count="36">
@@ -3761,7 +3776,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3786,6 +3801,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -4248,28 +4275,28 @@
       <x:c r="B7" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C7" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F7" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G7" s="8" t="s">
-        <x:v>32</x:v>
+      <x:c r="C7" t="str">
+        <x:v>15个</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>R-MC-001~015</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
+        <x:v>统一自动化执行引擎与多终端执行网关：统一管理移动端（真机/云手机/ARM 板卡/虚拟化真机）与桌面端（指纹浏览器 Profile）两类执行终端；收口所有终端动作（可观测/可审计/可熔断）；承担账号资源平台级权威源与智能体执行宿主两项职责；M-MC-15（V3.0 / V3.10 新增）承载真机 Agent 运行时与编排（CON-15 独立部署单元，借鉴 SonicCloudOrg）。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7" ht="54">
       <x:c r="D8" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E8" t="s">
-        <x:v>34</x:v>
+      <x:c r="E8" t="str">
+        <x:v>执行终端接入与台账（终端资源池管理者；V3.0 / V3.10 边界调整：Agent 接入归 M-MC-15，本模块回归纯台账持有方）</x:v>
       </x:c>
       <x:c r="F8" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G8" s="8" t="s">
-        <x:v>36</x:v>
+      <x:c r="G8" s="8" t="str">
+        <x:v>维护四类执行终端（移动端真机/云手机/ARM 板卡/虚拟化真机、桌面端指纹浏览器 Profile）的台账数据库与状态查询——元数据 CRUD、分组标签、批量操作编排、REST 查询；订阅 M-MC-15 设备上下线事件写库；桌面端 Profile 创建（调 EI-06）仍归本模块。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7" ht="72">
@@ -5450,8 +5477,8 @@
       <x:c r="D3" s="5" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E3" s="5" t="s">
-        <x:v>36</x:v>
+      <x:c r="E3" s="5" t="str">
+        <x:v>维护四类执行终端（移动端真机/云手机/ARM 板卡/虚拟化真机、桌面端指纹浏览器 Profile）的台账数据库与状态查询——元数据 CRUD、分组标签、批量操作编排、REST 查询；订阅 M-MC-15 设备上下线事件写库；桌面端 Profile 创建（调 EI-06）仍归本模块。V3.0 / V3.10 边界调整：原 Agent 接入归 M-MC-15，本模块回归纯台账持有方。</x:v>
       </x:c>
       <x:c r="F3" s="5" t="s">
         <x:v>304</x:v>
@@ -5947,8 +5974,8 @@
       <x:c r="E22" s="5" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="F22" s="5" t="s">
-        <x:v>385</x:v>
+      <x:c r="F22" s="5" t="str">
+        <x:v>F-MC-05-01 动作收口与转发；F-MC-05-02 动作鉴权；F-MC-05-03 动作记录与上报；F-MC-05-04 异常熔断；F-MC-05-05 设备SDK接口与通道路由（V3.0 / V3.10 收缩为薄层，真机实现下沉 M-MC-15）</x:v>
       </x:c>
       <x:c r="G22" s="5" t="s">
         <x:v>386</x:v>
@@ -6068,23 +6095,23 @@
       <x:c r="B27" s="6" t="s">
         <x:v>407</x:v>
       </x:c>
-      <x:c r="C27" s="7" t="s">
-        <x:v>408</x:v>
+      <x:c r="C27" s="7" t="str">
+        <x:v>设备SDK接口与通道路由（V3.0 / V3.10 收缩为薄层）</x:v>
       </x:c>
       <x:c r="D27" s="7" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="E27" s="7" t="s">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="F27" s="7" t="s">
-        <x:v>410</x:v>
+      <x:c r="E27" s="7" t="str">
+        <x:v>本模块只持 DeviceSdk 统一接口（click/input/screenshot/install/execute）+ DeviceChannelRouter 按 terminal_type 路由；真机 RealDeviceSdk 实现下沉 M-MC-15，桌面端 ProfileSdk（CDP 直连 EI-06）留 V1.2；移动端 ADB/无障碍、桌面端 CDP 对上层透明。</x:v>
+      </x:c>
+      <x:c r="F27" s="7" t="str">
+        <x:v>DeviceSdk 接口定义；DeviceChannelRouter 按 terminal_type 路由；真机实现下沉 M-MC-15；其余 4 SDK 留 V1.2</x:v>
       </x:c>
       <x:c r="G27" s="7" t="s">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="H27" s="7" t="s">
-        <x:v>220</x:v>
+      <x:c r="H27" s="7" t="str">
+        <x:v>V3.0 / V3.10 接口/实现分离，真机实现归 M-MC-15，详见 SDD §5.2.1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:8" ht="67.5">
@@ -7437,6 +7464,188 @@
       </x:c>
       <x:c r="H79" s="7" t="s">
         <x:v>534</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="100" customHeight="1">
+      <x:c r="A80" s="9" t="str">
+        <x:v>②模块</x:v>
+      </x:c>
+      <x:c r="B80" s="9" t="str">
+        <x:v>M-MC-15</x:v>
+      </x:c>
+      <x:c r="C80" s="10" t="str">
+        <x:v>真机 Agent 运行时与编排（真机落地执行单元，V3.0 / V3.10 新增，CON-15）</x:v>
+      </x:c>
+      <x:c r="D80" s="9" t="str">
+        <x:v>R-MC-015</x:v>
+      </x:c>
+      <x:c r="E80" s="10" t="str">
+        <x:v>作为所有真机动作的物理落地单元和 Agent 连接的生命周期管理者。双形态——M-MC-15.c 中心侧编排器（mc-service 同进程）持 II-02 WS endpoint，全权管 Agent 注册/心跳/占用锁/媒体面协商；作为 RealDeviceSdk 的实现方接收 M-MC-05 网关下发的动作。M-MC-15.a 设备主机侧 Agent 运行时（独立部署单元，每台插真机的主机一台 Spring Boot 进程）是 MC 体系内唯一触碰真机的进程，承载 ddmlib+uia2+scrcpy。借鉴 SonicCloudOrg（已 archived，Apache 2.0 fork 自维护）。</x:v>
+      </x:c>
+      <x:c r="F80" s="10" t="str">
+        <x:v>F-MC-15-01 Agent注册与鉴权握手；F-MC-15-02 心跳保活与在线状态判定；F-MC-15-03 设备占用锁；F-MC-15-04 ADB控制通道；F-MC-15-05 无障碍控制通道(uia2)；F-MC-15-06 远控画面源(scrcpy)</x:v>
+      </x:c>
+      <x:c r="G80" s="9" t="str">
+        <x:v>SRS R-MC-015</x:v>
+      </x:c>
+      <x:c r="H80" s="10" t="str">
+        <x:v>对应 R-MC-015，CON-15 Agent 独立部署单元；F-MC-05-05 真机实现下沉本模块；动作路径 M-MC-05→M-MC-15.c→II-02→M-MC-15.a→ADB/uia2/scrcpy；V1.2 加 iOS/热插拔/设备保护/远程升级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="36" customHeight="1">
+      <x:c r="A81" s="11" t="str">
+        <x:v>③功能</x:v>
+      </x:c>
+      <x:c r="B81" s="11" t="str">
+        <x:v>F-MC-15-01</x:v>
+      </x:c>
+      <x:c r="C81" s="12" t="str">
+        <x:v>Agent 注册与鉴权握手</x:v>
+      </x:c>
+      <x:c r="D81" s="11" t="str">
+        <x:v>R-MC-015</x:v>
+      </x:c>
+      <x:c r="E81" s="12" t="str">
+        <x:v>Agent 启动经 II-02 WS 连中心侧编排器，agentKey 配置文件校验 + 版本/能力上报(auth 消息)；中心侧回 authResult 分配 agentId</x:v>
+      </x:c>
+      <x:c r="F81" s="12" t="str">
+        <x:v>agentKey 配置校验；版本/能力上报；agentId 分配</x:v>
+      </x:c>
+      <x:c r="G81" s="11" t="str">
+        <x:v>SRS R-MC-015</x:v>
+      </x:c>
+      <x:c r="H81" s="12" t="str">
+        <x:v>MVP 不做密钥轮换；Sonic TransportServer auth 对应</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="36" customHeight="1">
+      <x:c r="A82" s="11" t="str">
+        <x:v>③功能</x:v>
+      </x:c>
+      <x:c r="B82" s="11" t="str">
+        <x:v>F-MC-15-02</x:v>
+      </x:c>
+      <x:c r="C82" s="12" t="str">
+        <x:v>心跳保活与在线状态判定</x:v>
+      </x:c>
+      <x:c r="D82" s="11" t="str">
+        <x:v>R-MC-015</x:v>
+      </x:c>
+      <x:c r="E82" s="12" t="str">
+        <x:v>Agent 周期发 heartBeat(默认30s)，超时(默认90s)判掉线；推 terminal_offline 事件给 M-MC-01 更新台账在线状态</x:v>
+      </x:c>
+      <x:c r="F82" s="12" t="str">
+        <x:v>30s 心跳；90s 超时判离线；推事件给 M-MC-01</x:v>
+      </x:c>
+      <x:c r="G82" s="11" t="str">
+        <x:v>SRS R-MC-015</x:v>
+      </x:c>
+      <x:c r="H82" s="12" t="str">
+        <x:v>台账在线状态数据源</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="36" customHeight="1">
+      <x:c r="A83" s="11" t="str">
+        <x:v>③功能</x:v>
+      </x:c>
+      <x:c r="B83" s="11" t="str">
+        <x:v>F-MC-15-03</x:v>
+      </x:c>
+      <x:c r="C83" s="12" t="str">
+        <x:v>设备占用锁</x:v>
+      </x:c>
+      <x:c r="D83" s="11" t="str">
+        <x:v>R-MC-015</x:v>
+      </x:c>
+      <x:c r="E83" s="12" t="str">
+        <x:v>设备占用锁(occupy/release)，一台设备同时只让一个会话用(远控/自动化互斥)；内存锁(单 mc-service 副本)，不做分布式锁</x:v>
+      </x:c>
+      <x:c r="F83" s="12" t="str">
+        <x:v>occupy/release；远控/自动化互斥；内存锁</x:v>
+      </x:c>
+      <x:c r="G83" s="11" t="str">
+        <x:v>SRS R-MC-015</x:v>
+      </x:c>
+      <x:c r="H83" s="12" t="str">
+        <x:v>防远控和自动化并发打架；分布式锁留 V1.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="36" customHeight="1">
+      <x:c r="A84" s="11" t="str">
+        <x:v>③功能</x:v>
+      </x:c>
+      <x:c r="B84" s="11" t="str">
+        <x:v>F-MC-15-04</x:v>
+      </x:c>
+      <x:c r="C84" s="12" t="str">
+        <x:v>ADB 控制通道</x:v>
+      </x:c>
+      <x:c r="D84" s="11" t="str">
+        <x:v>R-MC-015</x:v>
+      </x:c>
+      <x:c r="E84" s="12" t="str">
+        <x:v>ddmlib 实现 ADB 通道：install/uninstall/pressKey/reboot/screenshot；动作子集(不做交互式 shell 终端)；经 runAction 消息收口(与 F-MC-15-05 共享)</x:v>
+      </x:c>
+      <x:c r="F84" s="12" t="str">
+        <x:v>install/pressKey/reboot/screenshot；ddmlib 封装</x:v>
+      </x:c>
+      <x:c r="G84" s="11" t="str">
+        <x:v>SRS R-MC-015</x:v>
+      </x:c>
+      <x:c r="H84" s="12" t="str">
+        <x:v>Sonic AndroidDeviceBridgeTool 对应</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="36" customHeight="1">
+      <x:c r="A85" s="11" t="str">
+        <x:v>③功能</x:v>
+      </x:c>
+      <x:c r="B85" s="11" t="str">
+        <x:v>F-MC-15-05</x:v>
+      </x:c>
+      <x:c r="C85" s="12" t="str">
+        <x:v>无障碍控制通道(uia2)</x:v>
+      </x:c>
+      <x:c r="D85" s="11" t="str">
+        <x:v>R-MC-015</x:v>
+      </x:c>
+      <x:c r="E85" s="12" t="str">
+        <x:v>引 sonic-driver-core(Maven jar) 封装 uiautomator2-server：UI 元素 find/click/sendKeys/swipe；断言类步骤全砍；经 runAction 消息收口</x:v>
+      </x:c>
+      <x:c r="F85" s="12" t="str">
+        <x:v>find/click/sendKeys/swipe；sonic-driver-core 封装</x:v>
+      </x:c>
+      <x:c r="G85" s="11" t="str">
+        <x:v>SRS R-MC-015</x:v>
+      </x:c>
+      <x:c r="H85" s="12" t="str">
+        <x:v>依赖 archived 库 sonic-driver-core；uia2 协议本身稳定</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="48" customHeight="1">
+      <x:c r="A86" s="11" t="str">
+        <x:v>③功能</x:v>
+      </x:c>
+      <x:c r="B86" s="11" t="str">
+        <x:v>F-MC-15-06</x:v>
+      </x:c>
+      <x:c r="C86" s="12" t="str">
+        <x:v>远控画面源(scrcpy)</x:v>
+      </x:c>
+      <x:c r="D86" s="11" t="str">
+        <x:v>R-MC-015</x:v>
+      </x:c>
+      <x:c r="E86" s="12" t="str">
+        <x:v>抄 Sonic ScrcpyInputSocketThread/OutputSocketThread(Apache2.0)；启动 scrcpy server 抓 H.264 → 经 startScrcpy 推到 mc-sfu 指定端口；本功能只产画面源，WebRTC 转发由 M-MC-04 mc-sfu 承担</x:v>
+      </x:c>
+      <x:c r="F86" s="12" t="str">
+        <x:v>scrcpy 启动+H.264 推流到 mc-sfu；不经 mc-service WS 转发</x:v>
+      </x:c>
+      <x:c r="G86" s="11" t="str">
+        <x:v>SRS R-MC-015</x:v>
+      </x:c>
+      <x:c r="H86" s="12" t="str">
+        <x:v>画面源与转发分离；媒体面 Agent→mc-sfu 端口直推</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
